--- a/songs/Titanium_v1/quelle/struktur.xlsx
+++ b/songs/Titanium_v1/quelle/struktur.xlsx
@@ -436,15 +436,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,6 +469,7 @@
       <c r="C2" s="2" t="n">
         <v>11</v>
       </c>
+      <c r="D2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -478,6 +480,7 @@
       <c r="C3" s="2" t="n">
         <v>126</v>
       </c>
+      <c r="D3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -488,6 +491,7 @@
       <c r="C4" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="D4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -502,20 +506,25 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Effektidee</t>
+          <t>Effekt (füllt KI)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>Änderungswunsch</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>Energie 0-5</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>BPM pro Part</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>bisher (alter Code)</t>
         </is>
@@ -530,13 +539,21 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progBlack(6000, 5)   (Matrix: progScrollText("Titanium by David Guetta", 14900, 75, getRandomColor(), 5))
+progCircles(14950, 10, 475)
+! der alte Code teilt diese 2 Parts anders auf (Summe identisch)</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>progBlack(6000, 5)   (Matrix: progScrollText("Titanium by David Guetta", 14900, 75, getRandomColor(), 5))
 progCircles(14950, 10, 475)
@@ -554,12 +571,13 @@
         </is>
       </c>
       <c r="C7" s="6" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -570,13 +588,19 @@
           <t>v1: u shout it out</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progPalette(15240, 6, 15)</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>progPalette(15240, 6, 15)</t>
         </is>
@@ -591,13 +615,19 @@
           <t>v1: im criticised</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progPalette(15240, 3, 20)</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>progPalette(15240, 3, 20)</t>
         </is>
@@ -612,13 +642,19 @@
           <t>im bulletproof</t>
         </is>
       </c>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progMatrixScanner(15235, 25, 20)</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>progMatrixScanner(15235, 25, 20)</t>
         </is>
@@ -633,13 +669,19 @@
           <t>chorus 1</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFullColors(15240, 30, 475)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>progFullColors(15240, 30, 475)</t>
         </is>
@@ -654,13 +696,20 @@
           <t>bridge</t>
         </is>
       </c>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(7620, 4, 32)
+! Excel: 8 Takte, der alte Code ist anders</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(7620, 4, 32)
 ! Excel: 8 Takte, der alte Code ist anders</t>
@@ -676,13 +725,19 @@
           <t>half time</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progMatrixScanner(7620, 35, 20)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>progMatrixScanner(7620, 35, 20)</t>
         </is>
@@ -697,13 +752,19 @@
           <t>v2: cut me down</t>
         </is>
       </c>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progPalette(15235, 9, 40)</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>progPalette(15235, 9, 40)</t>
         </is>
@@ -718,13 +779,19 @@
           <t>v2: race your voice</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progWaterRipple(15240, 45, 50, true, false)</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(15240, 45, 50, true, false)</t>
         </is>
@@ -739,13 +806,19 @@
           <t>im bulletproof</t>
         </is>
       </c>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progMatrixScanner(15235, 50, 20)</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>progMatrixScanner(15235, 50, 20)</t>
         </is>
@@ -760,13 +833,19 @@
           <t>chorus 2</t>
         </is>
       </c>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFullColors(15240, 55, 475)</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>progFullColors(15240, 55, 475)</t>
         </is>
@@ -781,13 +860,19 @@
           <t>bridge</t>
         </is>
       </c>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(14760, 8, 60)</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(14760, 8, 60)</t>
         </is>
@@ -802,13 +887,19 @@
           <t>Pause: STONE HEART ..</t>
         </is>
       </c>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progBlack(15715, 65)</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>progBlack(15715, 65)</t>
         </is>
@@ -823,13 +914,19 @@
           <t>chorus 3</t>
         </is>
       </c>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(30480, 1, 75, 1, 100, 2000)</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(30480, 1, 75, 1, 100, 2000)</t>
         </is>
@@ -844,13 +941,19 @@
           <t>bridge triolisch</t>
         </is>
       </c>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(13330, 80, 175, 255, 255, 255)</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>progStrobo(13330, 80, 175, 255, 255, 255)</t>
         </is>
@@ -865,13 +968,19 @@
           <t>matrix</t>
         </is>
       </c>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+matrixMovieFX(7620, 85, 100, 6)</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>matrixMovieFX(7620, 85, 100, 6)</t>
         </is>
@@ -891,10 +1000,10 @@
           <t>10 sek. BLACK</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
         <v>0</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <f>$C$3</f>
         <v/>
       </c>

--- a/songs/Titanium_v1/quelle/struktur.xlsx
+++ b/songs/Titanium_v1/quelle/struktur.xlsx
@@ -532,7 +532,7 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>6.25</v>
+        <v>7.25</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -581,7 +581,7 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
@@ -608,7 +608,7 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>90.75</v>
+        <v>91.75</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>

--- a/songs/Titanium_v1/quelle/struktur.xlsx
+++ b/songs/Titanium_v1/quelle/struktur.xlsx
@@ -436,16 +436,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -470,6 +471,7 @@
         <v>11</v>
       </c>
       <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -481,6 +483,7 @@
         <v>126</v>
       </c>
       <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -492,6 +495,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -516,15 +520,20 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>Neuer Vorschlag (KI)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>Energie 0-5</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>BPM pro Part</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>bisher (alter Code)</t>
         </is>
@@ -548,12 +557,13 @@
         </is>
       </c>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>progBlack(6000, 5)   (Matrix: progScrollText("Titanium by David Guetta", 14900, 75, getRandomColor(), 5))
 progCircles(14950, 10, 475)
@@ -572,12 +582,17 @@
       </c>
       <c r="C7" s="6" t="n"/>
       <c r="D7" s="6" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G7" s="6" t="n"/>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Szene Glow, ICE, weich eingeblendet (fade_in 4 Beats): füllt sich langsam in Eisblau (bisher Kreise im Beat).</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -595,12 +610,17 @@
         </is>
       </c>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Szene Calm, ICE, Farbwanderung (triad, 2 Takte): ruhiges Atmen, nur Gitarre und Stimme.</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>progPalette(15240, 6, 15)</t>
         </is>
@@ -622,12 +642,17 @@
         </is>
       </c>
       <c r="D9" s="6" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Szene Rain, ROYAL: Leuchtspuren, kleine Steigerung; weich eingeblendet (fade, 2 Beats).</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>progPalette(15240, 3, 20)</t>
         </is>
@@ -649,12 +674,17 @@
         </is>
       </c>
       <c r="D10" s="6" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Szene Verse, ICE, darüber baut sich ein Glitzern auf (Ebene Sparkle, fade_in über 8 Takte); letzter Takt Szene Buildup (tail 4 Beats), Explosion auf "I am titanium". Fester Look für beide.</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>progMatrixScanner(15235, 25, 20)</t>
         </is>
@@ -676,12 +706,17 @@
         </is>
       </c>
       <c r="D11" s="6" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Szene Colors, WHITE -&gt; Farbwanderung nach ICE, soft 30; Blinder auf den Einsatz (2 Beats). Auf der Matrix "TITANIUM" über der Szene, blendet nach 2 Takten aus.</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>progFullColors(15240, 30, 475)</t>
         </is>
@@ -704,12 +739,17 @@
         </is>
       </c>
       <c r="D12" s="6" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Der Drop: Szene Drop, NEON (Schockwellen und Beat-Blitze) statt dezenter Einzelblitze; weißer Blitz auf den Einsatz (Übergang flash).</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(7620, 4, 32)
 ! Excel: 8 Takte, der alte Code ist anders</t>
@@ -732,12 +772,17 @@
         </is>
       </c>
       <c r="D13" s="6" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>Blinder auf jede Halbe (alle 2 Beats, je 1,5 Beats lang) über dunklem Atmen - Halftime sichtbar.</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>progMatrixScanner(7620, 35, 20)</t>
         </is>
@@ -759,12 +804,17 @@
         </is>
       </c>
       <c r="D14" s="6" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Szene DNA Flip, ICE: stehende Helix auf der Matrix, alle anderen pulsieren einmal je Takt.</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>progPalette(15235, 9, 40)</t>
         </is>
@@ -786,12 +836,17 @@
         </is>
       </c>
       <c r="D15" s="6" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Wasserringe bleiben, Farbwanderung.</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(15240, 45, 50, true, false)</t>
         </is>
@@ -813,12 +868,17 @@
         </is>
       </c>
       <c r="D16" s="6" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>wie beim ersten Mal (Verse ICE + Glitzern, Buildup-Tail).</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>progMatrixScanner(15235, 50, 20)</t>
         </is>
@@ -840,12 +900,17 @@
         </is>
       </c>
       <c r="D17" s="6" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>wie chorus 1 (Colors WHITE/ICE, Text TITANIUM), dazu blitzen die Lampen weiß auf 2 und 4.</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>progFullColors(15240, 55, 475)</t>
         </is>
@@ -867,12 +932,17 @@
         </is>
       </c>
       <c r="D18" s="6" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Drop wie beim ersten Mal (Szene Drop, NEON); starker Blinder auf der letzten Viertel (Takt 91,5), danach Schwarz.</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(14760, 8, 60)</t>
         </is>
@@ -894,12 +964,17 @@
         </is>
       </c>
       <c r="D19" s="6" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Statt 8 Takten Schwarz: nur Gitarre und Bass zeigen einen Herzschlag in Rot (progHeartbeat), Lampen und Matrix bleiben dunkel. In den letzten 2 Takten blendet ein Blinder ein, voll auf Takt 100.</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>progBlack(15715, 65)</t>
         </is>
@@ -921,12 +996,17 @@
         </is>
       </c>
       <c r="D20" s="6" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Anwachsende Einzelblitze bleiben (16 Takte), in ICE -&gt; ab der Hälfte FIRE (bei Takt 108 eine eigene Zeile anlegen); der Blinder aus der Pause steht auf dem Einsatz.</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(30480, 1, 75, 1, 100, 2000)</t>
         </is>
@@ -948,12 +1028,17 @@
         </is>
       </c>
       <c r="D21" s="6" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Weißer Strobo bleibt (triolisch); drei kurze Blinder auf den letzten drei Vierteln (Takt 122,25 / 122,5 / 122,75).</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>progStrobo(13330, 80, 175, 255, 255, 255)</t>
         </is>
@@ -975,12 +1060,17 @@
         </is>
       </c>
       <c r="D22" s="6" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Szene Fadeout, ICE: blendet über die 4 Takte weich nach Schwarz (die Matrix kann ihren Regen behalten).</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>matrixMovieFX(7620, 85, 100, 6)</t>
         </is>
@@ -1000,10 +1090,10 @@
           <t>10 sek. BLACK</t>
         </is>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>0</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <f>$C$3</f>
         <v/>
       </c>

--- a/songs/Titanium_v1/quelle/struktur.xlsx
+++ b/songs/Titanium_v1/quelle/struktur.xlsx
@@ -433,10 +433,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -539,7 +539,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" collapsed="1">
       <c r="A6" s="4" t="n">
         <v>1</v>
       </c>
@@ -550,10 +550,8 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>alter Code (handgeschrieben, läuft so in der Firmware):
-progBlack(6000, 5)   (Matrix: progScrollText("Titanium by David Guetta", 14900, 75, getRandomColor(), 5))
-progCircles(14950, 10, 475)
-! der alte Code teilt diese 2 Parts anders auf (Summe identisch)</t>
+          <t>progBlack(11905, 3), Farben SCHEME_ICE
+Alles schwarz bis zum Einsatz (die Matrix zeigt den Titel-Lauftext).</t>
         </is>
       </c>
       <c r="D6" s="6" t="n"/>
@@ -571,529 +569,6404 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="1" outlineLevel="2">
       <c r="A7" s="4" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>intro</t>
-        </is>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="B7" s="5" t="n"/>
       <c r="C7" s="6" t="n"/>
       <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="6" t="n"/>
+    </row>
+    <row r="8" hidden="1" outlineLevel="2">
+      <c r="A8" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="6" t="n"/>
+    </row>
+    <row r="9" hidden="1" outlineLevel="2">
+      <c r="A9" s="4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="6" t="n"/>
+    </row>
+    <row r="10" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="6" t="n"/>
+    </row>
+    <row r="11" hidden="1" outlineLevel="2">
+      <c r="A11" s="4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="6" t="n"/>
+    </row>
+    <row r="12" hidden="1" outlineLevel="2">
+      <c r="A12" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="6" t="n"/>
+    </row>
+    <row r="13" hidden="1" outlineLevel="2">
+      <c r="A13" s="4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="6" t="n"/>
+    </row>
+    <row r="14" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A14" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="6" t="n"/>
+    </row>
+    <row r="15" hidden="1" outlineLevel="2">
+      <c r="A15" s="4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="6" t="n"/>
+    </row>
+    <row r="16" hidden="1" outlineLevel="2">
+      <c r="A16" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="6" t="n"/>
+    </row>
+    <row r="17" hidden="1" outlineLevel="2">
+      <c r="A17" s="4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="6" t="n"/>
+    </row>
+    <row r="18" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A18" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="6" t="n"/>
+    </row>
+    <row r="19" hidden="1" outlineLevel="2">
+      <c r="A19" s="4" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="6" t="n"/>
+    </row>
+    <row r="20" hidden="1" outlineLevel="2">
+      <c r="A20" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="6" t="n"/>
+    </row>
+    <row r="21" hidden="1" outlineLevel="2">
+      <c r="A21" s="4" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="6" t="n"/>
+    </row>
+    <row r="22" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A22" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="6" t="n"/>
+    </row>
+    <row r="23" hidden="1" outlineLevel="2">
+      <c r="A23" s="4" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="6" t="n"/>
+    </row>
+    <row r="24" hidden="1" outlineLevel="2">
+      <c r="A24" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="6" t="n"/>
+    </row>
+    <row r="25" hidden="1" outlineLevel="2">
+      <c r="A25" s="4" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="6" t="n"/>
+    </row>
+    <row r="26" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A26" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="6" t="n"/>
+    </row>
+    <row r="27" hidden="1" outlineLevel="2">
+      <c r="A27" s="4" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="6" t="n"/>
+    </row>
+    <row r="28" hidden="1" outlineLevel="2">
+      <c r="A28" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="6" t="n"/>
+    </row>
+    <row r="29" hidden="1" outlineLevel="2">
+      <c r="A29" s="4" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="6" t="n"/>
+    </row>
+    <row r="30" hidden="1" outlineLevel="1">
+      <c r="A30" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="6" t="n"/>
+    </row>
+    <row r="31" collapsed="1">
+      <c r="A31" s="4" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>intro</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_GLOW, Farben SCHEME_ICE
+Ausgabe: blendet 1905 ms ein
+Weich eingeblendet: die Geräte füllen sich langsam in Eisblau.</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="inlineStr">
         <is>
           <t>Szene Glow, ICE, weich eingeblendet (fade_in 4 Beats): füllt sich langsam in Eisblau (bisher Kreise im Beat).</t>
         </is>
       </c>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5">
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H7" s="6" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="H31" s="6" t="n"/>
+    </row>
+    <row r="32" hidden="1" outlineLevel="2">
+      <c r="A32" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5" t="n"/>
+      <c r="H32" s="6" t="n"/>
+    </row>
+    <row r="33" hidden="1" outlineLevel="2">
+      <c r="A33" s="4" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="B33" s="5" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="6" t="n"/>
+    </row>
+    <row r="34" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A34" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B34" s="5" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="6" t="n"/>
+    </row>
+    <row r="35" hidden="1" outlineLevel="2">
+      <c r="A35" s="4" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="B35" s="5" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="6" t="n"/>
+      <c r="F35" s="5" t="n"/>
+      <c r="G35" s="5" t="n"/>
+      <c r="H35" s="6" t="n"/>
+    </row>
+    <row r="36" hidden="1" outlineLevel="2">
+      <c r="A36" s="4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="B36" s="5" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="6" t="n"/>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="5" t="n"/>
+      <c r="H36" s="6" t="n"/>
+    </row>
+    <row r="37" hidden="1" outlineLevel="2">
+      <c r="A37" s="4" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="B37" s="5" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="6" t="n"/>
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="5" t="n"/>
+      <c r="H37" s="6" t="n"/>
+    </row>
+    <row r="38" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A38" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B38" s="5" t="n"/>
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="6" t="n"/>
+      <c r="E38" s="6" t="n"/>
+      <c r="F38" s="5" t="n"/>
+      <c r="G38" s="5" t="n"/>
+      <c r="H38" s="6" t="n"/>
+    </row>
+    <row r="39" hidden="1" outlineLevel="2">
+      <c r="A39" s="4" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="B39" s="5" t="n"/>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="6" t="n"/>
+      <c r="E39" s="6" t="n"/>
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="5" t="n"/>
+      <c r="H39" s="6" t="n"/>
+    </row>
+    <row r="40" hidden="1" outlineLevel="2">
+      <c r="A40" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="B40" s="5" t="n"/>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="6" t="n"/>
+      <c r="E40" s="6" t="n"/>
+      <c r="F40" s="5" t="n"/>
+      <c r="G40" s="5" t="n"/>
+      <c r="H40" s="6" t="n"/>
+    </row>
+    <row r="41" hidden="1" outlineLevel="2">
+      <c r="A41" s="4" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="B41" s="5" t="n"/>
+      <c r="C41" s="6" t="n"/>
+      <c r="D41" s="6" t="n"/>
+      <c r="E41" s="6" t="n"/>
+      <c r="F41" s="5" t="n"/>
+      <c r="G41" s="5" t="n"/>
+      <c r="H41" s="6" t="n"/>
+    </row>
+    <row r="42" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A42" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B42" s="5" t="n"/>
+      <c r="C42" s="6" t="n"/>
+      <c r="D42" s="6" t="n"/>
+      <c r="E42" s="6" t="n"/>
+      <c r="F42" s="5" t="n"/>
+      <c r="G42" s="5" t="n"/>
+      <c r="H42" s="6" t="n"/>
+    </row>
+    <row r="43" hidden="1" outlineLevel="2">
+      <c r="A43" s="4" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="B43" s="5" t="n"/>
+      <c r="C43" s="6" t="n"/>
+      <c r="D43" s="6" t="n"/>
+      <c r="E43" s="6" t="n"/>
+      <c r="F43" s="5" t="n"/>
+      <c r="G43" s="5" t="n"/>
+      <c r="H43" s="6" t="n"/>
+    </row>
+    <row r="44" hidden="1" outlineLevel="2">
+      <c r="A44" s="4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B44" s="5" t="n"/>
+      <c r="C44" s="6" t="n"/>
+      <c r="D44" s="6" t="n"/>
+      <c r="E44" s="6" t="n"/>
+      <c r="F44" s="5" t="n"/>
+      <c r="G44" s="5" t="n"/>
+      <c r="H44" s="6" t="n"/>
+    </row>
+    <row r="45" hidden="1" outlineLevel="2">
+      <c r="A45" s="4" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="B45" s="5" t="n"/>
+      <c r="C45" s="6" t="n"/>
+      <c r="D45" s="6" t="n"/>
+      <c r="E45" s="6" t="n"/>
+      <c r="F45" s="5" t="n"/>
+      <c r="G45" s="5" t="n"/>
+      <c r="H45" s="6" t="n"/>
+    </row>
+    <row r="46" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A46" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B46" s="5" t="n"/>
+      <c r="C46" s="6" t="n"/>
+      <c r="D46" s="6" t="n"/>
+      <c r="E46" s="6" t="n"/>
+      <c r="F46" s="5" t="n"/>
+      <c r="G46" s="5" t="n"/>
+      <c r="H46" s="6" t="n"/>
+    </row>
+    <row r="47" hidden="1" outlineLevel="2">
+      <c r="A47" s="4" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="B47" s="5" t="n"/>
+      <c r="C47" s="6" t="n"/>
+      <c r="D47" s="6" t="n"/>
+      <c r="E47" s="6" t="n"/>
+      <c r="F47" s="5" t="n"/>
+      <c r="G47" s="5" t="n"/>
+      <c r="H47" s="6" t="n"/>
+    </row>
+    <row r="48" hidden="1" outlineLevel="2">
+      <c r="A48" s="4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="B48" s="5" t="n"/>
+      <c r="C48" s="6" t="n"/>
+      <c r="D48" s="6" t="n"/>
+      <c r="E48" s="6" t="n"/>
+      <c r="F48" s="5" t="n"/>
+      <c r="G48" s="5" t="n"/>
+      <c r="H48" s="6" t="n"/>
+    </row>
+    <row r="49" hidden="1" outlineLevel="2">
+      <c r="A49" s="4" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="B49" s="5" t="n"/>
+      <c r="C49" s="6" t="n"/>
+      <c r="D49" s="6" t="n"/>
+      <c r="E49" s="6" t="n"/>
+      <c r="F49" s="5" t="n"/>
+      <c r="G49" s="5" t="n"/>
+      <c r="H49" s="6" t="n"/>
+    </row>
+    <row r="50" collapsed="1">
+      <c r="A50" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>v1: u shout it out</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>alter Code (handgeschrieben, läuft so in der Firmware):
-progPalette(15240, 6, 15)</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_CALM, Farben SCHEME_ICE, Farbwanderung to triad, per 8
+Nur Gitarre und Stimme: ruhiges Atmen in Eisblau, die Farben wandern alle 2 Takte nach Pink/Gelb und zurück.</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="n"/>
+      <c r="E50" s="6" t="inlineStr">
         <is>
           <t>Szene Calm, ICE, Farbwanderung (triad, 2 Takte): ruhiges Atmen, nur Gitarre und Stimme.</t>
         </is>
       </c>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5">
+      <c r="F50" s="5" t="n"/>
+      <c r="G50" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H50" s="6" t="inlineStr">
         <is>
           <t>progPalette(15240, 6, 15)</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="n">
+    <row r="51" hidden="1" outlineLevel="2">
+      <c r="A51" s="4" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="B51" s="5" t="n"/>
+      <c r="C51" s="6" t="n"/>
+      <c r="D51" s="6" t="n"/>
+      <c r="E51" s="6" t="n"/>
+      <c r="F51" s="5" t="n"/>
+      <c r="G51" s="5" t="n"/>
+      <c r="H51" s="6" t="n"/>
+    </row>
+    <row r="52" hidden="1" outlineLevel="2">
+      <c r="A52" s="4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="B52" s="5" t="n"/>
+      <c r="C52" s="6" t="n"/>
+      <c r="D52" s="6" t="n"/>
+      <c r="E52" s="6" t="n"/>
+      <c r="F52" s="5" t="n"/>
+      <c r="G52" s="5" t="n"/>
+      <c r="H52" s="6" t="n"/>
+    </row>
+    <row r="53" hidden="1" outlineLevel="2">
+      <c r="A53" s="4" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="B53" s="5" t="n"/>
+      <c r="C53" s="6" t="n"/>
+      <c r="D53" s="6" t="n"/>
+      <c r="E53" s="6" t="n"/>
+      <c r="F53" s="5" t="n"/>
+      <c r="G53" s="5" t="n"/>
+      <c r="H53" s="6" t="n"/>
+    </row>
+    <row r="54" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A54" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B54" s="5" t="n"/>
+      <c r="C54" s="6" t="n"/>
+      <c r="D54" s="6" t="n"/>
+      <c r="E54" s="6" t="n"/>
+      <c r="F54" s="5" t="n"/>
+      <c r="G54" s="5" t="n"/>
+      <c r="H54" s="6" t="n"/>
+    </row>
+    <row r="55" hidden="1" outlineLevel="2">
+      <c r="A55" s="4" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="B55" s="5" t="n"/>
+      <c r="C55" s="6" t="n"/>
+      <c r="D55" s="6" t="n"/>
+      <c r="E55" s="6" t="n"/>
+      <c r="F55" s="5" t="n"/>
+      <c r="G55" s="5" t="n"/>
+      <c r="H55" s="6" t="n"/>
+    </row>
+    <row r="56" hidden="1" outlineLevel="2">
+      <c r="A56" s="4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B56" s="5" t="n"/>
+      <c r="C56" s="6" t="n"/>
+      <c r="D56" s="6" t="n"/>
+      <c r="E56" s="6" t="n"/>
+      <c r="F56" s="5" t="n"/>
+      <c r="G56" s="5" t="n"/>
+      <c r="H56" s="6" t="n"/>
+    </row>
+    <row r="57" hidden="1" outlineLevel="2">
+      <c r="A57" s="4" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="B57" s="5" t="n"/>
+      <c r="C57" s="6" t="n"/>
+      <c r="D57" s="6" t="n"/>
+      <c r="E57" s="6" t="n"/>
+      <c r="F57" s="5" t="n"/>
+      <c r="G57" s="5" t="n"/>
+      <c r="H57" s="6" t="n"/>
+    </row>
+    <row r="58" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A58" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B58" s="5" t="n"/>
+      <c r="C58" s="6" t="n"/>
+      <c r="D58" s="6" t="n"/>
+      <c r="E58" s="6" t="n"/>
+      <c r="F58" s="5" t="n"/>
+      <c r="G58" s="5" t="n"/>
+      <c r="H58" s="6" t="n"/>
+    </row>
+    <row r="59" hidden="1" outlineLevel="2">
+      <c r="A59" s="4" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="B59" s="5" t="n"/>
+      <c r="C59" s="6" t="n"/>
+      <c r="D59" s="6" t="n"/>
+      <c r="E59" s="6" t="n"/>
+      <c r="F59" s="5" t="n"/>
+      <c r="G59" s="5" t="n"/>
+      <c r="H59" s="6" t="n"/>
+    </row>
+    <row r="60" hidden="1" outlineLevel="2">
+      <c r="A60" s="4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="B60" s="5" t="n"/>
+      <c r="C60" s="6" t="n"/>
+      <c r="D60" s="6" t="n"/>
+      <c r="E60" s="6" t="n"/>
+      <c r="F60" s="5" t="n"/>
+      <c r="G60" s="5" t="n"/>
+      <c r="H60" s="6" t="n"/>
+    </row>
+    <row r="61" hidden="1" outlineLevel="2">
+      <c r="A61" s="4" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="B61" s="5" t="n"/>
+      <c r="C61" s="6" t="n"/>
+      <c r="D61" s="6" t="n"/>
+      <c r="E61" s="6" t="n"/>
+      <c r="F61" s="5" t="n"/>
+      <c r="G61" s="5" t="n"/>
+      <c r="H61" s="6" t="n"/>
+    </row>
+    <row r="62" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A62" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B62" s="5" t="n"/>
+      <c r="C62" s="6" t="n"/>
+      <c r="D62" s="6" t="n"/>
+      <c r="E62" s="6" t="n"/>
+      <c r="F62" s="5" t="n"/>
+      <c r="G62" s="5" t="n"/>
+      <c r="H62" s="6" t="n"/>
+    </row>
+    <row r="63" hidden="1" outlineLevel="2">
+      <c r="A63" s="4" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="B63" s="5" t="n"/>
+      <c r="C63" s="6" t="n"/>
+      <c r="D63" s="6" t="n"/>
+      <c r="E63" s="6" t="n"/>
+      <c r="F63" s="5" t="n"/>
+      <c r="G63" s="5" t="n"/>
+      <c r="H63" s="6" t="n"/>
+    </row>
+    <row r="64" hidden="1" outlineLevel="2">
+      <c r="A64" s="4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="B64" s="5" t="n"/>
+      <c r="C64" s="6" t="n"/>
+      <c r="D64" s="6" t="n"/>
+      <c r="E64" s="6" t="n"/>
+      <c r="F64" s="5" t="n"/>
+      <c r="G64" s="5" t="n"/>
+      <c r="H64" s="6" t="n"/>
+    </row>
+    <row r="65" hidden="1" outlineLevel="2">
+      <c r="A65" s="4" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="B65" s="5" t="n"/>
+      <c r="C65" s="6" t="n"/>
+      <c r="D65" s="6" t="n"/>
+      <c r="E65" s="6" t="n"/>
+      <c r="F65" s="5" t="n"/>
+      <c r="G65" s="5" t="n"/>
+      <c r="H65" s="6" t="n"/>
+    </row>
+    <row r="66" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A66" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B66" s="5" t="n"/>
+      <c r="C66" s="6" t="n"/>
+      <c r="D66" s="6" t="n"/>
+      <c r="E66" s="6" t="n"/>
+      <c r="F66" s="5" t="n"/>
+      <c r="G66" s="5" t="n"/>
+      <c r="H66" s="6" t="n"/>
+    </row>
+    <row r="67" hidden="1" outlineLevel="2">
+      <c r="A67" s="4" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="B67" s="5" t="n"/>
+      <c r="C67" s="6" t="n"/>
+      <c r="D67" s="6" t="n"/>
+      <c r="E67" s="6" t="n"/>
+      <c r="F67" s="5" t="n"/>
+      <c r="G67" s="5" t="n"/>
+      <c r="H67" s="6" t="n"/>
+    </row>
+    <row r="68" hidden="1" outlineLevel="2">
+      <c r="A68" s="4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="B68" s="5" t="n"/>
+      <c r="C68" s="6" t="n"/>
+      <c r="D68" s="6" t="n"/>
+      <c r="E68" s="6" t="n"/>
+      <c r="F68" s="5" t="n"/>
+      <c r="G68" s="5" t="n"/>
+      <c r="H68" s="6" t="n"/>
+    </row>
+    <row r="69" hidden="1" outlineLevel="2">
+      <c r="A69" s="4" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="B69" s="5" t="n"/>
+      <c r="C69" s="6" t="n"/>
+      <c r="D69" s="6" t="n"/>
+      <c r="E69" s="6" t="n"/>
+      <c r="F69" s="5" t="n"/>
+      <c r="G69" s="5" t="n"/>
+      <c r="H69" s="6" t="n"/>
+    </row>
+    <row r="70" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A70" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B70" s="5" t="n"/>
+      <c r="C70" s="6" t="n"/>
+      <c r="D70" s="6" t="n"/>
+      <c r="E70" s="6" t="n"/>
+      <c r="F70" s="5" t="n"/>
+      <c r="G70" s="5" t="n"/>
+      <c r="H70" s="6" t="n"/>
+    </row>
+    <row r="71" hidden="1" outlineLevel="2">
+      <c r="A71" s="4" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="B71" s="5" t="n"/>
+      <c r="C71" s="6" t="n"/>
+      <c r="D71" s="6" t="n"/>
+      <c r="E71" s="6" t="n"/>
+      <c r="F71" s="5" t="n"/>
+      <c r="G71" s="5" t="n"/>
+      <c r="H71" s="6" t="n"/>
+    </row>
+    <row r="72" hidden="1" outlineLevel="2">
+      <c r="A72" s="4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="B72" s="5" t="n"/>
+      <c r="C72" s="6" t="n"/>
+      <c r="D72" s="6" t="n"/>
+      <c r="E72" s="6" t="n"/>
+      <c r="F72" s="5" t="n"/>
+      <c r="G72" s="5" t="n"/>
+      <c r="H72" s="6" t="n"/>
+    </row>
+    <row r="73" hidden="1" outlineLevel="2">
+      <c r="A73" s="4" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="B73" s="5" t="n"/>
+      <c r="C73" s="6" t="n"/>
+      <c r="D73" s="6" t="n"/>
+      <c r="E73" s="6" t="n"/>
+      <c r="F73" s="5" t="n"/>
+      <c r="G73" s="5" t="n"/>
+      <c r="H73" s="6" t="n"/>
+    </row>
+    <row r="74" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A74" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B74" s="5" t="n"/>
+      <c r="C74" s="6" t="n"/>
+      <c r="D74" s="6" t="n"/>
+      <c r="E74" s="6" t="n"/>
+      <c r="F74" s="5" t="n"/>
+      <c r="G74" s="5" t="n"/>
+      <c r="H74" s="6" t="n"/>
+    </row>
+    <row r="75" hidden="1" outlineLevel="2">
+      <c r="A75" s="4" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="B75" s="5" t="n"/>
+      <c r="C75" s="6" t="n"/>
+      <c r="D75" s="6" t="n"/>
+      <c r="E75" s="6" t="n"/>
+      <c r="F75" s="5" t="n"/>
+      <c r="G75" s="5" t="n"/>
+      <c r="H75" s="6" t="n"/>
+    </row>
+    <row r="76" hidden="1" outlineLevel="2">
+      <c r="A76" s="4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="B76" s="5" t="n"/>
+      <c r="C76" s="6" t="n"/>
+      <c r="D76" s="6" t="n"/>
+      <c r="E76" s="6" t="n"/>
+      <c r="F76" s="5" t="n"/>
+      <c r="G76" s="5" t="n"/>
+      <c r="H76" s="6" t="n"/>
+    </row>
+    <row r="77" hidden="1" outlineLevel="2">
+      <c r="A77" s="4" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="B77" s="5" t="n"/>
+      <c r="C77" s="6" t="n"/>
+      <c r="D77" s="6" t="n"/>
+      <c r="E77" s="6" t="n"/>
+      <c r="F77" s="5" t="n"/>
+      <c r="G77" s="5" t="n"/>
+      <c r="H77" s="6" t="n"/>
+    </row>
+    <row r="78" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A78" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B78" s="5" t="n"/>
+      <c r="C78" s="6" t="n"/>
+      <c r="D78" s="6" t="n"/>
+      <c r="E78" s="6" t="n"/>
+      <c r="F78" s="5" t="n"/>
+      <c r="G78" s="5" t="n"/>
+      <c r="H78" s="6" t="n"/>
+    </row>
+    <row r="79" hidden="1" outlineLevel="2">
+      <c r="A79" s="4" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="B79" s="5" t="n"/>
+      <c r="C79" s="6" t="n"/>
+      <c r="D79" s="6" t="n"/>
+      <c r="E79" s="6" t="n"/>
+      <c r="F79" s="5" t="n"/>
+      <c r="G79" s="5" t="n"/>
+      <c r="H79" s="6" t="n"/>
+    </row>
+    <row r="80" hidden="1" outlineLevel="2">
+      <c r="A80" s="4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="B80" s="5" t="n"/>
+      <c r="C80" s="6" t="n"/>
+      <c r="D80" s="6" t="n"/>
+      <c r="E80" s="6" t="n"/>
+      <c r="F80" s="5" t="n"/>
+      <c r="G80" s="5" t="n"/>
+      <c r="H80" s="6" t="n"/>
+    </row>
+    <row r="81" hidden="1" outlineLevel="2">
+      <c r="A81" s="4" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="B81" s="5" t="n"/>
+      <c r="C81" s="6" t="n"/>
+      <c r="D81" s="6" t="n"/>
+      <c r="E81" s="6" t="n"/>
+      <c r="F81" s="5" t="n"/>
+      <c r="G81" s="5" t="n"/>
+      <c r="H81" s="6" t="n"/>
+    </row>
+    <row r="82" collapsed="1">
+      <c r="A82" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B82" s="5" t="inlineStr">
         <is>
           <t>v1: im criticised</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>alter Code (handgeschrieben, läuft so in der Firmware):
-progPalette(15240, 3, 20)</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_RAIN, Farben SCHEME_ROYAL
+Ausgabe: Übergang fade 952 ms
+Kleine Steigerung: fallende Leuchtspuren in Blau und Lila, weich eingeblendet.</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="n"/>
+      <c r="E82" s="6" t="inlineStr">
         <is>
           <t>Szene Rain, ROYAL: Leuchtspuren, kleine Steigerung; weich eingeblendet (fade, 2 Beats).</t>
         </is>
       </c>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5">
+      <c r="F82" s="5" t="n"/>
+      <c r="G82" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H82" s="6" t="inlineStr">
         <is>
           <t>progPalette(15240, 3, 20)</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="n">
+    <row r="83" hidden="1" outlineLevel="2">
+      <c r="A83" s="4" t="n">
+        <v>20.25</v>
+      </c>
+      <c r="B83" s="5" t="n"/>
+      <c r="C83" s="6" t="n"/>
+      <c r="D83" s="6" t="n"/>
+      <c r="E83" s="6" t="n"/>
+      <c r="F83" s="5" t="n"/>
+      <c r="G83" s="5" t="n"/>
+      <c r="H83" s="6" t="n"/>
+    </row>
+    <row r="84" hidden="1" outlineLevel="2">
+      <c r="A84" s="4" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="B84" s="5" t="n"/>
+      <c r="C84" s="6" t="n"/>
+      <c r="D84" s="6" t="n"/>
+      <c r="E84" s="6" t="n"/>
+      <c r="F84" s="5" t="n"/>
+      <c r="G84" s="5" t="n"/>
+      <c r="H84" s="6" t="n"/>
+    </row>
+    <row r="85" hidden="1" outlineLevel="2">
+      <c r="A85" s="4" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="B85" s="5" t="n"/>
+      <c r="C85" s="6" t="n"/>
+      <c r="D85" s="6" t="n"/>
+      <c r="E85" s="6" t="n"/>
+      <c r="F85" s="5" t="n"/>
+      <c r="G85" s="5" t="n"/>
+      <c r="H85" s="6" t="n"/>
+    </row>
+    <row r="86" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A86" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B86" s="5" t="n"/>
+      <c r="C86" s="6" t="n"/>
+      <c r="D86" s="6" t="n"/>
+      <c r="E86" s="6" t="n"/>
+      <c r="F86" s="5" t="n"/>
+      <c r="G86" s="5" t="n"/>
+      <c r="H86" s="6" t="n"/>
+    </row>
+    <row r="87" hidden="1" outlineLevel="2">
+      <c r="A87" s="4" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="B87" s="5" t="n"/>
+      <c r="C87" s="6" t="n"/>
+      <c r="D87" s="6" t="n"/>
+      <c r="E87" s="6" t="n"/>
+      <c r="F87" s="5" t="n"/>
+      <c r="G87" s="5" t="n"/>
+      <c r="H87" s="6" t="n"/>
+    </row>
+    <row r="88" hidden="1" outlineLevel="2">
+      <c r="A88" s="4" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="B88" s="5" t="n"/>
+      <c r="C88" s="6" t="n"/>
+      <c r="D88" s="6" t="n"/>
+      <c r="E88" s="6" t="n"/>
+      <c r="F88" s="5" t="n"/>
+      <c r="G88" s="5" t="n"/>
+      <c r="H88" s="6" t="n"/>
+    </row>
+    <row r="89" hidden="1" outlineLevel="2">
+      <c r="A89" s="4" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="B89" s="5" t="n"/>
+      <c r="C89" s="6" t="n"/>
+      <c r="D89" s="6" t="n"/>
+      <c r="E89" s="6" t="n"/>
+      <c r="F89" s="5" t="n"/>
+      <c r="G89" s="5" t="n"/>
+      <c r="H89" s="6" t="n"/>
+    </row>
+    <row r="90" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A90" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B90" s="5" t="n"/>
+      <c r="C90" s="6" t="n"/>
+      <c r="D90" s="6" t="n"/>
+      <c r="E90" s="6" t="n"/>
+      <c r="F90" s="5" t="n"/>
+      <c r="G90" s="5" t="n"/>
+      <c r="H90" s="6" t="n"/>
+    </row>
+    <row r="91" hidden="1" outlineLevel="2">
+      <c r="A91" s="4" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="B91" s="5" t="n"/>
+      <c r="C91" s="6" t="n"/>
+      <c r="D91" s="6" t="n"/>
+      <c r="E91" s="6" t="n"/>
+      <c r="F91" s="5" t="n"/>
+      <c r="G91" s="5" t="n"/>
+      <c r="H91" s="6" t="n"/>
+    </row>
+    <row r="92" hidden="1" outlineLevel="2">
+      <c r="A92" s="4" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="B92" s="5" t="n"/>
+      <c r="C92" s="6" t="n"/>
+      <c r="D92" s="6" t="n"/>
+      <c r="E92" s="6" t="n"/>
+      <c r="F92" s="5" t="n"/>
+      <c r="G92" s="5" t="n"/>
+      <c r="H92" s="6" t="n"/>
+    </row>
+    <row r="93" hidden="1" outlineLevel="2">
+      <c r="A93" s="4" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="B93" s="5" t="n"/>
+      <c r="C93" s="6" t="n"/>
+      <c r="D93" s="6" t="n"/>
+      <c r="E93" s="6" t="n"/>
+      <c r="F93" s="5" t="n"/>
+      <c r="G93" s="5" t="n"/>
+      <c r="H93" s="6" t="n"/>
+    </row>
+    <row r="94" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A94" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B94" s="5" t="n"/>
+      <c r="C94" s="6" t="n"/>
+      <c r="D94" s="6" t="n"/>
+      <c r="E94" s="6" t="n"/>
+      <c r="F94" s="5" t="n"/>
+      <c r="G94" s="5" t="n"/>
+      <c r="H94" s="6" t="n"/>
+    </row>
+    <row r="95" hidden="1" outlineLevel="2">
+      <c r="A95" s="4" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="B95" s="5" t="n"/>
+      <c r="C95" s="6" t="n"/>
+      <c r="D95" s="6" t="n"/>
+      <c r="E95" s="6" t="n"/>
+      <c r="F95" s="5" t="n"/>
+      <c r="G95" s="5" t="n"/>
+      <c r="H95" s="6" t="n"/>
+    </row>
+    <row r="96" hidden="1" outlineLevel="2">
+      <c r="A96" s="4" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="B96" s="5" t="n"/>
+      <c r="C96" s="6" t="n"/>
+      <c r="D96" s="6" t="n"/>
+      <c r="E96" s="6" t="n"/>
+      <c r="F96" s="5" t="n"/>
+      <c r="G96" s="5" t="n"/>
+      <c r="H96" s="6" t="n"/>
+    </row>
+    <row r="97" hidden="1" outlineLevel="2">
+      <c r="A97" s="4" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="B97" s="5" t="n"/>
+      <c r="C97" s="6" t="n"/>
+      <c r="D97" s="6" t="n"/>
+      <c r="E97" s="6" t="n"/>
+      <c r="F97" s="5" t="n"/>
+      <c r="G97" s="5" t="n"/>
+      <c r="H97" s="6" t="n"/>
+    </row>
+    <row r="98" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A98" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B98" s="5" t="n"/>
+      <c r="C98" s="6" t="n"/>
+      <c r="D98" s="6" t="n"/>
+      <c r="E98" s="6" t="n"/>
+      <c r="F98" s="5" t="n"/>
+      <c r="G98" s="5" t="n"/>
+      <c r="H98" s="6" t="n"/>
+    </row>
+    <row r="99" hidden="1" outlineLevel="2">
+      <c r="A99" s="4" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="B99" s="5" t="n"/>
+      <c r="C99" s="6" t="n"/>
+      <c r="D99" s="6" t="n"/>
+      <c r="E99" s="6" t="n"/>
+      <c r="F99" s="5" t="n"/>
+      <c r="G99" s="5" t="n"/>
+      <c r="H99" s="6" t="n"/>
+    </row>
+    <row r="100" hidden="1" outlineLevel="2">
+      <c r="A100" s="4" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="B100" s="5" t="n"/>
+      <c r="C100" s="6" t="n"/>
+      <c r="D100" s="6" t="n"/>
+      <c r="E100" s="6" t="n"/>
+      <c r="F100" s="5" t="n"/>
+      <c r="G100" s="5" t="n"/>
+      <c r="H100" s="6" t="n"/>
+    </row>
+    <row r="101" hidden="1" outlineLevel="2">
+      <c r="A101" s="4" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="B101" s="5" t="n"/>
+      <c r="C101" s="6" t="n"/>
+      <c r="D101" s="6" t="n"/>
+      <c r="E101" s="6" t="n"/>
+      <c r="F101" s="5" t="n"/>
+      <c r="G101" s="5" t="n"/>
+      <c r="H101" s="6" t="n"/>
+    </row>
+    <row r="102" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A102" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B102" s="5" t="n"/>
+      <c r="C102" s="6" t="n"/>
+      <c r="D102" s="6" t="n"/>
+      <c r="E102" s="6" t="n"/>
+      <c r="F102" s="5" t="n"/>
+      <c r="G102" s="5" t="n"/>
+      <c r="H102" s="6" t="n"/>
+    </row>
+    <row r="103" hidden="1" outlineLevel="2">
+      <c r="A103" s="4" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="B103" s="5" t="n"/>
+      <c r="C103" s="6" t="n"/>
+      <c r="D103" s="6" t="n"/>
+      <c r="E103" s="6" t="n"/>
+      <c r="F103" s="5" t="n"/>
+      <c r="G103" s="5" t="n"/>
+      <c r="H103" s="6" t="n"/>
+    </row>
+    <row r="104" hidden="1" outlineLevel="2">
+      <c r="A104" s="4" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="B104" s="5" t="n"/>
+      <c r="C104" s="6" t="n"/>
+      <c r="D104" s="6" t="n"/>
+      <c r="E104" s="6" t="n"/>
+      <c r="F104" s="5" t="n"/>
+      <c r="G104" s="5" t="n"/>
+      <c r="H104" s="6" t="n"/>
+    </row>
+    <row r="105" hidden="1" outlineLevel="2">
+      <c r="A105" s="4" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="B105" s="5" t="n"/>
+      <c r="C105" s="6" t="n"/>
+      <c r="D105" s="6" t="n"/>
+      <c r="E105" s="6" t="n"/>
+      <c r="F105" s="5" t="n"/>
+      <c r="G105" s="5" t="n"/>
+      <c r="H105" s="6" t="n"/>
+    </row>
+    <row r="106" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A106" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B106" s="5" t="n"/>
+      <c r="C106" s="6" t="n"/>
+      <c r="D106" s="6" t="n"/>
+      <c r="E106" s="6" t="n"/>
+      <c r="F106" s="5" t="n"/>
+      <c r="G106" s="5" t="n"/>
+      <c r="H106" s="6" t="n"/>
+    </row>
+    <row r="107" hidden="1" outlineLevel="2">
+      <c r="A107" s="4" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="B107" s="5" t="n"/>
+      <c r="C107" s="6" t="n"/>
+      <c r="D107" s="6" t="n"/>
+      <c r="E107" s="6" t="n"/>
+      <c r="F107" s="5" t="n"/>
+      <c r="G107" s="5" t="n"/>
+      <c r="H107" s="6" t="n"/>
+    </row>
+    <row r="108" hidden="1" outlineLevel="2">
+      <c r="A108" s="4" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="B108" s="5" t="n"/>
+      <c r="C108" s="6" t="n"/>
+      <c r="D108" s="6" t="n"/>
+      <c r="E108" s="6" t="n"/>
+      <c r="F108" s="5" t="n"/>
+      <c r="G108" s="5" t="n"/>
+      <c r="H108" s="6" t="n"/>
+    </row>
+    <row r="109" hidden="1" outlineLevel="2">
+      <c r="A109" s="4" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="B109" s="5" t="n"/>
+      <c r="C109" s="6" t="n"/>
+      <c r="D109" s="6" t="n"/>
+      <c r="E109" s="6" t="n"/>
+      <c r="F109" s="5" t="n"/>
+      <c r="G109" s="5" t="n"/>
+      <c r="H109" s="6" t="n"/>
+    </row>
+    <row r="110" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A110" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B110" s="5" t="n"/>
+      <c r="C110" s="6" t="n"/>
+      <c r="D110" s="6" t="n"/>
+      <c r="E110" s="6" t="n"/>
+      <c r="F110" s="5" t="n"/>
+      <c r="G110" s="5" t="n"/>
+      <c r="H110" s="6" t="n"/>
+    </row>
+    <row r="111" hidden="1" outlineLevel="2">
+      <c r="A111" s="4" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="B111" s="5" t="n"/>
+      <c r="C111" s="6" t="n"/>
+      <c r="D111" s="6" t="n"/>
+      <c r="E111" s="6" t="n"/>
+      <c r="F111" s="5" t="n"/>
+      <c r="G111" s="5" t="n"/>
+      <c r="H111" s="6" t="n"/>
+    </row>
+    <row r="112" hidden="1" outlineLevel="2">
+      <c r="A112" s="4" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="B112" s="5" t="n"/>
+      <c r="C112" s="6" t="n"/>
+      <c r="D112" s="6" t="n"/>
+      <c r="E112" s="6" t="n"/>
+      <c r="F112" s="5" t="n"/>
+      <c r="G112" s="5" t="n"/>
+      <c r="H112" s="6" t="n"/>
+    </row>
+    <row r="113" hidden="1" outlineLevel="2">
+      <c r="A113" s="4" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="B113" s="5" t="n"/>
+      <c r="C113" s="6" t="n"/>
+      <c r="D113" s="6" t="n"/>
+      <c r="E113" s="6" t="n"/>
+      <c r="F113" s="5" t="n"/>
+      <c r="G113" s="5" t="n"/>
+      <c r="H113" s="6" t="n"/>
+    </row>
+    <row r="114" collapsed="1">
+      <c r="A114" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B114" s="5" t="inlineStr">
         <is>
           <t>im bulletproof</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>alter Code (handgeschrieben, läuft so in der Firmware):
-progMatrixScanner(15235, 25, 20)</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_VERSE, Farben SCHEME_ICE
+Ebene SCENE_SPARKLE (add, 40 %, baut sich 13333 ms auf)
+Schluss (4 Beats): SCENE_BUILDUP, Farben SCHEME_WHITE
+Aufbau zum Chorus: dezenter Puls im Beat in Eisblau, auf der Matrix Sinuswellen, darüber baut sich ein Glitzern auf; im letzten Takt lädt sich alles weiß auf, Explosion auf 'I am titanium'.</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="n"/>
+      <c r="E114" s="6" t="inlineStr">
         <is>
           <t>Szene Verse, ICE, darüber baut sich ein Glitzern auf (Ebene Sparkle, fade_in über 8 Takte); letzter Takt Szene Buildup (tail 4 Beats), Explosion auf "I am titanium". Fester Look für beide.</t>
         </is>
       </c>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5">
+      <c r="F114" s="5" t="n"/>
+      <c r="G114" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H114" s="6" t="inlineStr">
         <is>
           <t>progMatrixScanner(15235, 25, 20)</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="n">
+    <row r="115" hidden="1" outlineLevel="2">
+      <c r="A115" s="4" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="B115" s="5" t="n"/>
+      <c r="C115" s="6" t="n"/>
+      <c r="D115" s="6" t="n"/>
+      <c r="E115" s="6" t="n"/>
+      <c r="F115" s="5" t="n"/>
+      <c r="G115" s="5" t="n"/>
+      <c r="H115" s="6" t="n"/>
+    </row>
+    <row r="116" hidden="1" outlineLevel="2">
+      <c r="A116" s="4" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="B116" s="5" t="n"/>
+      <c r="C116" s="6" t="n"/>
+      <c r="D116" s="6" t="n"/>
+      <c r="E116" s="6" t="n"/>
+      <c r="F116" s="5" t="n"/>
+      <c r="G116" s="5" t="n"/>
+      <c r="H116" s="6" t="n"/>
+    </row>
+    <row r="117" hidden="1" outlineLevel="2">
+      <c r="A117" s="4" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="B117" s="5" t="n"/>
+      <c r="C117" s="6" t="n"/>
+      <c r="D117" s="6" t="n"/>
+      <c r="E117" s="6" t="n"/>
+      <c r="F117" s="5" t="n"/>
+      <c r="G117" s="5" t="n"/>
+      <c r="H117" s="6" t="n"/>
+    </row>
+    <row r="118" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A118" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B118" s="5" t="n"/>
+      <c r="C118" s="6" t="n"/>
+      <c r="D118" s="6" t="n"/>
+      <c r="E118" s="6" t="n"/>
+      <c r="F118" s="5" t="n"/>
+      <c r="G118" s="5" t="n"/>
+      <c r="H118" s="6" t="n"/>
+    </row>
+    <row r="119" hidden="1" outlineLevel="2">
+      <c r="A119" s="4" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="B119" s="5" t="n"/>
+      <c r="C119" s="6" t="n"/>
+      <c r="D119" s="6" t="n"/>
+      <c r="E119" s="6" t="n"/>
+      <c r="F119" s="5" t="n"/>
+      <c r="G119" s="5" t="n"/>
+      <c r="H119" s="6" t="n"/>
+    </row>
+    <row r="120" hidden="1" outlineLevel="2">
+      <c r="A120" s="4" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="B120" s="5" t="n"/>
+      <c r="C120" s="6" t="n"/>
+      <c r="D120" s="6" t="n"/>
+      <c r="E120" s="6" t="n"/>
+      <c r="F120" s="5" t="n"/>
+      <c r="G120" s="5" t="n"/>
+      <c r="H120" s="6" t="n"/>
+    </row>
+    <row r="121" hidden="1" outlineLevel="2">
+      <c r="A121" s="4" t="n">
+        <v>29.75</v>
+      </c>
+      <c r="B121" s="5" t="n"/>
+      <c r="C121" s="6" t="n"/>
+      <c r="D121" s="6" t="n"/>
+      <c r="E121" s="6" t="n"/>
+      <c r="F121" s="5" t="n"/>
+      <c r="G121" s="5" t="n"/>
+      <c r="H121" s="6" t="n"/>
+    </row>
+    <row r="122" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A122" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B122" s="5" t="n"/>
+      <c r="C122" s="6" t="n"/>
+      <c r="D122" s="6" t="n"/>
+      <c r="E122" s="6" t="n"/>
+      <c r="F122" s="5" t="n"/>
+      <c r="G122" s="5" t="n"/>
+      <c r="H122" s="6" t="n"/>
+    </row>
+    <row r="123" hidden="1" outlineLevel="2">
+      <c r="A123" s="4" t="n">
+        <v>30.25</v>
+      </c>
+      <c r="B123" s="5" t="n"/>
+      <c r="C123" s="6" t="n"/>
+      <c r="D123" s="6" t="n"/>
+      <c r="E123" s="6" t="n"/>
+      <c r="F123" s="5" t="n"/>
+      <c r="G123" s="5" t="n"/>
+      <c r="H123" s="6" t="n"/>
+    </row>
+    <row r="124" hidden="1" outlineLevel="2">
+      <c r="A124" s="4" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="B124" s="5" t="n"/>
+      <c r="C124" s="6" t="n"/>
+      <c r="D124" s="6" t="n"/>
+      <c r="E124" s="6" t="n"/>
+      <c r="F124" s="5" t="n"/>
+      <c r="G124" s="5" t="n"/>
+      <c r="H124" s="6" t="n"/>
+    </row>
+    <row r="125" hidden="1" outlineLevel="2">
+      <c r="A125" s="4" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="B125" s="5" t="n"/>
+      <c r="C125" s="6" t="n"/>
+      <c r="D125" s="6" t="n"/>
+      <c r="E125" s="6" t="n"/>
+      <c r="F125" s="5" t="n"/>
+      <c r="G125" s="5" t="n"/>
+      <c r="H125" s="6" t="n"/>
+    </row>
+    <row r="126" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A126" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="B126" s="5" t="n"/>
+      <c r="C126" s="6" t="n"/>
+      <c r="D126" s="6" t="n"/>
+      <c r="E126" s="6" t="n"/>
+      <c r="F126" s="5" t="n"/>
+      <c r="G126" s="5" t="n"/>
+      <c r="H126" s="6" t="n"/>
+    </row>
+    <row r="127" hidden="1" outlineLevel="2">
+      <c r="A127" s="4" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="B127" s="5" t="n"/>
+      <c r="C127" s="6" t="n"/>
+      <c r="D127" s="6" t="n"/>
+      <c r="E127" s="6" t="n"/>
+      <c r="F127" s="5" t="n"/>
+      <c r="G127" s="5" t="n"/>
+      <c r="H127" s="6" t="n"/>
+    </row>
+    <row r="128" hidden="1" outlineLevel="2">
+      <c r="A128" s="4" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="B128" s="5" t="n"/>
+      <c r="C128" s="6" t="n"/>
+      <c r="D128" s="6" t="n"/>
+      <c r="E128" s="6" t="n"/>
+      <c r="F128" s="5" t="n"/>
+      <c r="G128" s="5" t="n"/>
+      <c r="H128" s="6" t="n"/>
+    </row>
+    <row r="129" hidden="1" outlineLevel="2">
+      <c r="A129" s="4" t="n">
+        <v>31.75</v>
+      </c>
+      <c r="B129" s="5" t="n"/>
+      <c r="C129" s="6" t="n"/>
+      <c r="D129" s="6" t="n"/>
+      <c r="E129" s="6" t="n"/>
+      <c r="F129" s="5" t="n"/>
+      <c r="G129" s="5" t="n"/>
+      <c r="H129" s="6" t="n"/>
+    </row>
+    <row r="130" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A130" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B130" s="5" t="n"/>
+      <c r="C130" s="6" t="n"/>
+      <c r="D130" s="6" t="n"/>
+      <c r="E130" s="6" t="n"/>
+      <c r="F130" s="5" t="n"/>
+      <c r="G130" s="5" t="n"/>
+      <c r="H130" s="6" t="n"/>
+    </row>
+    <row r="131" hidden="1" outlineLevel="2">
+      <c r="A131" s="4" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="B131" s="5" t="n"/>
+      <c r="C131" s="6" t="n"/>
+      <c r="D131" s="6" t="n"/>
+      <c r="E131" s="6" t="n"/>
+      <c r="F131" s="5" t="n"/>
+      <c r="G131" s="5" t="n"/>
+      <c r="H131" s="6" t="n"/>
+    </row>
+    <row r="132" hidden="1" outlineLevel="2">
+      <c r="A132" s="4" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="B132" s="5" t="n"/>
+      <c r="C132" s="6" t="n"/>
+      <c r="D132" s="6" t="n"/>
+      <c r="E132" s="6" t="n"/>
+      <c r="F132" s="5" t="n"/>
+      <c r="G132" s="5" t="n"/>
+      <c r="H132" s="6" t="n"/>
+    </row>
+    <row r="133" hidden="1" outlineLevel="2">
+      <c r="A133" s="4" t="n">
+        <v>32.75</v>
+      </c>
+      <c r="B133" s="5" t="n"/>
+      <c r="C133" s="6" t="n"/>
+      <c r="D133" s="6" t="n"/>
+      <c r="E133" s="6" t="n"/>
+      <c r="F133" s="5" t="n"/>
+      <c r="G133" s="5" t="n"/>
+      <c r="H133" s="6" t="n"/>
+    </row>
+    <row r="134" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A134" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="B134" s="5" t="n"/>
+      <c r="C134" s="6" t="n"/>
+      <c r="D134" s="6" t="n"/>
+      <c r="E134" s="6" t="n"/>
+      <c r="F134" s="5" t="n"/>
+      <c r="G134" s="5" t="n"/>
+      <c r="H134" s="6" t="n"/>
+    </row>
+    <row r="135" hidden="1" outlineLevel="2">
+      <c r="A135" s="4" t="n">
+        <v>33.25</v>
+      </c>
+      <c r="B135" s="5" t="n"/>
+      <c r="C135" s="6" t="n"/>
+      <c r="D135" s="6" t="n"/>
+      <c r="E135" s="6" t="n"/>
+      <c r="F135" s="5" t="n"/>
+      <c r="G135" s="5" t="n"/>
+      <c r="H135" s="6" t="n"/>
+    </row>
+    <row r="136" hidden="1" outlineLevel="2">
+      <c r="A136" s="4" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="B136" s="5" t="n"/>
+      <c r="C136" s="6" t="n"/>
+      <c r="D136" s="6" t="n"/>
+      <c r="E136" s="6" t="n"/>
+      <c r="F136" s="5" t="n"/>
+      <c r="G136" s="5" t="n"/>
+      <c r="H136" s="6" t="n"/>
+    </row>
+    <row r="137" hidden="1" outlineLevel="2">
+      <c r="A137" s="4" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="B137" s="5" t="n"/>
+      <c r="C137" s="6" t="n"/>
+      <c r="D137" s="6" t="n"/>
+      <c r="E137" s="6" t="n"/>
+      <c r="F137" s="5" t="n"/>
+      <c r="G137" s="5" t="n"/>
+      <c r="H137" s="6" t="n"/>
+    </row>
+    <row r="138" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A138" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B138" s="5" t="n"/>
+      <c r="C138" s="6" t="n"/>
+      <c r="D138" s="6" t="n"/>
+      <c r="E138" s="6" t="n"/>
+      <c r="F138" s="5" t="n"/>
+      <c r="G138" s="5" t="n"/>
+      <c r="H138" s="6" t="n"/>
+    </row>
+    <row r="139" hidden="1" outlineLevel="2">
+      <c r="A139" s="4" t="n">
+        <v>34.25</v>
+      </c>
+      <c r="B139" s="5" t="n"/>
+      <c r="C139" s="6" t="n"/>
+      <c r="D139" s="6" t="n"/>
+      <c r="E139" s="6" t="n"/>
+      <c r="F139" s="5" t="n"/>
+      <c r="G139" s="5" t="n"/>
+      <c r="H139" s="6" t="n"/>
+    </row>
+    <row r="140" hidden="1" outlineLevel="2">
+      <c r="A140" s="4" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="B140" s="5" t="n"/>
+      <c r="C140" s="6" t="n"/>
+      <c r="D140" s="6" t="n"/>
+      <c r="E140" s="6" t="n"/>
+      <c r="F140" s="5" t="n"/>
+      <c r="G140" s="5" t="n"/>
+      <c r="H140" s="6" t="n"/>
+    </row>
+    <row r="141" hidden="1" outlineLevel="2">
+      <c r="A141" s="4" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="B141" s="5" t="n"/>
+      <c r="C141" s="6" t="n"/>
+      <c r="D141" s="6" t="n"/>
+      <c r="E141" s="6" t="n"/>
+      <c r="F141" s="5" t="n"/>
+      <c r="G141" s="5" t="n"/>
+      <c r="H141" s="6" t="n"/>
+    </row>
+    <row r="142" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A142" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B142" s="5" t="n"/>
+      <c r="C142" s="6" t="n"/>
+      <c r="D142" s="6" t="n"/>
+      <c r="E142" s="6" t="n"/>
+      <c r="F142" s="5" t="n"/>
+      <c r="G142" s="5" t="n"/>
+      <c r="H142" s="6" t="n"/>
+    </row>
+    <row r="143" hidden="1" outlineLevel="2">
+      <c r="A143" s="4" t="n">
+        <v>35.25</v>
+      </c>
+      <c r="B143" s="5" t="n"/>
+      <c r="C143" s="6" t="n"/>
+      <c r="D143" s="6" t="n"/>
+      <c r="E143" s="6" t="n"/>
+      <c r="F143" s="5" t="n"/>
+      <c r="G143" s="5" t="n"/>
+      <c r="H143" s="6" t="n"/>
+    </row>
+    <row r="144" hidden="1" outlineLevel="2">
+      <c r="A144" s="4" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="B144" s="5" t="n"/>
+      <c r="C144" s="6" t="n"/>
+      <c r="D144" s="6" t="n"/>
+      <c r="E144" s="6" t="n"/>
+      <c r="F144" s="5" t="n"/>
+      <c r="G144" s="5" t="n"/>
+      <c r="H144" s="6" t="n"/>
+    </row>
+    <row r="145" hidden="1" outlineLevel="2">
+      <c r="A145" s="4" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="B145" s="5" t="n"/>
+      <c r="C145" s="6" t="n"/>
+      <c r="D145" s="6" t="n"/>
+      <c r="E145" s="6" t="n"/>
+      <c r="F145" s="5" t="n"/>
+      <c r="G145" s="5" t="n"/>
+      <c r="H145" s="6" t="n"/>
+    </row>
+    <row r="146" collapsed="1">
+      <c r="A146" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B146" s="5" t="inlineStr">
         <is>
           <t>chorus 1</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>alter Code (handgeschrieben, läuft so in der Firmware):
-progFullColors(15240, 30, 475)</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="C146" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_COLORS, Farben SCHEME_WHITE, Farbwanderung to SCHEME_ICE, per 8
+Text (Matrix): "TITANIUM": steht durchgehend, ohne Pulsieren (über der Szene)
+   ab 0 ms bis 3810 ms, klingt 952 ms ab, darunter 15 %
+Ausgabe: Farbwechsel weich (30 % des Schritts), Blinder bei 0 ms, 952 ms lang, Blinder liegt unter dem Text
+Die ganze Bühne in einer Farbe pro Beat, von Weiß alle 2 Takte nach Eisblau und zurück, mit kurzer Blende; warmweißer Blinder auf den Einsatz, auf der Matrix TITANIUM, blendet nach 2 Takten aus.</t>
+        </is>
+      </c>
+      <c r="D146" s="6" t="n"/>
+      <c r="E146" s="6" t="inlineStr">
         <is>
           <t>Szene Colors, WHITE -&gt; Farbwanderung nach ICE, soft 30; Blinder auf den Einsatz (2 Beats). Auf der Matrix "TITANIUM" über der Szene, blendet nach 2 Takten aus.</t>
         </is>
       </c>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5">
+      <c r="F146" s="5" t="n"/>
+      <c r="G146" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H146" s="6" t="inlineStr">
         <is>
           <t>progFullColors(15240, 30, 475)</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="n">
+    <row r="147" hidden="1" outlineLevel="2">
+      <c r="A147" s="4" t="n">
+        <v>36.25</v>
+      </c>
+      <c r="B147" s="5" t="n"/>
+      <c r="C147" s="6" t="n"/>
+      <c r="D147" s="6" t="n"/>
+      <c r="E147" s="6" t="n"/>
+      <c r="F147" s="5" t="n"/>
+      <c r="G147" s="5" t="n"/>
+      <c r="H147" s="6" t="n"/>
+    </row>
+    <row r="148" hidden="1" outlineLevel="2">
+      <c r="A148" s="4" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="B148" s="5" t="n"/>
+      <c r="C148" s="6" t="n"/>
+      <c r="D148" s="6" t="n"/>
+      <c r="E148" s="6" t="n"/>
+      <c r="F148" s="5" t="n"/>
+      <c r="G148" s="5" t="n"/>
+      <c r="H148" s="6" t="n"/>
+    </row>
+    <row r="149" hidden="1" outlineLevel="2">
+      <c r="A149" s="4" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="B149" s="5" t="n"/>
+      <c r="C149" s="6" t="n"/>
+      <c r="D149" s="6" t="n"/>
+      <c r="E149" s="6" t="n"/>
+      <c r="F149" s="5" t="n"/>
+      <c r="G149" s="5" t="n"/>
+      <c r="H149" s="6" t="n"/>
+    </row>
+    <row r="150" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A150" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="B150" s="5" t="n"/>
+      <c r="C150" s="6" t="n"/>
+      <c r="D150" s="6" t="n"/>
+      <c r="E150" s="6" t="n"/>
+      <c r="F150" s="5" t="n"/>
+      <c r="G150" s="5" t="n"/>
+      <c r="H150" s="6" t="n"/>
+    </row>
+    <row r="151" hidden="1" outlineLevel="2">
+      <c r="A151" s="4" t="n">
+        <v>37.25</v>
+      </c>
+      <c r="B151" s="5" t="n"/>
+      <c r="C151" s="6" t="n"/>
+      <c r="D151" s="6" t="n"/>
+      <c r="E151" s="6" t="n"/>
+      <c r="F151" s="5" t="n"/>
+      <c r="G151" s="5" t="n"/>
+      <c r="H151" s="6" t="n"/>
+    </row>
+    <row r="152" hidden="1" outlineLevel="2">
+      <c r="A152" s="4" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="B152" s="5" t="n"/>
+      <c r="C152" s="6" t="n"/>
+      <c r="D152" s="6" t="n"/>
+      <c r="E152" s="6" t="n"/>
+      <c r="F152" s="5" t="n"/>
+      <c r="G152" s="5" t="n"/>
+      <c r="H152" s="6" t="n"/>
+    </row>
+    <row r="153" hidden="1" outlineLevel="2">
+      <c r="A153" s="4" t="n">
+        <v>37.75</v>
+      </c>
+      <c r="B153" s="5" t="n"/>
+      <c r="C153" s="6" t="n"/>
+      <c r="D153" s="6" t="n"/>
+      <c r="E153" s="6" t="n"/>
+      <c r="F153" s="5" t="n"/>
+      <c r="G153" s="5" t="n"/>
+      <c r="H153" s="6" t="n"/>
+    </row>
+    <row r="154" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A154" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="B154" s="5" t="n"/>
+      <c r="C154" s="6" t="n"/>
+      <c r="D154" s="6" t="n"/>
+      <c r="E154" s="6" t="n"/>
+      <c r="F154" s="5" t="n"/>
+      <c r="G154" s="5" t="n"/>
+      <c r="H154" s="6" t="n"/>
+    </row>
+    <row r="155" hidden="1" outlineLevel="2">
+      <c r="A155" s="4" t="n">
+        <v>38.25</v>
+      </c>
+      <c r="B155" s="5" t="n"/>
+      <c r="C155" s="6" t="n"/>
+      <c r="D155" s="6" t="n"/>
+      <c r="E155" s="6" t="n"/>
+      <c r="F155" s="5" t="n"/>
+      <c r="G155" s="5" t="n"/>
+      <c r="H155" s="6" t="n"/>
+    </row>
+    <row r="156" hidden="1" outlineLevel="2">
+      <c r="A156" s="4" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="B156" s="5" t="n"/>
+      <c r="C156" s="6" t="n"/>
+      <c r="D156" s="6" t="n"/>
+      <c r="E156" s="6" t="n"/>
+      <c r="F156" s="5" t="n"/>
+      <c r="G156" s="5" t="n"/>
+      <c r="H156" s="6" t="n"/>
+    </row>
+    <row r="157" hidden="1" outlineLevel="2">
+      <c r="A157" s="4" t="n">
+        <v>38.75</v>
+      </c>
+      <c r="B157" s="5" t="n"/>
+      <c r="C157" s="6" t="n"/>
+      <c r="D157" s="6" t="n"/>
+      <c r="E157" s="6" t="n"/>
+      <c r="F157" s="5" t="n"/>
+      <c r="G157" s="5" t="n"/>
+      <c r="H157" s="6" t="n"/>
+    </row>
+    <row r="158" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A158" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="B158" s="5" t="n"/>
+      <c r="C158" s="6" t="n"/>
+      <c r="D158" s="6" t="n"/>
+      <c r="E158" s="6" t="n"/>
+      <c r="F158" s="5" t="n"/>
+      <c r="G158" s="5" t="n"/>
+      <c r="H158" s="6" t="n"/>
+    </row>
+    <row r="159" hidden="1" outlineLevel="2">
+      <c r="A159" s="4" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="B159" s="5" t="n"/>
+      <c r="C159" s="6" t="n"/>
+      <c r="D159" s="6" t="n"/>
+      <c r="E159" s="6" t="n"/>
+      <c r="F159" s="5" t="n"/>
+      <c r="G159" s="5" t="n"/>
+      <c r="H159" s="6" t="n"/>
+    </row>
+    <row r="160" hidden="1" outlineLevel="2">
+      <c r="A160" s="4" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="B160" s="5" t="n"/>
+      <c r="C160" s="6" t="n"/>
+      <c r="D160" s="6" t="n"/>
+      <c r="E160" s="6" t="n"/>
+      <c r="F160" s="5" t="n"/>
+      <c r="G160" s="5" t="n"/>
+      <c r="H160" s="6" t="n"/>
+    </row>
+    <row r="161" hidden="1" outlineLevel="2">
+      <c r="A161" s="4" t="n">
+        <v>39.75</v>
+      </c>
+      <c r="B161" s="5" t="n"/>
+      <c r="C161" s="6" t="n"/>
+      <c r="D161" s="6" t="n"/>
+      <c r="E161" s="6" t="n"/>
+      <c r="F161" s="5" t="n"/>
+      <c r="G161" s="5" t="n"/>
+      <c r="H161" s="6" t="n"/>
+    </row>
+    <row r="162" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A162" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="B162" s="5" t="n"/>
+      <c r="C162" s="6" t="n"/>
+      <c r="D162" s="6" t="n"/>
+      <c r="E162" s="6" t="n"/>
+      <c r="F162" s="5" t="n"/>
+      <c r="G162" s="5" t="n"/>
+      <c r="H162" s="6" t="n"/>
+    </row>
+    <row r="163" hidden="1" outlineLevel="2">
+      <c r="A163" s="4" t="n">
+        <v>40.25</v>
+      </c>
+      <c r="B163" s="5" t="n"/>
+      <c r="C163" s="6" t="n"/>
+      <c r="D163" s="6" t="n"/>
+      <c r="E163" s="6" t="n"/>
+      <c r="F163" s="5" t="n"/>
+      <c r="G163" s="5" t="n"/>
+      <c r="H163" s="6" t="n"/>
+    </row>
+    <row r="164" hidden="1" outlineLevel="2">
+      <c r="A164" s="4" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="B164" s="5" t="n"/>
+      <c r="C164" s="6" t="n"/>
+      <c r="D164" s="6" t="n"/>
+      <c r="E164" s="6" t="n"/>
+      <c r="F164" s="5" t="n"/>
+      <c r="G164" s="5" t="n"/>
+      <c r="H164" s="6" t="n"/>
+    </row>
+    <row r="165" hidden="1" outlineLevel="2">
+      <c r="A165" s="4" t="n">
+        <v>40.75</v>
+      </c>
+      <c r="B165" s="5" t="n"/>
+      <c r="C165" s="6" t="n"/>
+      <c r="D165" s="6" t="n"/>
+      <c r="E165" s="6" t="n"/>
+      <c r="F165" s="5" t="n"/>
+      <c r="G165" s="5" t="n"/>
+      <c r="H165" s="6" t="n"/>
+    </row>
+    <row r="166" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A166" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="B166" s="5" t="n"/>
+      <c r="C166" s="6" t="n"/>
+      <c r="D166" s="6" t="n"/>
+      <c r="E166" s="6" t="n"/>
+      <c r="F166" s="5" t="n"/>
+      <c r="G166" s="5" t="n"/>
+      <c r="H166" s="6" t="n"/>
+    </row>
+    <row r="167" hidden="1" outlineLevel="2">
+      <c r="A167" s="4" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="B167" s="5" t="n"/>
+      <c r="C167" s="6" t="n"/>
+      <c r="D167" s="6" t="n"/>
+      <c r="E167" s="6" t="n"/>
+      <c r="F167" s="5" t="n"/>
+      <c r="G167" s="5" t="n"/>
+      <c r="H167" s="6" t="n"/>
+    </row>
+    <row r="168" hidden="1" outlineLevel="2">
+      <c r="A168" s="4" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="B168" s="5" t="n"/>
+      <c r="C168" s="6" t="n"/>
+      <c r="D168" s="6" t="n"/>
+      <c r="E168" s="6" t="n"/>
+      <c r="F168" s="5" t="n"/>
+      <c r="G168" s="5" t="n"/>
+      <c r="H168" s="6" t="n"/>
+    </row>
+    <row r="169" hidden="1" outlineLevel="2">
+      <c r="A169" s="4" t="n">
+        <v>41.75</v>
+      </c>
+      <c r="B169" s="5" t="n"/>
+      <c r="C169" s="6" t="n"/>
+      <c r="D169" s="6" t="n"/>
+      <c r="E169" s="6" t="n"/>
+      <c r="F169" s="5" t="n"/>
+      <c r="G169" s="5" t="n"/>
+      <c r="H169" s="6" t="n"/>
+    </row>
+    <row r="170" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A170" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="B170" s="5" t="n"/>
+      <c r="C170" s="6" t="n"/>
+      <c r="D170" s="6" t="n"/>
+      <c r="E170" s="6" t="n"/>
+      <c r="F170" s="5" t="n"/>
+      <c r="G170" s="5" t="n"/>
+      <c r="H170" s="6" t="n"/>
+    </row>
+    <row r="171" hidden="1" outlineLevel="2">
+      <c r="A171" s="4" t="n">
+        <v>42.25</v>
+      </c>
+      <c r="B171" s="5" t="n"/>
+      <c r="C171" s="6" t="n"/>
+      <c r="D171" s="6" t="n"/>
+      <c r="E171" s="6" t="n"/>
+      <c r="F171" s="5" t="n"/>
+      <c r="G171" s="5" t="n"/>
+      <c r="H171" s="6" t="n"/>
+    </row>
+    <row r="172" hidden="1" outlineLevel="2">
+      <c r="A172" s="4" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="B172" s="5" t="n"/>
+      <c r="C172" s="6" t="n"/>
+      <c r="D172" s="6" t="n"/>
+      <c r="E172" s="6" t="n"/>
+      <c r="F172" s="5" t="n"/>
+      <c r="G172" s="5" t="n"/>
+      <c r="H172" s="6" t="n"/>
+    </row>
+    <row r="173" hidden="1" outlineLevel="2">
+      <c r="A173" s="4" t="n">
+        <v>42.75</v>
+      </c>
+      <c r="B173" s="5" t="n"/>
+      <c r="C173" s="6" t="n"/>
+      <c r="D173" s="6" t="n"/>
+      <c r="E173" s="6" t="n"/>
+      <c r="F173" s="5" t="n"/>
+      <c r="G173" s="5" t="n"/>
+      <c r="H173" s="6" t="n"/>
+    </row>
+    <row r="174" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A174" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="B174" s="5" t="n"/>
+      <c r="C174" s="6" t="n"/>
+      <c r="D174" s="6" t="n"/>
+      <c r="E174" s="6" t="n"/>
+      <c r="F174" s="5" t="n"/>
+      <c r="G174" s="5" t="n"/>
+      <c r="H174" s="6" t="n"/>
+    </row>
+    <row r="175" hidden="1" outlineLevel="2">
+      <c r="A175" s="4" t="n">
+        <v>43.25</v>
+      </c>
+      <c r="B175" s="5" t="n"/>
+      <c r="C175" s="6" t="n"/>
+      <c r="D175" s="6" t="n"/>
+      <c r="E175" s="6" t="n"/>
+      <c r="F175" s="5" t="n"/>
+      <c r="G175" s="5" t="n"/>
+      <c r="H175" s="6" t="n"/>
+    </row>
+    <row r="176" hidden="1" outlineLevel="2">
+      <c r="A176" s="4" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="B176" s="5" t="n"/>
+      <c r="C176" s="6" t="n"/>
+      <c r="D176" s="6" t="n"/>
+      <c r="E176" s="6" t="n"/>
+      <c r="F176" s="5" t="n"/>
+      <c r="G176" s="5" t="n"/>
+      <c r="H176" s="6" t="n"/>
+    </row>
+    <row r="177" hidden="1" outlineLevel="2">
+      <c r="A177" s="4" t="n">
+        <v>43.75</v>
+      </c>
+      <c r="B177" s="5" t="n"/>
+      <c r="C177" s="6" t="n"/>
+      <c r="D177" s="6" t="n"/>
+      <c r="E177" s="6" t="n"/>
+      <c r="F177" s="5" t="n"/>
+      <c r="G177" s="5" t="n"/>
+      <c r="H177" s="6" t="n"/>
+    </row>
+    <row r="178" collapsed="1">
+      <c r="A178" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B178" s="5" t="inlineStr">
         <is>
           <t>bridge</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>alter Code (handgeschrieben, läuft so in der Firmware):
-progFastBlingBling(7620, 4, 32)
-! Excel: 8 Takte, der alte Code ist anders</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="C178" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_DROP, Farben SCHEME_NEON
+Ausgabe: Übergang flash 476 ms
+Der Drop: weißer Blitz auf den Einsatz, danach Schockwellen und Blitze auf jeden Beat in Pink, Cyan und Violett.</t>
+        </is>
+      </c>
+      <c r="D178" s="6" t="n"/>
+      <c r="E178" s="6" t="inlineStr">
         <is>
           <t>Der Drop: Szene Drop, NEON (Schockwellen und Beat-Blitze) statt dezenter Einzelblitze; weißer Blitz auf den Einsatz (Übergang flash).</t>
         </is>
       </c>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5">
+      <c r="F178" s="5" t="n"/>
+      <c r="G178" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H178" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(7620, 4, 32)
 ! Excel: 8 Takte, der alte Code ist anders</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="n">
+    <row r="179" hidden="1" outlineLevel="2">
+      <c r="A179" s="4" t="n">
+        <v>44.25</v>
+      </c>
+      <c r="B179" s="5" t="n"/>
+      <c r="C179" s="6" t="n"/>
+      <c r="D179" s="6" t="n"/>
+      <c r="E179" s="6" t="n"/>
+      <c r="F179" s="5" t="n"/>
+      <c r="G179" s="5" t="n"/>
+      <c r="H179" s="6" t="n"/>
+    </row>
+    <row r="180" hidden="1" outlineLevel="2">
+      <c r="A180" s="4" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="B180" s="5" t="n"/>
+      <c r="C180" s="6" t="n"/>
+      <c r="D180" s="6" t="n"/>
+      <c r="E180" s="6" t="n"/>
+      <c r="F180" s="5" t="n"/>
+      <c r="G180" s="5" t="n"/>
+      <c r="H180" s="6" t="n"/>
+    </row>
+    <row r="181" hidden="1" outlineLevel="2">
+      <c r="A181" s="4" t="n">
+        <v>44.75</v>
+      </c>
+      <c r="B181" s="5" t="n"/>
+      <c r="C181" s="6" t="n"/>
+      <c r="D181" s="6" t="n"/>
+      <c r="E181" s="6" t="n"/>
+      <c r="F181" s="5" t="n"/>
+      <c r="G181" s="5" t="n"/>
+      <c r="H181" s="6" t="n"/>
+    </row>
+    <row r="182" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A182" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="B182" s="5" t="n"/>
+      <c r="C182" s="6" t="n"/>
+      <c r="D182" s="6" t="n"/>
+      <c r="E182" s="6" t="n"/>
+      <c r="F182" s="5" t="n"/>
+      <c r="G182" s="5" t="n"/>
+      <c r="H182" s="6" t="n"/>
+    </row>
+    <row r="183" hidden="1" outlineLevel="2">
+      <c r="A183" s="4" t="n">
+        <v>45.25</v>
+      </c>
+      <c r="B183" s="5" t="n"/>
+      <c r="C183" s="6" t="n"/>
+      <c r="D183" s="6" t="n"/>
+      <c r="E183" s="6" t="n"/>
+      <c r="F183" s="5" t="n"/>
+      <c r="G183" s="5" t="n"/>
+      <c r="H183" s="6" t="n"/>
+    </row>
+    <row r="184" hidden="1" outlineLevel="2">
+      <c r="A184" s="4" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="B184" s="5" t="n"/>
+      <c r="C184" s="6" t="n"/>
+      <c r="D184" s="6" t="n"/>
+      <c r="E184" s="6" t="n"/>
+      <c r="F184" s="5" t="n"/>
+      <c r="G184" s="5" t="n"/>
+      <c r="H184" s="6" t="n"/>
+    </row>
+    <row r="185" hidden="1" outlineLevel="2">
+      <c r="A185" s="4" t="n">
+        <v>45.75</v>
+      </c>
+      <c r="B185" s="5" t="n"/>
+      <c r="C185" s="6" t="n"/>
+      <c r="D185" s="6" t="n"/>
+      <c r="E185" s="6" t="n"/>
+      <c r="F185" s="5" t="n"/>
+      <c r="G185" s="5" t="n"/>
+      <c r="H185" s="6" t="n"/>
+    </row>
+    <row r="186" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A186" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="B186" s="5" t="n"/>
+      <c r="C186" s="6" t="n"/>
+      <c r="D186" s="6" t="n"/>
+      <c r="E186" s="6" t="n"/>
+      <c r="F186" s="5" t="n"/>
+      <c r="G186" s="5" t="n"/>
+      <c r="H186" s="6" t="n"/>
+    </row>
+    <row r="187" hidden="1" outlineLevel="2">
+      <c r="A187" s="4" t="n">
+        <v>46.25</v>
+      </c>
+      <c r="B187" s="5" t="n"/>
+      <c r="C187" s="6" t="n"/>
+      <c r="D187" s="6" t="n"/>
+      <c r="E187" s="6" t="n"/>
+      <c r="F187" s="5" t="n"/>
+      <c r="G187" s="5" t="n"/>
+      <c r="H187" s="6" t="n"/>
+    </row>
+    <row r="188" hidden="1" outlineLevel="2">
+      <c r="A188" s="4" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="B188" s="5" t="n"/>
+      <c r="C188" s="6" t="n"/>
+      <c r="D188" s="6" t="n"/>
+      <c r="E188" s="6" t="n"/>
+      <c r="F188" s="5" t="n"/>
+      <c r="G188" s="5" t="n"/>
+      <c r="H188" s="6" t="n"/>
+    </row>
+    <row r="189" hidden="1" outlineLevel="2">
+      <c r="A189" s="4" t="n">
+        <v>46.75</v>
+      </c>
+      <c r="B189" s="5" t="n"/>
+      <c r="C189" s="6" t="n"/>
+      <c r="D189" s="6" t="n"/>
+      <c r="E189" s="6" t="n"/>
+      <c r="F189" s="5" t="n"/>
+      <c r="G189" s="5" t="n"/>
+      <c r="H189" s="6" t="n"/>
+    </row>
+    <row r="190" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A190" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="B190" s="5" t="n"/>
+      <c r="C190" s="6" t="n"/>
+      <c r="D190" s="6" t="n"/>
+      <c r="E190" s="6" t="n"/>
+      <c r="F190" s="5" t="n"/>
+      <c r="G190" s="5" t="n"/>
+      <c r="H190" s="6" t="n"/>
+    </row>
+    <row r="191" hidden="1" outlineLevel="2">
+      <c r="A191" s="4" t="n">
+        <v>47.25</v>
+      </c>
+      <c r="B191" s="5" t="n"/>
+      <c r="C191" s="6" t="n"/>
+      <c r="D191" s="6" t="n"/>
+      <c r="E191" s="6" t="n"/>
+      <c r="F191" s="5" t="n"/>
+      <c r="G191" s="5" t="n"/>
+      <c r="H191" s="6" t="n"/>
+    </row>
+    <row r="192" hidden="1" outlineLevel="2">
+      <c r="A192" s="4" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="B192" s="5" t="n"/>
+      <c r="C192" s="6" t="n"/>
+      <c r="D192" s="6" t="n"/>
+      <c r="E192" s="6" t="n"/>
+      <c r="F192" s="5" t="n"/>
+      <c r="G192" s="5" t="n"/>
+      <c r="H192" s="6" t="n"/>
+    </row>
+    <row r="193" hidden="1" outlineLevel="2">
+      <c r="A193" s="4" t="n">
+        <v>47.75</v>
+      </c>
+      <c r="B193" s="5" t="n"/>
+      <c r="C193" s="6" t="n"/>
+      <c r="D193" s="6" t="n"/>
+      <c r="E193" s="6" t="n"/>
+      <c r="F193" s="5" t="n"/>
+      <c r="G193" s="5" t="n"/>
+      <c r="H193" s="6" t="n"/>
+    </row>
+    <row r="194" collapsed="1">
+      <c r="A194" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B194" s="5" t="inlineStr">
         <is>
           <t>half time</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>alter Code (handgeschrieben, läuft so in der Firmware):
-progMatrixScanner(7620, 35, 20)</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="C194" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_CALM, Farben SCHEME_NEON
+Ausgabe: Blinder alle 2 Beat(s), 714 ms
+Halftime sichtbar: ein warmweißer Blinder auf jede Halbe (alle 2 Beats, 1,5 Beats lang) über dunklem Atmen in Pink und Cyan.</t>
+        </is>
+      </c>
+      <c r="D194" s="6" t="n"/>
+      <c r="E194" s="6" t="inlineStr">
         <is>
           <t>Blinder auf jede Halbe (alle 2 Beats, je 1,5 Beats lang) über dunklem Atmen - Halftime sichtbar.</t>
         </is>
       </c>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5">
+      <c r="F194" s="5" t="n"/>
+      <c r="G194" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H194" s="6" t="inlineStr">
         <is>
           <t>progMatrixScanner(7620, 35, 20)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="n">
+    <row r="195" hidden="1" outlineLevel="2">
+      <c r="A195" s="4" t="n">
+        <v>48.25</v>
+      </c>
+      <c r="B195" s="5" t="n"/>
+      <c r="C195" s="6" t="n"/>
+      <c r="D195" s="6" t="n"/>
+      <c r="E195" s="6" t="n"/>
+      <c r="F195" s="5" t="n"/>
+      <c r="G195" s="5" t="n"/>
+      <c r="H195" s="6" t="n"/>
+    </row>
+    <row r="196" hidden="1" outlineLevel="2">
+      <c r="A196" s="4" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="B196" s="5" t="n"/>
+      <c r="C196" s="6" t="n"/>
+      <c r="D196" s="6" t="n"/>
+      <c r="E196" s="6" t="n"/>
+      <c r="F196" s="5" t="n"/>
+      <c r="G196" s="5" t="n"/>
+      <c r="H196" s="6" t="n"/>
+    </row>
+    <row r="197" hidden="1" outlineLevel="2">
+      <c r="A197" s="4" t="n">
+        <v>48.75</v>
+      </c>
+      <c r="B197" s="5" t="n"/>
+      <c r="C197" s="6" t="n"/>
+      <c r="D197" s="6" t="n"/>
+      <c r="E197" s="6" t="n"/>
+      <c r="F197" s="5" t="n"/>
+      <c r="G197" s="5" t="n"/>
+      <c r="H197" s="6" t="n"/>
+    </row>
+    <row r="198" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A198" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="B198" s="5" t="n"/>
+      <c r="C198" s="6" t="n"/>
+      <c r="D198" s="6" t="n"/>
+      <c r="E198" s="6" t="n"/>
+      <c r="F198" s="5" t="n"/>
+      <c r="G198" s="5" t="n"/>
+      <c r="H198" s="6" t="n"/>
+    </row>
+    <row r="199" hidden="1" outlineLevel="2">
+      <c r="A199" s="4" t="n">
+        <v>49.25</v>
+      </c>
+      <c r="B199" s="5" t="n"/>
+      <c r="C199" s="6" t="n"/>
+      <c r="D199" s="6" t="n"/>
+      <c r="E199" s="6" t="n"/>
+      <c r="F199" s="5" t="n"/>
+      <c r="G199" s="5" t="n"/>
+      <c r="H199" s="6" t="n"/>
+    </row>
+    <row r="200" hidden="1" outlineLevel="2">
+      <c r="A200" s="4" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="B200" s="5" t="n"/>
+      <c r="C200" s="6" t="n"/>
+      <c r="D200" s="6" t="n"/>
+      <c r="E200" s="6" t="n"/>
+      <c r="F200" s="5" t="n"/>
+      <c r="G200" s="5" t="n"/>
+      <c r="H200" s="6" t="n"/>
+    </row>
+    <row r="201" hidden="1" outlineLevel="2">
+      <c r="A201" s="4" t="n">
+        <v>49.75</v>
+      </c>
+      <c r="B201" s="5" t="n"/>
+      <c r="C201" s="6" t="n"/>
+      <c r="D201" s="6" t="n"/>
+      <c r="E201" s="6" t="n"/>
+      <c r="F201" s="5" t="n"/>
+      <c r="G201" s="5" t="n"/>
+      <c r="H201" s="6" t="n"/>
+    </row>
+    <row r="202" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A202" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="B202" s="5" t="n"/>
+      <c r="C202" s="6" t="n"/>
+      <c r="D202" s="6" t="n"/>
+      <c r="E202" s="6" t="n"/>
+      <c r="F202" s="5" t="n"/>
+      <c r="G202" s="5" t="n"/>
+      <c r="H202" s="6" t="n"/>
+    </row>
+    <row r="203" hidden="1" outlineLevel="2">
+      <c r="A203" s="4" t="n">
+        <v>50.25</v>
+      </c>
+      <c r="B203" s="5" t="n"/>
+      <c r="C203" s="6" t="n"/>
+      <c r="D203" s="6" t="n"/>
+      <c r="E203" s="6" t="n"/>
+      <c r="F203" s="5" t="n"/>
+      <c r="G203" s="5" t="n"/>
+      <c r="H203" s="6" t="n"/>
+    </row>
+    <row r="204" hidden="1" outlineLevel="2">
+      <c r="A204" s="4" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="B204" s="5" t="n"/>
+      <c r="C204" s="6" t="n"/>
+      <c r="D204" s="6" t="n"/>
+      <c r="E204" s="6" t="n"/>
+      <c r="F204" s="5" t="n"/>
+      <c r="G204" s="5" t="n"/>
+      <c r="H204" s="6" t="n"/>
+    </row>
+    <row r="205" hidden="1" outlineLevel="2">
+      <c r="A205" s="4" t="n">
+        <v>50.75</v>
+      </c>
+      <c r="B205" s="5" t="n"/>
+      <c r="C205" s="6" t="n"/>
+      <c r="D205" s="6" t="n"/>
+      <c r="E205" s="6" t="n"/>
+      <c r="F205" s="5" t="n"/>
+      <c r="G205" s="5" t="n"/>
+      <c r="H205" s="6" t="n"/>
+    </row>
+    <row r="206" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A206" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="B206" s="5" t="n"/>
+      <c r="C206" s="6" t="n"/>
+      <c r="D206" s="6" t="n"/>
+      <c r="E206" s="6" t="n"/>
+      <c r="F206" s="5" t="n"/>
+      <c r="G206" s="5" t="n"/>
+      <c r="H206" s="6" t="n"/>
+    </row>
+    <row r="207" hidden="1" outlineLevel="2">
+      <c r="A207" s="4" t="n">
+        <v>51.25</v>
+      </c>
+      <c r="B207" s="5" t="n"/>
+      <c r="C207" s="6" t="n"/>
+      <c r="D207" s="6" t="n"/>
+      <c r="E207" s="6" t="n"/>
+      <c r="F207" s="5" t="n"/>
+      <c r="G207" s="5" t="n"/>
+      <c r="H207" s="6" t="n"/>
+    </row>
+    <row r="208" hidden="1" outlineLevel="2">
+      <c r="A208" s="4" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="B208" s="5" t="n"/>
+      <c r="C208" s="6" t="n"/>
+      <c r="D208" s="6" t="n"/>
+      <c r="E208" s="6" t="n"/>
+      <c r="F208" s="5" t="n"/>
+      <c r="G208" s="5" t="n"/>
+      <c r="H208" s="6" t="n"/>
+    </row>
+    <row r="209" hidden="1" outlineLevel="2">
+      <c r="A209" s="4" t="n">
+        <v>51.75</v>
+      </c>
+      <c r="B209" s="5" t="n"/>
+      <c r="C209" s="6" t="n"/>
+      <c r="D209" s="6" t="n"/>
+      <c r="E209" s="6" t="n"/>
+      <c r="F209" s="5" t="n"/>
+      <c r="G209" s="5" t="n"/>
+      <c r="H209" s="6" t="n"/>
+    </row>
+    <row r="210" collapsed="1">
+      <c r="A210" s="4" t="n">
         <v>52</v>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B210" s="5" t="inlineStr">
         <is>
           <t>v2: cut me down</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>alter Code (handgeschrieben, läuft so in der Firmware):
-progPalette(15235, 9, 40)</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="C210" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_DNA_FLIP, Farben SCHEME_ICE
+Stehende DNA-Helix in Eisblau auf der Matrix, die Stränge tauschen jeden Takt die Seiten; alle anderen Geräte pulsieren einmal je Takt.</t>
+        </is>
+      </c>
+      <c r="D210" s="6" t="n"/>
+      <c r="E210" s="6" t="inlineStr">
         <is>
           <t>Szene DNA Flip, ICE: stehende Helix auf der Matrix, alle anderen pulsieren einmal je Takt.</t>
         </is>
       </c>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5">
+      <c r="F210" s="5" t="n"/>
+      <c r="G210" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H210" s="6" t="inlineStr">
         <is>
           <t>progPalette(15235, 9, 40)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
+    <row r="211" hidden="1" outlineLevel="2">
+      <c r="A211" s="4" t="n">
+        <v>52.25</v>
+      </c>
+      <c r="B211" s="5" t="n"/>
+      <c r="C211" s="6" t="n"/>
+      <c r="D211" s="6" t="n"/>
+      <c r="E211" s="6" t="n"/>
+      <c r="F211" s="5" t="n"/>
+      <c r="G211" s="5" t="n"/>
+      <c r="H211" s="6" t="n"/>
+    </row>
+    <row r="212" hidden="1" outlineLevel="2">
+      <c r="A212" s="4" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="B212" s="5" t="n"/>
+      <c r="C212" s="6" t="n"/>
+      <c r="D212" s="6" t="n"/>
+      <c r="E212" s="6" t="n"/>
+      <c r="F212" s="5" t="n"/>
+      <c r="G212" s="5" t="n"/>
+      <c r="H212" s="6" t="n"/>
+    </row>
+    <row r="213" hidden="1" outlineLevel="2">
+      <c r="A213" s="4" t="n">
+        <v>52.75</v>
+      </c>
+      <c r="B213" s="5" t="n"/>
+      <c r="C213" s="6" t="n"/>
+      <c r="D213" s="6" t="n"/>
+      <c r="E213" s="6" t="n"/>
+      <c r="F213" s="5" t="n"/>
+      <c r="G213" s="5" t="n"/>
+      <c r="H213" s="6" t="n"/>
+    </row>
+    <row r="214" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A214" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="B214" s="5" t="n"/>
+      <c r="C214" s="6" t="n"/>
+      <c r="D214" s="6" t="n"/>
+      <c r="E214" s="6" t="n"/>
+      <c r="F214" s="5" t="n"/>
+      <c r="G214" s="5" t="n"/>
+      <c r="H214" s="6" t="n"/>
+    </row>
+    <row r="215" hidden="1" outlineLevel="2">
+      <c r="A215" s="4" t="n">
+        <v>53.25</v>
+      </c>
+      <c r="B215" s="5" t="n"/>
+      <c r="C215" s="6" t="n"/>
+      <c r="D215" s="6" t="n"/>
+      <c r="E215" s="6" t="n"/>
+      <c r="F215" s="5" t="n"/>
+      <c r="G215" s="5" t="n"/>
+      <c r="H215" s="6" t="n"/>
+    </row>
+    <row r="216" hidden="1" outlineLevel="2">
+      <c r="A216" s="4" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="B216" s="5" t="n"/>
+      <c r="C216" s="6" t="n"/>
+      <c r="D216" s="6" t="n"/>
+      <c r="E216" s="6" t="n"/>
+      <c r="F216" s="5" t="n"/>
+      <c r="G216" s="5" t="n"/>
+      <c r="H216" s="6" t="n"/>
+    </row>
+    <row r="217" hidden="1" outlineLevel="2">
+      <c r="A217" s="4" t="n">
+        <v>53.75</v>
+      </c>
+      <c r="B217" s="5" t="n"/>
+      <c r="C217" s="6" t="n"/>
+      <c r="D217" s="6" t="n"/>
+      <c r="E217" s="6" t="n"/>
+      <c r="F217" s="5" t="n"/>
+      <c r="G217" s="5" t="n"/>
+      <c r="H217" s="6" t="n"/>
+    </row>
+    <row r="218" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A218" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="B218" s="5" t="n"/>
+      <c r="C218" s="6" t="n"/>
+      <c r="D218" s="6" t="n"/>
+      <c r="E218" s="6" t="n"/>
+      <c r="F218" s="5" t="n"/>
+      <c r="G218" s="5" t="n"/>
+      <c r="H218" s="6" t="n"/>
+    </row>
+    <row r="219" hidden="1" outlineLevel="2">
+      <c r="A219" s="4" t="n">
+        <v>54.25</v>
+      </c>
+      <c r="B219" s="5" t="n"/>
+      <c r="C219" s="6" t="n"/>
+      <c r="D219" s="6" t="n"/>
+      <c r="E219" s="6" t="n"/>
+      <c r="F219" s="5" t="n"/>
+      <c r="G219" s="5" t="n"/>
+      <c r="H219" s="6" t="n"/>
+    </row>
+    <row r="220" hidden="1" outlineLevel="2">
+      <c r="A220" s="4" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="B220" s="5" t="n"/>
+      <c r="C220" s="6" t="n"/>
+      <c r="D220" s="6" t="n"/>
+      <c r="E220" s="6" t="n"/>
+      <c r="F220" s="5" t="n"/>
+      <c r="G220" s="5" t="n"/>
+      <c r="H220" s="6" t="n"/>
+    </row>
+    <row r="221" hidden="1" outlineLevel="2">
+      <c r="A221" s="4" t="n">
+        <v>54.75</v>
+      </c>
+      <c r="B221" s="5" t="n"/>
+      <c r="C221" s="6" t="n"/>
+      <c r="D221" s="6" t="n"/>
+      <c r="E221" s="6" t="n"/>
+      <c r="F221" s="5" t="n"/>
+      <c r="G221" s="5" t="n"/>
+      <c r="H221" s="6" t="n"/>
+    </row>
+    <row r="222" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A222" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="B222" s="5" t="n"/>
+      <c r="C222" s="6" t="n"/>
+      <c r="D222" s="6" t="n"/>
+      <c r="E222" s="6" t="n"/>
+      <c r="F222" s="5" t="n"/>
+      <c r="G222" s="5" t="n"/>
+      <c r="H222" s="6" t="n"/>
+    </row>
+    <row r="223" hidden="1" outlineLevel="2">
+      <c r="A223" s="4" t="n">
+        <v>55.25</v>
+      </c>
+      <c r="B223" s="5" t="n"/>
+      <c r="C223" s="6" t="n"/>
+      <c r="D223" s="6" t="n"/>
+      <c r="E223" s="6" t="n"/>
+      <c r="F223" s="5" t="n"/>
+      <c r="G223" s="5" t="n"/>
+      <c r="H223" s="6" t="n"/>
+    </row>
+    <row r="224" hidden="1" outlineLevel="2">
+      <c r="A224" s="4" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="B224" s="5" t="n"/>
+      <c r="C224" s="6" t="n"/>
+      <c r="D224" s="6" t="n"/>
+      <c r="E224" s="6" t="n"/>
+      <c r="F224" s="5" t="n"/>
+      <c r="G224" s="5" t="n"/>
+      <c r="H224" s="6" t="n"/>
+    </row>
+    <row r="225" hidden="1" outlineLevel="2">
+      <c r="A225" s="4" t="n">
+        <v>55.75</v>
+      </c>
+      <c r="B225" s="5" t="n"/>
+      <c r="C225" s="6" t="n"/>
+      <c r="D225" s="6" t="n"/>
+      <c r="E225" s="6" t="n"/>
+      <c r="F225" s="5" t="n"/>
+      <c r="G225" s="5" t="n"/>
+      <c r="H225" s="6" t="n"/>
+    </row>
+    <row r="226" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A226" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="B226" s="5" t="n"/>
+      <c r="C226" s="6" t="n"/>
+      <c r="D226" s="6" t="n"/>
+      <c r="E226" s="6" t="n"/>
+      <c r="F226" s="5" t="n"/>
+      <c r="G226" s="5" t="n"/>
+      <c r="H226" s="6" t="n"/>
+    </row>
+    <row r="227" hidden="1" outlineLevel="2">
+      <c r="A227" s="4" t="n">
+        <v>56.25</v>
+      </c>
+      <c r="B227" s="5" t="n"/>
+      <c r="C227" s="6" t="n"/>
+      <c r="D227" s="6" t="n"/>
+      <c r="E227" s="6" t="n"/>
+      <c r="F227" s="5" t="n"/>
+      <c r="G227" s="5" t="n"/>
+      <c r="H227" s="6" t="n"/>
+    </row>
+    <row r="228" hidden="1" outlineLevel="2">
+      <c r="A228" s="4" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="B228" s="5" t="n"/>
+      <c r="C228" s="6" t="n"/>
+      <c r="D228" s="6" t="n"/>
+      <c r="E228" s="6" t="n"/>
+      <c r="F228" s="5" t="n"/>
+      <c r="G228" s="5" t="n"/>
+      <c r="H228" s="6" t="n"/>
+    </row>
+    <row r="229" hidden="1" outlineLevel="2">
+      <c r="A229" s="4" t="n">
+        <v>56.75</v>
+      </c>
+      <c r="B229" s="5" t="n"/>
+      <c r="C229" s="6" t="n"/>
+      <c r="D229" s="6" t="n"/>
+      <c r="E229" s="6" t="n"/>
+      <c r="F229" s="5" t="n"/>
+      <c r="G229" s="5" t="n"/>
+      <c r="H229" s="6" t="n"/>
+    </row>
+    <row r="230" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A230" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="B230" s="5" t="n"/>
+      <c r="C230" s="6" t="n"/>
+      <c r="D230" s="6" t="n"/>
+      <c r="E230" s="6" t="n"/>
+      <c r="F230" s="5" t="n"/>
+      <c r="G230" s="5" t="n"/>
+      <c r="H230" s="6" t="n"/>
+    </row>
+    <row r="231" hidden="1" outlineLevel="2">
+      <c r="A231" s="4" t="n">
+        <v>57.25</v>
+      </c>
+      <c r="B231" s="5" t="n"/>
+      <c r="C231" s="6" t="n"/>
+      <c r="D231" s="6" t="n"/>
+      <c r="E231" s="6" t="n"/>
+      <c r="F231" s="5" t="n"/>
+      <c r="G231" s="5" t="n"/>
+      <c r="H231" s="6" t="n"/>
+    </row>
+    <row r="232" hidden="1" outlineLevel="2">
+      <c r="A232" s="4" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="B232" s="5" t="n"/>
+      <c r="C232" s="6" t="n"/>
+      <c r="D232" s="6" t="n"/>
+      <c r="E232" s="6" t="n"/>
+      <c r="F232" s="5" t="n"/>
+      <c r="G232" s="5" t="n"/>
+      <c r="H232" s="6" t="n"/>
+    </row>
+    <row r="233" hidden="1" outlineLevel="2">
+      <c r="A233" s="4" t="n">
+        <v>57.75</v>
+      </c>
+      <c r="B233" s="5" t="n"/>
+      <c r="C233" s="6" t="n"/>
+      <c r="D233" s="6" t="n"/>
+      <c r="E233" s="6" t="n"/>
+      <c r="F233" s="5" t="n"/>
+      <c r="G233" s="5" t="n"/>
+      <c r="H233" s="6" t="n"/>
+    </row>
+    <row r="234" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A234" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="B234" s="5" t="n"/>
+      <c r="C234" s="6" t="n"/>
+      <c r="D234" s="6" t="n"/>
+      <c r="E234" s="6" t="n"/>
+      <c r="F234" s="5" t="n"/>
+      <c r="G234" s="5" t="n"/>
+      <c r="H234" s="6" t="n"/>
+    </row>
+    <row r="235" hidden="1" outlineLevel="2">
+      <c r="A235" s="4" t="n">
+        <v>58.25</v>
+      </c>
+      <c r="B235" s="5" t="n"/>
+      <c r="C235" s="6" t="n"/>
+      <c r="D235" s="6" t="n"/>
+      <c r="E235" s="6" t="n"/>
+      <c r="F235" s="5" t="n"/>
+      <c r="G235" s="5" t="n"/>
+      <c r="H235" s="6" t="n"/>
+    </row>
+    <row r="236" hidden="1" outlineLevel="2">
+      <c r="A236" s="4" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="B236" s="5" t="n"/>
+      <c r="C236" s="6" t="n"/>
+      <c r="D236" s="6" t="n"/>
+      <c r="E236" s="6" t="n"/>
+      <c r="F236" s="5" t="n"/>
+      <c r="G236" s="5" t="n"/>
+      <c r="H236" s="6" t="n"/>
+    </row>
+    <row r="237" hidden="1" outlineLevel="2">
+      <c r="A237" s="4" t="n">
+        <v>58.75</v>
+      </c>
+      <c r="B237" s="5" t="n"/>
+      <c r="C237" s="6" t="n"/>
+      <c r="D237" s="6" t="n"/>
+      <c r="E237" s="6" t="n"/>
+      <c r="F237" s="5" t="n"/>
+      <c r="G237" s="5" t="n"/>
+      <c r="H237" s="6" t="n"/>
+    </row>
+    <row r="238" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A238" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="B238" s="5" t="n"/>
+      <c r="C238" s="6" t="n"/>
+      <c r="D238" s="6" t="n"/>
+      <c r="E238" s="6" t="n"/>
+      <c r="F238" s="5" t="n"/>
+      <c r="G238" s="5" t="n"/>
+      <c r="H238" s="6" t="n"/>
+    </row>
+    <row r="239" hidden="1" outlineLevel="2">
+      <c r="A239" s="4" t="n">
+        <v>59.25</v>
+      </c>
+      <c r="B239" s="5" t="n"/>
+      <c r="C239" s="6" t="n"/>
+      <c r="D239" s="6" t="n"/>
+      <c r="E239" s="6" t="n"/>
+      <c r="F239" s="5" t="n"/>
+      <c r="G239" s="5" t="n"/>
+      <c r="H239" s="6" t="n"/>
+    </row>
+    <row r="240" hidden="1" outlineLevel="2">
+      <c r="A240" s="4" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="B240" s="5" t="n"/>
+      <c r="C240" s="6" t="n"/>
+      <c r="D240" s="6" t="n"/>
+      <c r="E240" s="6" t="n"/>
+      <c r="F240" s="5" t="n"/>
+      <c r="G240" s="5" t="n"/>
+      <c r="H240" s="6" t="n"/>
+    </row>
+    <row r="241" hidden="1" outlineLevel="2">
+      <c r="A241" s="4" t="n">
+        <v>59.75</v>
+      </c>
+      <c r="B241" s="5" t="n"/>
+      <c r="C241" s="6" t="n"/>
+      <c r="D241" s="6" t="n"/>
+      <c r="E241" s="6" t="n"/>
+      <c r="F241" s="5" t="n"/>
+      <c r="G241" s="5" t="n"/>
+      <c r="H241" s="6" t="n"/>
+    </row>
+    <row r="242" collapsed="1">
+      <c r="A242" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B242" s="5" t="inlineStr">
         <is>
           <t>v2: race your voice</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>alter Code (handgeschrieben, läuft so in der Firmware):
-progWaterRipple(15240, 45, 50, true, false)</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="C242" s="6" t="inlineStr">
+        <is>
+          <t>progWaterRipple(15238, 13, 50, true, false), Farben SCHEME_ICE, Farbwanderung to triad, per 8
+Wasserringe (wie bisher), die Farben wandern alle 2 Takte weiter.</t>
+        </is>
+      </c>
+      <c r="D242" s="6" t="n"/>
+      <c r="E242" s="6" t="inlineStr">
         <is>
           <t>Wasserringe bleiben, Farbwanderung.</t>
         </is>
       </c>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5">
+      <c r="F242" s="5" t="n"/>
+      <c r="G242" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H242" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(15240, 45, 50, true, false)</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="n">
+    <row r="243" hidden="1" outlineLevel="2">
+      <c r="A243" s="4" t="n">
+        <v>60.25</v>
+      </c>
+      <c r="B243" s="5" t="n"/>
+      <c r="C243" s="6" t="n"/>
+      <c r="D243" s="6" t="n"/>
+      <c r="E243" s="6" t="n"/>
+      <c r="F243" s="5" t="n"/>
+      <c r="G243" s="5" t="n"/>
+      <c r="H243" s="6" t="n"/>
+    </row>
+    <row r="244" hidden="1" outlineLevel="2">
+      <c r="A244" s="4" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="B244" s="5" t="n"/>
+      <c r="C244" s="6" t="n"/>
+      <c r="D244" s="6" t="n"/>
+      <c r="E244" s="6" t="n"/>
+      <c r="F244" s="5" t="n"/>
+      <c r="G244" s="5" t="n"/>
+      <c r="H244" s="6" t="n"/>
+    </row>
+    <row r="245" hidden="1" outlineLevel="2">
+      <c r="A245" s="4" t="n">
+        <v>60.75</v>
+      </c>
+      <c r="B245" s="5" t="n"/>
+      <c r="C245" s="6" t="n"/>
+      <c r="D245" s="6" t="n"/>
+      <c r="E245" s="6" t="n"/>
+      <c r="F245" s="5" t="n"/>
+      <c r="G245" s="5" t="n"/>
+      <c r="H245" s="6" t="n"/>
+    </row>
+    <row r="246" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A246" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="B246" s="5" t="n"/>
+      <c r="C246" s="6" t="n"/>
+      <c r="D246" s="6" t="n"/>
+      <c r="E246" s="6" t="n"/>
+      <c r="F246" s="5" t="n"/>
+      <c r="G246" s="5" t="n"/>
+      <c r="H246" s="6" t="n"/>
+    </row>
+    <row r="247" hidden="1" outlineLevel="2">
+      <c r="A247" s="4" t="n">
+        <v>61.25</v>
+      </c>
+      <c r="B247" s="5" t="n"/>
+      <c r="C247" s="6" t="n"/>
+      <c r="D247" s="6" t="n"/>
+      <c r="E247" s="6" t="n"/>
+      <c r="F247" s="5" t="n"/>
+      <c r="G247" s="5" t="n"/>
+      <c r="H247" s="6" t="n"/>
+    </row>
+    <row r="248" hidden="1" outlineLevel="2">
+      <c r="A248" s="4" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="B248" s="5" t="n"/>
+      <c r="C248" s="6" t="n"/>
+      <c r="D248" s="6" t="n"/>
+      <c r="E248" s="6" t="n"/>
+      <c r="F248" s="5" t="n"/>
+      <c r="G248" s="5" t="n"/>
+      <c r="H248" s="6" t="n"/>
+    </row>
+    <row r="249" hidden="1" outlineLevel="2">
+      <c r="A249" s="4" t="n">
+        <v>61.75</v>
+      </c>
+      <c r="B249" s="5" t="n"/>
+      <c r="C249" s="6" t="n"/>
+      <c r="D249" s="6" t="n"/>
+      <c r="E249" s="6" t="n"/>
+      <c r="F249" s="5" t="n"/>
+      <c r="G249" s="5" t="n"/>
+      <c r="H249" s="6" t="n"/>
+    </row>
+    <row r="250" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A250" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="B250" s="5" t="n"/>
+      <c r="C250" s="6" t="n"/>
+      <c r="D250" s="6" t="n"/>
+      <c r="E250" s="6" t="n"/>
+      <c r="F250" s="5" t="n"/>
+      <c r="G250" s="5" t="n"/>
+      <c r="H250" s="6" t="n"/>
+    </row>
+    <row r="251" hidden="1" outlineLevel="2">
+      <c r="A251" s="4" t="n">
+        <v>62.25</v>
+      </c>
+      <c r="B251" s="5" t="n"/>
+      <c r="C251" s="6" t="n"/>
+      <c r="D251" s="6" t="n"/>
+      <c r="E251" s="6" t="n"/>
+      <c r="F251" s="5" t="n"/>
+      <c r="G251" s="5" t="n"/>
+      <c r="H251" s="6" t="n"/>
+    </row>
+    <row r="252" hidden="1" outlineLevel="2">
+      <c r="A252" s="4" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="B252" s="5" t="n"/>
+      <c r="C252" s="6" t="n"/>
+      <c r="D252" s="6" t="n"/>
+      <c r="E252" s="6" t="n"/>
+      <c r="F252" s="5" t="n"/>
+      <c r="G252" s="5" t="n"/>
+      <c r="H252" s="6" t="n"/>
+    </row>
+    <row r="253" hidden="1" outlineLevel="2">
+      <c r="A253" s="4" t="n">
+        <v>62.75</v>
+      </c>
+      <c r="B253" s="5" t="n"/>
+      <c r="C253" s="6" t="n"/>
+      <c r="D253" s="6" t="n"/>
+      <c r="E253" s="6" t="n"/>
+      <c r="F253" s="5" t="n"/>
+      <c r="G253" s="5" t="n"/>
+      <c r="H253" s="6" t="n"/>
+    </row>
+    <row r="254" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A254" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="B254" s="5" t="n"/>
+      <c r="C254" s="6" t="n"/>
+      <c r="D254" s="6" t="n"/>
+      <c r="E254" s="6" t="n"/>
+      <c r="F254" s="5" t="n"/>
+      <c r="G254" s="5" t="n"/>
+      <c r="H254" s="6" t="n"/>
+    </row>
+    <row r="255" hidden="1" outlineLevel="2">
+      <c r="A255" s="4" t="n">
+        <v>63.25</v>
+      </c>
+      <c r="B255" s="5" t="n"/>
+      <c r="C255" s="6" t="n"/>
+      <c r="D255" s="6" t="n"/>
+      <c r="E255" s="6" t="n"/>
+      <c r="F255" s="5" t="n"/>
+      <c r="G255" s="5" t="n"/>
+      <c r="H255" s="6" t="n"/>
+    </row>
+    <row r="256" hidden="1" outlineLevel="2">
+      <c r="A256" s="4" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="B256" s="5" t="n"/>
+      <c r="C256" s="6" t="n"/>
+      <c r="D256" s="6" t="n"/>
+      <c r="E256" s="6" t="n"/>
+      <c r="F256" s="5" t="n"/>
+      <c r="G256" s="5" t="n"/>
+      <c r="H256" s="6" t="n"/>
+    </row>
+    <row r="257" hidden="1" outlineLevel="2">
+      <c r="A257" s="4" t="n">
+        <v>63.75</v>
+      </c>
+      <c r="B257" s="5" t="n"/>
+      <c r="C257" s="6" t="n"/>
+      <c r="D257" s="6" t="n"/>
+      <c r="E257" s="6" t="n"/>
+      <c r="F257" s="5" t="n"/>
+      <c r="G257" s="5" t="n"/>
+      <c r="H257" s="6" t="n"/>
+    </row>
+    <row r="258" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A258" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="B258" s="5" t="n"/>
+      <c r="C258" s="6" t="n"/>
+      <c r="D258" s="6" t="n"/>
+      <c r="E258" s="6" t="n"/>
+      <c r="F258" s="5" t="n"/>
+      <c r="G258" s="5" t="n"/>
+      <c r="H258" s="6" t="n"/>
+    </row>
+    <row r="259" hidden="1" outlineLevel="2">
+      <c r="A259" s="4" t="n">
+        <v>64.25</v>
+      </c>
+      <c r="B259" s="5" t="n"/>
+      <c r="C259" s="6" t="n"/>
+      <c r="D259" s="6" t="n"/>
+      <c r="E259" s="6" t="n"/>
+      <c r="F259" s="5" t="n"/>
+      <c r="G259" s="5" t="n"/>
+      <c r="H259" s="6" t="n"/>
+    </row>
+    <row r="260" hidden="1" outlineLevel="2">
+      <c r="A260" s="4" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="B260" s="5" t="n"/>
+      <c r="C260" s="6" t="n"/>
+      <c r="D260" s="6" t="n"/>
+      <c r="E260" s="6" t="n"/>
+      <c r="F260" s="5" t="n"/>
+      <c r="G260" s="5" t="n"/>
+      <c r="H260" s="6" t="n"/>
+    </row>
+    <row r="261" hidden="1" outlineLevel="2">
+      <c r="A261" s="4" t="n">
+        <v>64.75</v>
+      </c>
+      <c r="B261" s="5" t="n"/>
+      <c r="C261" s="6" t="n"/>
+      <c r="D261" s="6" t="n"/>
+      <c r="E261" s="6" t="n"/>
+      <c r="F261" s="5" t="n"/>
+      <c r="G261" s="5" t="n"/>
+      <c r="H261" s="6" t="n"/>
+    </row>
+    <row r="262" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A262" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="B262" s="5" t="n"/>
+      <c r="C262" s="6" t="n"/>
+      <c r="D262" s="6" t="n"/>
+      <c r="E262" s="6" t="n"/>
+      <c r="F262" s="5" t="n"/>
+      <c r="G262" s="5" t="n"/>
+      <c r="H262" s="6" t="n"/>
+    </row>
+    <row r="263" hidden="1" outlineLevel="2">
+      <c r="A263" s="4" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="B263" s="5" t="n"/>
+      <c r="C263" s="6" t="n"/>
+      <c r="D263" s="6" t="n"/>
+      <c r="E263" s="6" t="n"/>
+      <c r="F263" s="5" t="n"/>
+      <c r="G263" s="5" t="n"/>
+      <c r="H263" s="6" t="n"/>
+    </row>
+    <row r="264" hidden="1" outlineLevel="2">
+      <c r="A264" s="4" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="B264" s="5" t="n"/>
+      <c r="C264" s="6" t="n"/>
+      <c r="D264" s="6" t="n"/>
+      <c r="E264" s="6" t="n"/>
+      <c r="F264" s="5" t="n"/>
+      <c r="G264" s="5" t="n"/>
+      <c r="H264" s="6" t="n"/>
+    </row>
+    <row r="265" hidden="1" outlineLevel="2">
+      <c r="A265" s="4" t="n">
+        <v>65.75</v>
+      </c>
+      <c r="B265" s="5" t="n"/>
+      <c r="C265" s="6" t="n"/>
+      <c r="D265" s="6" t="n"/>
+      <c r="E265" s="6" t="n"/>
+      <c r="F265" s="5" t="n"/>
+      <c r="G265" s="5" t="n"/>
+      <c r="H265" s="6" t="n"/>
+    </row>
+    <row r="266" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A266" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="B266" s="5" t="n"/>
+      <c r="C266" s="6" t="n"/>
+      <c r="D266" s="6" t="n"/>
+      <c r="E266" s="6" t="n"/>
+      <c r="F266" s="5" t="n"/>
+      <c r="G266" s="5" t="n"/>
+      <c r="H266" s="6" t="n"/>
+    </row>
+    <row r="267" hidden="1" outlineLevel="2">
+      <c r="A267" s="4" t="n">
+        <v>66.25</v>
+      </c>
+      <c r="B267" s="5" t="n"/>
+      <c r="C267" s="6" t="n"/>
+      <c r="D267" s="6" t="n"/>
+      <c r="E267" s="6" t="n"/>
+      <c r="F267" s="5" t="n"/>
+      <c r="G267" s="5" t="n"/>
+      <c r="H267" s="6" t="n"/>
+    </row>
+    <row r="268" hidden="1" outlineLevel="2">
+      <c r="A268" s="4" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="B268" s="5" t="n"/>
+      <c r="C268" s="6" t="n"/>
+      <c r="D268" s="6" t="n"/>
+      <c r="E268" s="6" t="n"/>
+      <c r="F268" s="5" t="n"/>
+      <c r="G268" s="5" t="n"/>
+      <c r="H268" s="6" t="n"/>
+    </row>
+    <row r="269" hidden="1" outlineLevel="2">
+      <c r="A269" s="4" t="n">
+        <v>66.75</v>
+      </c>
+      <c r="B269" s="5" t="n"/>
+      <c r="C269" s="6" t="n"/>
+      <c r="D269" s="6" t="n"/>
+      <c r="E269" s="6" t="n"/>
+      <c r="F269" s="5" t="n"/>
+      <c r="G269" s="5" t="n"/>
+      <c r="H269" s="6" t="n"/>
+    </row>
+    <row r="270" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A270" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="B270" s="5" t="n"/>
+      <c r="C270" s="6" t="n"/>
+      <c r="D270" s="6" t="n"/>
+      <c r="E270" s="6" t="n"/>
+      <c r="F270" s="5" t="n"/>
+      <c r="G270" s="5" t="n"/>
+      <c r="H270" s="6" t="n"/>
+    </row>
+    <row r="271" hidden="1" outlineLevel="2">
+      <c r="A271" s="4" t="n">
+        <v>67.25</v>
+      </c>
+      <c r="B271" s="5" t="n"/>
+      <c r="C271" s="6" t="n"/>
+      <c r="D271" s="6" t="n"/>
+      <c r="E271" s="6" t="n"/>
+      <c r="F271" s="5" t="n"/>
+      <c r="G271" s="5" t="n"/>
+      <c r="H271" s="6" t="n"/>
+    </row>
+    <row r="272" hidden="1" outlineLevel="2">
+      <c r="A272" s="4" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="B272" s="5" t="n"/>
+      <c r="C272" s="6" t="n"/>
+      <c r="D272" s="6" t="n"/>
+      <c r="E272" s="6" t="n"/>
+      <c r="F272" s="5" t="n"/>
+      <c r="G272" s="5" t="n"/>
+      <c r="H272" s="6" t="n"/>
+    </row>
+    <row r="273" hidden="1" outlineLevel="2">
+      <c r="A273" s="4" t="n">
+        <v>67.75</v>
+      </c>
+      <c r="B273" s="5" t="n"/>
+      <c r="C273" s="6" t="n"/>
+      <c r="D273" s="6" t="n"/>
+      <c r="E273" s="6" t="n"/>
+      <c r="F273" s="5" t="n"/>
+      <c r="G273" s="5" t="n"/>
+      <c r="H273" s="6" t="n"/>
+    </row>
+    <row r="274" collapsed="1">
+      <c r="A274" s="4" t="n">
         <v>68</v>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B274" s="5" t="inlineStr">
         <is>
           <t>im bulletproof</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>alter Code (handgeschrieben, läuft so in der Firmware):
-progMatrixScanner(15235, 50, 20)</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="C274" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_VERSE, Farben SCHEME_ICE
+Ebene SCENE_SPARKLE (add, 40 %, baut sich 13333 ms auf)
+Schluss (4 Beats): SCENE_BUILDUP, Farben SCHEME_WHITE
+Aufbau zum Chorus: dezenter Puls im Beat in Eisblau, auf der Matrix Sinuswellen, darüber baut sich ein Glitzern auf; im letzten Takt lädt sich alles weiß auf, Explosion auf 'I am titanium'.</t>
+        </is>
+      </c>
+      <c r="D274" s="6" t="n"/>
+      <c r="E274" s="6" t="inlineStr">
         <is>
           <t>wie beim ersten Mal (Verse ICE + Glitzern, Buildup-Tail).</t>
         </is>
       </c>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5">
+      <c r="F274" s="5" t="n"/>
+      <c r="G274" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="H274" s="6" t="inlineStr">
         <is>
           <t>progMatrixScanner(15235, 50, 20)</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
+    <row r="275" hidden="1" outlineLevel="2">
+      <c r="A275" s="4" t="n">
+        <v>68.25</v>
+      </c>
+      <c r="B275" s="5" t="n"/>
+      <c r="C275" s="6" t="n"/>
+      <c r="D275" s="6" t="n"/>
+      <c r="E275" s="6" t="n"/>
+      <c r="F275" s="5" t="n"/>
+      <c r="G275" s="5" t="n"/>
+      <c r="H275" s="6" t="n"/>
+    </row>
+    <row r="276" hidden="1" outlineLevel="2">
+      <c r="A276" s="4" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="B276" s="5" t="n"/>
+      <c r="C276" s="6" t="n"/>
+      <c r="D276" s="6" t="n"/>
+      <c r="E276" s="6" t="n"/>
+      <c r="F276" s="5" t="n"/>
+      <c r="G276" s="5" t="n"/>
+      <c r="H276" s="6" t="n"/>
+    </row>
+    <row r="277" hidden="1" outlineLevel="2">
+      <c r="A277" s="4" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="B277" s="5" t="n"/>
+      <c r="C277" s="6" t="n"/>
+      <c r="D277" s="6" t="n"/>
+      <c r="E277" s="6" t="n"/>
+      <c r="F277" s="5" t="n"/>
+      <c r="G277" s="5" t="n"/>
+      <c r="H277" s="6" t="n"/>
+    </row>
+    <row r="278" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A278" s="4" t="n">
+        <v>69</v>
+      </c>
+      <c r="B278" s="5" t="n"/>
+      <c r="C278" s="6" t="n"/>
+      <c r="D278" s="6" t="n"/>
+      <c r="E278" s="6" t="n"/>
+      <c r="F278" s="5" t="n"/>
+      <c r="G278" s="5" t="n"/>
+      <c r="H278" s="6" t="n"/>
+    </row>
+    <row r="279" hidden="1" outlineLevel="2">
+      <c r="A279" s="4" t="n">
+        <v>69.25</v>
+      </c>
+      <c r="B279" s="5" t="n"/>
+      <c r="C279" s="6" t="n"/>
+      <c r="D279" s="6" t="n"/>
+      <c r="E279" s="6" t="n"/>
+      <c r="F279" s="5" t="n"/>
+      <c r="G279" s="5" t="n"/>
+      <c r="H279" s="6" t="n"/>
+    </row>
+    <row r="280" hidden="1" outlineLevel="2">
+      <c r="A280" s="4" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="B280" s="5" t="n"/>
+      <c r="C280" s="6" t="n"/>
+      <c r="D280" s="6" t="n"/>
+      <c r="E280" s="6" t="n"/>
+      <c r="F280" s="5" t="n"/>
+      <c r="G280" s="5" t="n"/>
+      <c r="H280" s="6" t="n"/>
+    </row>
+    <row r="281" hidden="1" outlineLevel="2">
+      <c r="A281" s="4" t="n">
+        <v>69.75</v>
+      </c>
+      <c r="B281" s="5" t="n"/>
+      <c r="C281" s="6" t="n"/>
+      <c r="D281" s="6" t="n"/>
+      <c r="E281" s="6" t="n"/>
+      <c r="F281" s="5" t="n"/>
+      <c r="G281" s="5" t="n"/>
+      <c r="H281" s="6" t="n"/>
+    </row>
+    <row r="282" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A282" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="B282" s="5" t="n"/>
+      <c r="C282" s="6" t="n"/>
+      <c r="D282" s="6" t="n"/>
+      <c r="E282" s="6" t="n"/>
+      <c r="F282" s="5" t="n"/>
+      <c r="G282" s="5" t="n"/>
+      <c r="H282" s="6" t="n"/>
+    </row>
+    <row r="283" hidden="1" outlineLevel="2">
+      <c r="A283" s="4" t="n">
+        <v>70.25</v>
+      </c>
+      <c r="B283" s="5" t="n"/>
+      <c r="C283" s="6" t="n"/>
+      <c r="D283" s="6" t="n"/>
+      <c r="E283" s="6" t="n"/>
+      <c r="F283" s="5" t="n"/>
+      <c r="G283" s="5" t="n"/>
+      <c r="H283" s="6" t="n"/>
+    </row>
+    <row r="284" hidden="1" outlineLevel="2">
+      <c r="A284" s="4" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="B284" s="5" t="n"/>
+      <c r="C284" s="6" t="n"/>
+      <c r="D284" s="6" t="n"/>
+      <c r="E284" s="6" t="n"/>
+      <c r="F284" s="5" t="n"/>
+      <c r="G284" s="5" t="n"/>
+      <c r="H284" s="6" t="n"/>
+    </row>
+    <row r="285" hidden="1" outlineLevel="2">
+      <c r="A285" s="4" t="n">
+        <v>70.75</v>
+      </c>
+      <c r="B285" s="5" t="n"/>
+      <c r="C285" s="6" t="n"/>
+      <c r="D285" s="6" t="n"/>
+      <c r="E285" s="6" t="n"/>
+      <c r="F285" s="5" t="n"/>
+      <c r="G285" s="5" t="n"/>
+      <c r="H285" s="6" t="n"/>
+    </row>
+    <row r="286" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A286" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="B286" s="5" t="n"/>
+      <c r="C286" s="6" t="n"/>
+      <c r="D286" s="6" t="n"/>
+      <c r="E286" s="6" t="n"/>
+      <c r="F286" s="5" t="n"/>
+      <c r="G286" s="5" t="n"/>
+      <c r="H286" s="6" t="n"/>
+    </row>
+    <row r="287" hidden="1" outlineLevel="2">
+      <c r="A287" s="4" t="n">
+        <v>71.25</v>
+      </c>
+      <c r="B287" s="5" t="n"/>
+      <c r="C287" s="6" t="n"/>
+      <c r="D287" s="6" t="n"/>
+      <c r="E287" s="6" t="n"/>
+      <c r="F287" s="5" t="n"/>
+      <c r="G287" s="5" t="n"/>
+      <c r="H287" s="6" t="n"/>
+    </row>
+    <row r="288" hidden="1" outlineLevel="2">
+      <c r="A288" s="4" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="B288" s="5" t="n"/>
+      <c r="C288" s="6" t="n"/>
+      <c r="D288" s="6" t="n"/>
+      <c r="E288" s="6" t="n"/>
+      <c r="F288" s="5" t="n"/>
+      <c r="G288" s="5" t="n"/>
+      <c r="H288" s="6" t="n"/>
+    </row>
+    <row r="289" hidden="1" outlineLevel="2">
+      <c r="A289" s="4" t="n">
+        <v>71.75</v>
+      </c>
+      <c r="B289" s="5" t="n"/>
+      <c r="C289" s="6" t="n"/>
+      <c r="D289" s="6" t="n"/>
+      <c r="E289" s="6" t="n"/>
+      <c r="F289" s="5" t="n"/>
+      <c r="G289" s="5" t="n"/>
+      <c r="H289" s="6" t="n"/>
+    </row>
+    <row r="290" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A290" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="B290" s="5" t="n"/>
+      <c r="C290" s="6" t="n"/>
+      <c r="D290" s="6" t="n"/>
+      <c r="E290" s="6" t="n"/>
+      <c r="F290" s="5" t="n"/>
+      <c r="G290" s="5" t="n"/>
+      <c r="H290" s="6" t="n"/>
+    </row>
+    <row r="291" hidden="1" outlineLevel="2">
+      <c r="A291" s="4" t="n">
+        <v>72.25</v>
+      </c>
+      <c r="B291" s="5" t="n"/>
+      <c r="C291" s="6" t="n"/>
+      <c r="D291" s="6" t="n"/>
+      <c r="E291" s="6" t="n"/>
+      <c r="F291" s="5" t="n"/>
+      <c r="G291" s="5" t="n"/>
+      <c r="H291" s="6" t="n"/>
+    </row>
+    <row r="292" hidden="1" outlineLevel="2">
+      <c r="A292" s="4" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="B292" s="5" t="n"/>
+      <c r="C292" s="6" t="n"/>
+      <c r="D292" s="6" t="n"/>
+      <c r="E292" s="6" t="n"/>
+      <c r="F292" s="5" t="n"/>
+      <c r="G292" s="5" t="n"/>
+      <c r="H292" s="6" t="n"/>
+    </row>
+    <row r="293" hidden="1" outlineLevel="2">
+      <c r="A293" s="4" t="n">
+        <v>72.75</v>
+      </c>
+      <c r="B293" s="5" t="n"/>
+      <c r="C293" s="6" t="n"/>
+      <c r="D293" s="6" t="n"/>
+      <c r="E293" s="6" t="n"/>
+      <c r="F293" s="5" t="n"/>
+      <c r="G293" s="5" t="n"/>
+      <c r="H293" s="6" t="n"/>
+    </row>
+    <row r="294" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A294" s="4" t="n">
+        <v>73</v>
+      </c>
+      <c r="B294" s="5" t="n"/>
+      <c r="C294" s="6" t="n"/>
+      <c r="D294" s="6" t="n"/>
+      <c r="E294" s="6" t="n"/>
+      <c r="F294" s="5" t="n"/>
+      <c r="G294" s="5" t="n"/>
+      <c r="H294" s="6" t="n"/>
+    </row>
+    <row r="295" hidden="1" outlineLevel="2">
+      <c r="A295" s="4" t="n">
+        <v>73.25</v>
+      </c>
+      <c r="B295" s="5" t="n"/>
+      <c r="C295" s="6" t="n"/>
+      <c r="D295" s="6" t="n"/>
+      <c r="E295" s="6" t="n"/>
+      <c r="F295" s="5" t="n"/>
+      <c r="G295" s="5" t="n"/>
+      <c r="H295" s="6" t="n"/>
+    </row>
+    <row r="296" hidden="1" outlineLevel="2">
+      <c r="A296" s="4" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="B296" s="5" t="n"/>
+      <c r="C296" s="6" t="n"/>
+      <c r="D296" s="6" t="n"/>
+      <c r="E296" s="6" t="n"/>
+      <c r="F296" s="5" t="n"/>
+      <c r="G296" s="5" t="n"/>
+      <c r="H296" s="6" t="n"/>
+    </row>
+    <row r="297" hidden="1" outlineLevel="2">
+      <c r="A297" s="4" t="n">
+        <v>73.75</v>
+      </c>
+      <c r="B297" s="5" t="n"/>
+      <c r="C297" s="6" t="n"/>
+      <c r="D297" s="6" t="n"/>
+      <c r="E297" s="6" t="n"/>
+      <c r="F297" s="5" t="n"/>
+      <c r="G297" s="5" t="n"/>
+      <c r="H297" s="6" t="n"/>
+    </row>
+    <row r="298" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A298" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="B298" s="5" t="n"/>
+      <c r="C298" s="6" t="n"/>
+      <c r="D298" s="6" t="n"/>
+      <c r="E298" s="6" t="n"/>
+      <c r="F298" s="5" t="n"/>
+      <c r="G298" s="5" t="n"/>
+      <c r="H298" s="6" t="n"/>
+    </row>
+    <row r="299" hidden="1" outlineLevel="2">
+      <c r="A299" s="4" t="n">
+        <v>74.25</v>
+      </c>
+      <c r="B299" s="5" t="n"/>
+      <c r="C299" s="6" t="n"/>
+      <c r="D299" s="6" t="n"/>
+      <c r="E299" s="6" t="n"/>
+      <c r="F299" s="5" t="n"/>
+      <c r="G299" s="5" t="n"/>
+      <c r="H299" s="6" t="n"/>
+    </row>
+    <row r="300" hidden="1" outlineLevel="2">
+      <c r="A300" s="4" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="B300" s="5" t="n"/>
+      <c r="C300" s="6" t="n"/>
+      <c r="D300" s="6" t="n"/>
+      <c r="E300" s="6" t="n"/>
+      <c r="F300" s="5" t="n"/>
+      <c r="G300" s="5" t="n"/>
+      <c r="H300" s="6" t="n"/>
+    </row>
+    <row r="301" hidden="1" outlineLevel="2">
+      <c r="A301" s="4" t="n">
+        <v>74.75</v>
+      </c>
+      <c r="B301" s="5" t="n"/>
+      <c r="C301" s="6" t="n"/>
+      <c r="D301" s="6" t="n"/>
+      <c r="E301" s="6" t="n"/>
+      <c r="F301" s="5" t="n"/>
+      <c r="G301" s="5" t="n"/>
+      <c r="H301" s="6" t="n"/>
+    </row>
+    <row r="302" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A302" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="B302" s="5" t="n"/>
+      <c r="C302" s="6" t="n"/>
+      <c r="D302" s="6" t="n"/>
+      <c r="E302" s="6" t="n"/>
+      <c r="F302" s="5" t="n"/>
+      <c r="G302" s="5" t="n"/>
+      <c r="H302" s="6" t="n"/>
+    </row>
+    <row r="303" hidden="1" outlineLevel="2">
+      <c r="A303" s="4" t="n">
+        <v>75.25</v>
+      </c>
+      <c r="B303" s="5" t="n"/>
+      <c r="C303" s="6" t="n"/>
+      <c r="D303" s="6" t="n"/>
+      <c r="E303" s="6" t="n"/>
+      <c r="F303" s="5" t="n"/>
+      <c r="G303" s="5" t="n"/>
+      <c r="H303" s="6" t="n"/>
+    </row>
+    <row r="304" hidden="1" outlineLevel="2">
+      <c r="A304" s="4" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="B304" s="5" t="n"/>
+      <c r="C304" s="6" t="n"/>
+      <c r="D304" s="6" t="n"/>
+      <c r="E304" s="6" t="n"/>
+      <c r="F304" s="5" t="n"/>
+      <c r="G304" s="5" t="n"/>
+      <c r="H304" s="6" t="n"/>
+    </row>
+    <row r="305" hidden="1" outlineLevel="2">
+      <c r="A305" s="4" t="n">
+        <v>75.75</v>
+      </c>
+      <c r="B305" s="5" t="n"/>
+      <c r="C305" s="6" t="n"/>
+      <c r="D305" s="6" t="n"/>
+      <c r="E305" s="6" t="n"/>
+      <c r="F305" s="5" t="n"/>
+      <c r="G305" s="5" t="n"/>
+      <c r="H305" s="6" t="n"/>
+    </row>
+    <row r="306" collapsed="1">
+      <c r="A306" s="4" t="n">
         <v>76</v>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B306" s="5" t="inlineStr">
         <is>
           <t>chorus 2</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>alter Code (handgeschrieben, läuft so in der Firmware):
-progFullColors(15240, 55, 475)</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="C306" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_COLORS, Farben SCHEME_WHITE, Farbwanderung to SCHEME_ICE, per 8
+Text (Matrix): "TITANIUM": steht durchgehend, ohne Pulsieren (über der Szene)
+   ab 0 ms bis 3810 ms, klingt 952 ms ab, darunter 15 %
+Ausgabe: Farbwechsel weich (30 % des Schritts), Blinder bei 0 ms, 952 ms lang, Blinder alle 2 Beat(s), 238 ms, nur LAMPE1, LAMPE2, Blinder liegt unter dem Text
+Wie chorus 1 (eine Farbe pro Beat, Weiß nach Eisblau, Blinder auf den Einsatz, TITANIUM auf der Matrix); dazu blitzen die Lampen weiß auf 2 und 4.</t>
+        </is>
+      </c>
+      <c r="D306" s="6" t="n"/>
+      <c r="E306" s="6" t="inlineStr">
         <is>
           <t>wie chorus 1 (Colors WHITE/ICE, Text TITANIUM), dazu blitzen die Lampen weiß auf 2 und 4.</t>
         </is>
       </c>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5">
+      <c r="F306" s="5" t="n"/>
+      <c r="G306" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H306" s="6" t="inlineStr">
         <is>
           <t>progFullColors(15240, 55, 475)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="n">
+    <row r="307" hidden="1" outlineLevel="2">
+      <c r="A307" s="4" t="n">
+        <v>76.25</v>
+      </c>
+      <c r="B307" s="5" t="n"/>
+      <c r="C307" s="6" t="n"/>
+      <c r="D307" s="6" t="n"/>
+      <c r="E307" s="6" t="n"/>
+      <c r="F307" s="5" t="n"/>
+      <c r="G307" s="5" t="n"/>
+      <c r="H307" s="6" t="n"/>
+    </row>
+    <row r="308" hidden="1" outlineLevel="2">
+      <c r="A308" s="4" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="B308" s="5" t="n"/>
+      <c r="C308" s="6" t="n"/>
+      <c r="D308" s="6" t="n"/>
+      <c r="E308" s="6" t="n"/>
+      <c r="F308" s="5" t="n"/>
+      <c r="G308" s="5" t="n"/>
+      <c r="H308" s="6" t="n"/>
+    </row>
+    <row r="309" hidden="1" outlineLevel="2">
+      <c r="A309" s="4" t="n">
+        <v>76.75</v>
+      </c>
+      <c r="B309" s="5" t="n"/>
+      <c r="C309" s="6" t="n"/>
+      <c r="D309" s="6" t="n"/>
+      <c r="E309" s="6" t="n"/>
+      <c r="F309" s="5" t="n"/>
+      <c r="G309" s="5" t="n"/>
+      <c r="H309" s="6" t="n"/>
+    </row>
+    <row r="310" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A310" s="4" t="n">
+        <v>77</v>
+      </c>
+      <c r="B310" s="5" t="n"/>
+      <c r="C310" s="6" t="n"/>
+      <c r="D310" s="6" t="n"/>
+      <c r="E310" s="6" t="n"/>
+      <c r="F310" s="5" t="n"/>
+      <c r="G310" s="5" t="n"/>
+      <c r="H310" s="6" t="n"/>
+    </row>
+    <row r="311" hidden="1" outlineLevel="2">
+      <c r="A311" s="4" t="n">
+        <v>77.25</v>
+      </c>
+      <c r="B311" s="5" t="n"/>
+      <c r="C311" s="6" t="n"/>
+      <c r="D311" s="6" t="n"/>
+      <c r="E311" s="6" t="n"/>
+      <c r="F311" s="5" t="n"/>
+      <c r="G311" s="5" t="n"/>
+      <c r="H311" s="6" t="n"/>
+    </row>
+    <row r="312" hidden="1" outlineLevel="2">
+      <c r="A312" s="4" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="B312" s="5" t="n"/>
+      <c r="C312" s="6" t="n"/>
+      <c r="D312" s="6" t="n"/>
+      <c r="E312" s="6" t="n"/>
+      <c r="F312" s="5" t="n"/>
+      <c r="G312" s="5" t="n"/>
+      <c r="H312" s="6" t="n"/>
+    </row>
+    <row r="313" hidden="1" outlineLevel="2">
+      <c r="A313" s="4" t="n">
+        <v>77.75</v>
+      </c>
+      <c r="B313" s="5" t="n"/>
+      <c r="C313" s="6" t="n"/>
+      <c r="D313" s="6" t="n"/>
+      <c r="E313" s="6" t="n"/>
+      <c r="F313" s="5" t="n"/>
+      <c r="G313" s="5" t="n"/>
+      <c r="H313" s="6" t="n"/>
+    </row>
+    <row r="314" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A314" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="B314" s="5" t="n"/>
+      <c r="C314" s="6" t="n"/>
+      <c r="D314" s="6" t="n"/>
+      <c r="E314" s="6" t="n"/>
+      <c r="F314" s="5" t="n"/>
+      <c r="G314" s="5" t="n"/>
+      <c r="H314" s="6" t="n"/>
+    </row>
+    <row r="315" hidden="1" outlineLevel="2">
+      <c r="A315" s="4" t="n">
+        <v>78.25</v>
+      </c>
+      <c r="B315" s="5" t="n"/>
+      <c r="C315" s="6" t="n"/>
+      <c r="D315" s="6" t="n"/>
+      <c r="E315" s="6" t="n"/>
+      <c r="F315" s="5" t="n"/>
+      <c r="G315" s="5" t="n"/>
+      <c r="H315" s="6" t="n"/>
+    </row>
+    <row r="316" hidden="1" outlineLevel="2">
+      <c r="A316" s="4" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="B316" s="5" t="n"/>
+      <c r="C316" s="6" t="n"/>
+      <c r="D316" s="6" t="n"/>
+      <c r="E316" s="6" t="n"/>
+      <c r="F316" s="5" t="n"/>
+      <c r="G316" s="5" t="n"/>
+      <c r="H316" s="6" t="n"/>
+    </row>
+    <row r="317" hidden="1" outlineLevel="2">
+      <c r="A317" s="4" t="n">
+        <v>78.75</v>
+      </c>
+      <c r="B317" s="5" t="n"/>
+      <c r="C317" s="6" t="n"/>
+      <c r="D317" s="6" t="n"/>
+      <c r="E317" s="6" t="n"/>
+      <c r="F317" s="5" t="n"/>
+      <c r="G317" s="5" t="n"/>
+      <c r="H317" s="6" t="n"/>
+    </row>
+    <row r="318" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A318" s="4" t="n">
+        <v>79</v>
+      </c>
+      <c r="B318" s="5" t="n"/>
+      <c r="C318" s="6" t="n"/>
+      <c r="D318" s="6" t="n"/>
+      <c r="E318" s="6" t="n"/>
+      <c r="F318" s="5" t="n"/>
+      <c r="G318" s="5" t="n"/>
+      <c r="H318" s="6" t="n"/>
+    </row>
+    <row r="319" hidden="1" outlineLevel="2">
+      <c r="A319" s="4" t="n">
+        <v>79.25</v>
+      </c>
+      <c r="B319" s="5" t="n"/>
+      <c r="C319" s="6" t="n"/>
+      <c r="D319" s="6" t="n"/>
+      <c r="E319" s="6" t="n"/>
+      <c r="F319" s="5" t="n"/>
+      <c r="G319" s="5" t="n"/>
+      <c r="H319" s="6" t="n"/>
+    </row>
+    <row r="320" hidden="1" outlineLevel="2">
+      <c r="A320" s="4" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="B320" s="5" t="n"/>
+      <c r="C320" s="6" t="n"/>
+      <c r="D320" s="6" t="n"/>
+      <c r="E320" s="6" t="n"/>
+      <c r="F320" s="5" t="n"/>
+      <c r="G320" s="5" t="n"/>
+      <c r="H320" s="6" t="n"/>
+    </row>
+    <row r="321" hidden="1" outlineLevel="2">
+      <c r="A321" s="4" t="n">
+        <v>79.75</v>
+      </c>
+      <c r="B321" s="5" t="n"/>
+      <c r="C321" s="6" t="n"/>
+      <c r="D321" s="6" t="n"/>
+      <c r="E321" s="6" t="n"/>
+      <c r="F321" s="5" t="n"/>
+      <c r="G321" s="5" t="n"/>
+      <c r="H321" s="6" t="n"/>
+    </row>
+    <row r="322" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A322" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="B322" s="5" t="n"/>
+      <c r="C322" s="6" t="n"/>
+      <c r="D322" s="6" t="n"/>
+      <c r="E322" s="6" t="n"/>
+      <c r="F322" s="5" t="n"/>
+      <c r="G322" s="5" t="n"/>
+      <c r="H322" s="6" t="n"/>
+    </row>
+    <row r="323" hidden="1" outlineLevel="2">
+      <c r="A323" s="4" t="n">
+        <v>80.25</v>
+      </c>
+      <c r="B323" s="5" t="n"/>
+      <c r="C323" s="6" t="n"/>
+      <c r="D323" s="6" t="n"/>
+      <c r="E323" s="6" t="n"/>
+      <c r="F323" s="5" t="n"/>
+      <c r="G323" s="5" t="n"/>
+      <c r="H323" s="6" t="n"/>
+    </row>
+    <row r="324" hidden="1" outlineLevel="2">
+      <c r="A324" s="4" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="B324" s="5" t="n"/>
+      <c r="C324" s="6" t="n"/>
+      <c r="D324" s="6" t="n"/>
+      <c r="E324" s="6" t="n"/>
+      <c r="F324" s="5" t="n"/>
+      <c r="G324" s="5" t="n"/>
+      <c r="H324" s="6" t="n"/>
+    </row>
+    <row r="325" hidden="1" outlineLevel="2">
+      <c r="A325" s="4" t="n">
+        <v>80.75</v>
+      </c>
+      <c r="B325" s="5" t="n"/>
+      <c r="C325" s="6" t="n"/>
+      <c r="D325" s="6" t="n"/>
+      <c r="E325" s="6" t="n"/>
+      <c r="F325" s="5" t="n"/>
+      <c r="G325" s="5" t="n"/>
+      <c r="H325" s="6" t="n"/>
+    </row>
+    <row r="326" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A326" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="B326" s="5" t="n"/>
+      <c r="C326" s="6" t="n"/>
+      <c r="D326" s="6" t="n"/>
+      <c r="E326" s="6" t="n"/>
+      <c r="F326" s="5" t="n"/>
+      <c r="G326" s="5" t="n"/>
+      <c r="H326" s="6" t="n"/>
+    </row>
+    <row r="327" hidden="1" outlineLevel="2">
+      <c r="A327" s="4" t="n">
+        <v>81.25</v>
+      </c>
+      <c r="B327" s="5" t="n"/>
+      <c r="C327" s="6" t="n"/>
+      <c r="D327" s="6" t="n"/>
+      <c r="E327" s="6" t="n"/>
+      <c r="F327" s="5" t="n"/>
+      <c r="G327" s="5" t="n"/>
+      <c r="H327" s="6" t="n"/>
+    </row>
+    <row r="328" hidden="1" outlineLevel="2">
+      <c r="A328" s="4" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="B328" s="5" t="n"/>
+      <c r="C328" s="6" t="n"/>
+      <c r="D328" s="6" t="n"/>
+      <c r="E328" s="6" t="n"/>
+      <c r="F328" s="5" t="n"/>
+      <c r="G328" s="5" t="n"/>
+      <c r="H328" s="6" t="n"/>
+    </row>
+    <row r="329" hidden="1" outlineLevel="2">
+      <c r="A329" s="4" t="n">
+        <v>81.75</v>
+      </c>
+      <c r="B329" s="5" t="n"/>
+      <c r="C329" s="6" t="n"/>
+      <c r="D329" s="6" t="n"/>
+      <c r="E329" s="6" t="n"/>
+      <c r="F329" s="5" t="n"/>
+      <c r="G329" s="5" t="n"/>
+      <c r="H329" s="6" t="n"/>
+    </row>
+    <row r="330" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A330" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="B330" s="5" t="n"/>
+      <c r="C330" s="6" t="n"/>
+      <c r="D330" s="6" t="n"/>
+      <c r="E330" s="6" t="n"/>
+      <c r="F330" s="5" t="n"/>
+      <c r="G330" s="5" t="n"/>
+      <c r="H330" s="6" t="n"/>
+    </row>
+    <row r="331" hidden="1" outlineLevel="2">
+      <c r="A331" s="4" t="n">
+        <v>82.25</v>
+      </c>
+      <c r="B331" s="5" t="n"/>
+      <c r="C331" s="6" t="n"/>
+      <c r="D331" s="6" t="n"/>
+      <c r="E331" s="6" t="n"/>
+      <c r="F331" s="5" t="n"/>
+      <c r="G331" s="5" t="n"/>
+      <c r="H331" s="6" t="n"/>
+    </row>
+    <row r="332" hidden="1" outlineLevel="2">
+      <c r="A332" s="4" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="B332" s="5" t="n"/>
+      <c r="C332" s="6" t="n"/>
+      <c r="D332" s="6" t="n"/>
+      <c r="E332" s="6" t="n"/>
+      <c r="F332" s="5" t="n"/>
+      <c r="G332" s="5" t="n"/>
+      <c r="H332" s="6" t="n"/>
+    </row>
+    <row r="333" hidden="1" outlineLevel="2">
+      <c r="A333" s="4" t="n">
+        <v>82.75</v>
+      </c>
+      <c r="B333" s="5" t="n"/>
+      <c r="C333" s="6" t="n"/>
+      <c r="D333" s="6" t="n"/>
+      <c r="E333" s="6" t="n"/>
+      <c r="F333" s="5" t="n"/>
+      <c r="G333" s="5" t="n"/>
+      <c r="H333" s="6" t="n"/>
+    </row>
+    <row r="334" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A334" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="B334" s="5" t="n"/>
+      <c r="C334" s="6" t="n"/>
+      <c r="D334" s="6" t="n"/>
+      <c r="E334" s="6" t="n"/>
+      <c r="F334" s="5" t="n"/>
+      <c r="G334" s="5" t="n"/>
+      <c r="H334" s="6" t="n"/>
+    </row>
+    <row r="335" hidden="1" outlineLevel="2">
+      <c r="A335" s="4" t="n">
+        <v>83.25</v>
+      </c>
+      <c r="B335" s="5" t="n"/>
+      <c r="C335" s="6" t="n"/>
+      <c r="D335" s="6" t="n"/>
+      <c r="E335" s="6" t="n"/>
+      <c r="F335" s="5" t="n"/>
+      <c r="G335" s="5" t="n"/>
+      <c r="H335" s="6" t="n"/>
+    </row>
+    <row r="336" hidden="1" outlineLevel="2">
+      <c r="A336" s="4" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="B336" s="5" t="n"/>
+      <c r="C336" s="6" t="n"/>
+      <c r="D336" s="6" t="n"/>
+      <c r="E336" s="6" t="n"/>
+      <c r="F336" s="5" t="n"/>
+      <c r="G336" s="5" t="n"/>
+      <c r="H336" s="6" t="n"/>
+    </row>
+    <row r="337" hidden="1" outlineLevel="2">
+      <c r="A337" s="4" t="n">
+        <v>83.75</v>
+      </c>
+      <c r="B337" s="5" t="n"/>
+      <c r="C337" s="6" t="n"/>
+      <c r="D337" s="6" t="n"/>
+      <c r="E337" s="6" t="n"/>
+      <c r="F337" s="5" t="n"/>
+      <c r="G337" s="5" t="n"/>
+      <c r="H337" s="6" t="n"/>
+    </row>
+    <row r="338" collapsed="1">
+      <c r="A338" s="4" t="n">
         <v>84</v>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B338" s="5" t="inlineStr">
         <is>
           <t>bridge</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>alter Code (handgeschrieben, läuft so in der Firmware):
-progFastBlingBling(14760, 8, 60)</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="C338" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_DROP, Farben SCHEME_NEON
+Ausgabe: Übergang flash 476 ms, Blinder bei Takt 91,5 = 14286 ms, 476 ms lang, Blinder blendet 0 ms ein, 119 ms voll, 357 ms aus
+Der Drop wie beim ersten Mal: weißer Blitz auf den Einsatz, Schockwellen und Blitze in Pink, Cyan und Violett; starker Blinder auf der letzten Viertel (Takt 91,5), danach Schwarz.</t>
+        </is>
+      </c>
+      <c r="D338" s="6" t="n"/>
+      <c r="E338" s="6" t="inlineStr">
         <is>
           <t>Drop wie beim ersten Mal (Szene Drop, NEON); starker Blinder auf der letzten Viertel (Takt 91,5), danach Schwarz.</t>
         </is>
       </c>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5">
+      <c r="F338" s="5" t="n"/>
+      <c r="G338" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H18" s="6" t="inlineStr">
+      <c r="H338" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(14760, 8, 60)</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="n">
+    <row r="339" hidden="1" outlineLevel="2">
+      <c r="A339" s="4" t="n">
+        <v>84.25</v>
+      </c>
+      <c r="B339" s="5" t="n"/>
+      <c r="C339" s="6" t="n"/>
+      <c r="D339" s="6" t="n"/>
+      <c r="E339" s="6" t="n"/>
+      <c r="F339" s="5" t="n"/>
+      <c r="G339" s="5" t="n"/>
+      <c r="H339" s="6" t="n"/>
+    </row>
+    <row r="340" hidden="1" outlineLevel="2">
+      <c r="A340" s="4" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="B340" s="5" t="n"/>
+      <c r="C340" s="6" t="n"/>
+      <c r="D340" s="6" t="n"/>
+      <c r="E340" s="6" t="n"/>
+      <c r="F340" s="5" t="n"/>
+      <c r="G340" s="5" t="n"/>
+      <c r="H340" s="6" t="n"/>
+    </row>
+    <row r="341" hidden="1" outlineLevel="2">
+      <c r="A341" s="4" t="n">
+        <v>84.75</v>
+      </c>
+      <c r="B341" s="5" t="n"/>
+      <c r="C341" s="6" t="n"/>
+      <c r="D341" s="6" t="n"/>
+      <c r="E341" s="6" t="n"/>
+      <c r="F341" s="5" t="n"/>
+      <c r="G341" s="5" t="n"/>
+      <c r="H341" s="6" t="n"/>
+    </row>
+    <row r="342" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A342" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="B342" s="5" t="n"/>
+      <c r="C342" s="6" t="n"/>
+      <c r="D342" s="6" t="n"/>
+      <c r="E342" s="6" t="n"/>
+      <c r="F342" s="5" t="n"/>
+      <c r="G342" s="5" t="n"/>
+      <c r="H342" s="6" t="n"/>
+    </row>
+    <row r="343" hidden="1" outlineLevel="2">
+      <c r="A343" s="4" t="n">
+        <v>85.25</v>
+      </c>
+      <c r="B343" s="5" t="n"/>
+      <c r="C343" s="6" t="n"/>
+      <c r="D343" s="6" t="n"/>
+      <c r="E343" s="6" t="n"/>
+      <c r="F343" s="5" t="n"/>
+      <c r="G343" s="5" t="n"/>
+      <c r="H343" s="6" t="n"/>
+    </row>
+    <row r="344" hidden="1" outlineLevel="2">
+      <c r="A344" s="4" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="B344" s="5" t="n"/>
+      <c r="C344" s="6" t="n"/>
+      <c r="D344" s="6" t="n"/>
+      <c r="E344" s="6" t="n"/>
+      <c r="F344" s="5" t="n"/>
+      <c r="G344" s="5" t="n"/>
+      <c r="H344" s="6" t="n"/>
+    </row>
+    <row r="345" hidden="1" outlineLevel="2">
+      <c r="A345" s="4" t="n">
+        <v>85.75</v>
+      </c>
+      <c r="B345" s="5" t="n"/>
+      <c r="C345" s="6" t="n"/>
+      <c r="D345" s="6" t="n"/>
+      <c r="E345" s="6" t="n"/>
+      <c r="F345" s="5" t="n"/>
+      <c r="G345" s="5" t="n"/>
+      <c r="H345" s="6" t="n"/>
+    </row>
+    <row r="346" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A346" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="B346" s="5" t="n"/>
+      <c r="C346" s="6" t="n"/>
+      <c r="D346" s="6" t="n"/>
+      <c r="E346" s="6" t="n"/>
+      <c r="F346" s="5" t="n"/>
+      <c r="G346" s="5" t="n"/>
+      <c r="H346" s="6" t="n"/>
+    </row>
+    <row r="347" hidden="1" outlineLevel="2">
+      <c r="A347" s="4" t="n">
+        <v>86.25</v>
+      </c>
+      <c r="B347" s="5" t="n"/>
+      <c r="C347" s="6" t="n"/>
+      <c r="D347" s="6" t="n"/>
+      <c r="E347" s="6" t="n"/>
+      <c r="F347" s="5" t="n"/>
+      <c r="G347" s="5" t="n"/>
+      <c r="H347" s="6" t="n"/>
+    </row>
+    <row r="348" hidden="1" outlineLevel="2">
+      <c r="A348" s="4" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="B348" s="5" t="n"/>
+      <c r="C348" s="6" t="n"/>
+      <c r="D348" s="6" t="n"/>
+      <c r="E348" s="6" t="n"/>
+      <c r="F348" s="5" t="n"/>
+      <c r="G348" s="5" t="n"/>
+      <c r="H348" s="6" t="n"/>
+    </row>
+    <row r="349" hidden="1" outlineLevel="2">
+      <c r="A349" s="4" t="n">
+        <v>86.75</v>
+      </c>
+      <c r="B349" s="5" t="n"/>
+      <c r="C349" s="6" t="n"/>
+      <c r="D349" s="6" t="n"/>
+      <c r="E349" s="6" t="n"/>
+      <c r="F349" s="5" t="n"/>
+      <c r="G349" s="5" t="n"/>
+      <c r="H349" s="6" t="n"/>
+    </row>
+    <row r="350" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A350" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="B350" s="5" t="n"/>
+      <c r="C350" s="6" t="n"/>
+      <c r="D350" s="6" t="n"/>
+      <c r="E350" s="6" t="n"/>
+      <c r="F350" s="5" t="n"/>
+      <c r="G350" s="5" t="n"/>
+      <c r="H350" s="6" t="n"/>
+    </row>
+    <row r="351" hidden="1" outlineLevel="2">
+      <c r="A351" s="4" t="n">
+        <v>87.25</v>
+      </c>
+      <c r="B351" s="5" t="n"/>
+      <c r="C351" s="6" t="n"/>
+      <c r="D351" s="6" t="n"/>
+      <c r="E351" s="6" t="n"/>
+      <c r="F351" s="5" t="n"/>
+      <c r="G351" s="5" t="n"/>
+      <c r="H351" s="6" t="n"/>
+    </row>
+    <row r="352" hidden="1" outlineLevel="2">
+      <c r="A352" s="4" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="B352" s="5" t="n"/>
+      <c r="C352" s="6" t="n"/>
+      <c r="D352" s="6" t="n"/>
+      <c r="E352" s="6" t="n"/>
+      <c r="F352" s="5" t="n"/>
+      <c r="G352" s="5" t="n"/>
+      <c r="H352" s="6" t="n"/>
+    </row>
+    <row r="353" hidden="1" outlineLevel="2">
+      <c r="A353" s="4" t="n">
+        <v>87.75</v>
+      </c>
+      <c r="B353" s="5" t="n"/>
+      <c r="C353" s="6" t="n"/>
+      <c r="D353" s="6" t="n"/>
+      <c r="E353" s="6" t="n"/>
+      <c r="F353" s="5" t="n"/>
+      <c r="G353" s="5" t="n"/>
+      <c r="H353" s="6" t="n"/>
+    </row>
+    <row r="354" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A354" s="4" t="n">
+        <v>88</v>
+      </c>
+      <c r="B354" s="5" t="n"/>
+      <c r="C354" s="6" t="n"/>
+      <c r="D354" s="6" t="n"/>
+      <c r="E354" s="6" t="n"/>
+      <c r="F354" s="5" t="n"/>
+      <c r="G354" s="5" t="n"/>
+      <c r="H354" s="6" t="n"/>
+    </row>
+    <row r="355" hidden="1" outlineLevel="2">
+      <c r="A355" s="4" t="n">
+        <v>88.25</v>
+      </c>
+      <c r="B355" s="5" t="n"/>
+      <c r="C355" s="6" t="n"/>
+      <c r="D355" s="6" t="n"/>
+      <c r="E355" s="6" t="n"/>
+      <c r="F355" s="5" t="n"/>
+      <c r="G355" s="5" t="n"/>
+      <c r="H355" s="6" t="n"/>
+    </row>
+    <row r="356" hidden="1" outlineLevel="2">
+      <c r="A356" s="4" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="B356" s="5" t="n"/>
+      <c r="C356" s="6" t="n"/>
+      <c r="D356" s="6" t="n"/>
+      <c r="E356" s="6" t="n"/>
+      <c r="F356" s="5" t="n"/>
+      <c r="G356" s="5" t="n"/>
+      <c r="H356" s="6" t="n"/>
+    </row>
+    <row r="357" hidden="1" outlineLevel="2">
+      <c r="A357" s="4" t="n">
+        <v>88.75</v>
+      </c>
+      <c r="B357" s="5" t="n"/>
+      <c r="C357" s="6" t="n"/>
+      <c r="D357" s="6" t="n"/>
+      <c r="E357" s="6" t="n"/>
+      <c r="F357" s="5" t="n"/>
+      <c r="G357" s="5" t="n"/>
+      <c r="H357" s="6" t="n"/>
+    </row>
+    <row r="358" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A358" s="4" t="n">
+        <v>89</v>
+      </c>
+      <c r="B358" s="5" t="n"/>
+      <c r="C358" s="6" t="n"/>
+      <c r="D358" s="6" t="n"/>
+      <c r="E358" s="6" t="n"/>
+      <c r="F358" s="5" t="n"/>
+      <c r="G358" s="5" t="n"/>
+      <c r="H358" s="6" t="n"/>
+    </row>
+    <row r="359" hidden="1" outlineLevel="2">
+      <c r="A359" s="4" t="n">
+        <v>89.25</v>
+      </c>
+      <c r="B359" s="5" t="n"/>
+      <c r="C359" s="6" t="n"/>
+      <c r="D359" s="6" t="n"/>
+      <c r="E359" s="6" t="n"/>
+      <c r="F359" s="5" t="n"/>
+      <c r="G359" s="5" t="n"/>
+      <c r="H359" s="6" t="n"/>
+    </row>
+    <row r="360" hidden="1" outlineLevel="2">
+      <c r="A360" s="4" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="B360" s="5" t="n"/>
+      <c r="C360" s="6" t="n"/>
+      <c r="D360" s="6" t="n"/>
+      <c r="E360" s="6" t="n"/>
+      <c r="F360" s="5" t="n"/>
+      <c r="G360" s="5" t="n"/>
+      <c r="H360" s="6" t="n"/>
+    </row>
+    <row r="361" hidden="1" outlineLevel="2">
+      <c r="A361" s="4" t="n">
+        <v>89.75</v>
+      </c>
+      <c r="B361" s="5" t="n"/>
+      <c r="C361" s="6" t="n"/>
+      <c r="D361" s="6" t="n"/>
+      <c r="E361" s="6" t="n"/>
+      <c r="F361" s="5" t="n"/>
+      <c r="G361" s="5" t="n"/>
+      <c r="H361" s="6" t="n"/>
+    </row>
+    <row r="362" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A362" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="B362" s="5" t="n"/>
+      <c r="C362" s="6" t="n"/>
+      <c r="D362" s="6" t="n"/>
+      <c r="E362" s="6" t="n"/>
+      <c r="F362" s="5" t="n"/>
+      <c r="G362" s="5" t="n"/>
+      <c r="H362" s="6" t="n"/>
+    </row>
+    <row r="363" hidden="1" outlineLevel="2">
+      <c r="A363" s="4" t="n">
+        <v>90.25</v>
+      </c>
+      <c r="B363" s="5" t="n"/>
+      <c r="C363" s="6" t="n"/>
+      <c r="D363" s="6" t="n"/>
+      <c r="E363" s="6" t="n"/>
+      <c r="F363" s="5" t="n"/>
+      <c r="G363" s="5" t="n"/>
+      <c r="H363" s="6" t="n"/>
+    </row>
+    <row r="364" hidden="1" outlineLevel="2">
+      <c r="A364" s="4" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="B364" s="5" t="n"/>
+      <c r="C364" s="6" t="n"/>
+      <c r="D364" s="6" t="n"/>
+      <c r="E364" s="6" t="n"/>
+      <c r="F364" s="5" t="n"/>
+      <c r="G364" s="5" t="n"/>
+      <c r="H364" s="6" t="n"/>
+    </row>
+    <row r="365" hidden="1" outlineLevel="2">
+      <c r="A365" s="4" t="n">
+        <v>90.75</v>
+      </c>
+      <c r="B365" s="5" t="n"/>
+      <c r="C365" s="6" t="n"/>
+      <c r="D365" s="6" t="n"/>
+      <c r="E365" s="6" t="n"/>
+      <c r="F365" s="5" t="n"/>
+      <c r="G365" s="5" t="n"/>
+      <c r="H365" s="6" t="n"/>
+    </row>
+    <row r="366" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A366" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="B366" s="5" t="n"/>
+      <c r="C366" s="6" t="n"/>
+      <c r="D366" s="6" t="n"/>
+      <c r="E366" s="6" t="n"/>
+      <c r="F366" s="5" t="n"/>
+      <c r="G366" s="5" t="n"/>
+      <c r="H366" s="6" t="n"/>
+    </row>
+    <row r="367" hidden="1" outlineLevel="2">
+      <c r="A367" s="4" t="n">
+        <v>91.25</v>
+      </c>
+      <c r="B367" s="5" t="n"/>
+      <c r="C367" s="6" t="n"/>
+      <c r="D367" s="6" t="n"/>
+      <c r="E367" s="6" t="n"/>
+      <c r="F367" s="5" t="n"/>
+      <c r="G367" s="5" t="n"/>
+      <c r="H367" s="6" t="n"/>
+    </row>
+    <row r="368" hidden="1" outlineLevel="2">
+      <c r="A368" s="4" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="B368" s="5" t="n"/>
+      <c r="C368" s="6" t="n"/>
+      <c r="D368" s="6" t="n"/>
+      <c r="E368" s="6" t="n"/>
+      <c r="F368" s="5" t="n"/>
+      <c r="G368" s="5" t="n"/>
+      <c r="H368" s="6" t="n"/>
+    </row>
+    <row r="369" collapsed="1">
+      <c r="A369" s="4" t="n">
         <v>91.75</v>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B369" s="5" t="inlineStr">
         <is>
           <t>Pause: STONE HEART ..</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>alter Code (handgeschrieben, läuft so in der Firmware):
-progBlack(15715, 65)</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="C369" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_VERSE_HEART, Farben SCHEME_RED
+Ausgabe: nur guitar, Rest aus, Blinder von 'chorus 3' blendet in den letzten 3810 ms ein
+'Stone heart': nur Gitarre und Bass schlagen wie ein Herz auf jedem Beat in Rot, Lampen und Matrix bleiben dunkel; in den letzten 2 Takten blendet der Blinder für chorus 3 ein.</t>
+        </is>
+      </c>
+      <c r="D369" s="6" t="n"/>
+      <c r="E369" s="6" t="inlineStr">
         <is>
           <t>Statt 8 Takten Schwarz: nur Gitarre und Bass zeigen einen Herzschlag in Rot (progHeartbeat), Lampen und Matrix bleiben dunkel. In den letzten 2 Takten blendet ein Blinder ein, voll auf Takt 100.</t>
         </is>
       </c>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5">
+      <c r="F369" s="5" t="n"/>
+      <c r="G369" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H19" s="6" t="inlineStr">
+      <c r="H369" s="6" t="inlineStr">
         <is>
           <t>progBlack(15715, 65)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="n">
+    <row r="370" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A370" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="B370" s="5" t="n"/>
+      <c r="C370" s="6" t="n"/>
+      <c r="D370" s="6" t="n"/>
+      <c r="E370" s="6" t="n"/>
+      <c r="F370" s="5" t="n"/>
+      <c r="G370" s="5" t="n"/>
+      <c r="H370" s="6" t="n"/>
+    </row>
+    <row r="371" hidden="1" outlineLevel="2">
+      <c r="A371" s="4" t="n">
+        <v>92.25</v>
+      </c>
+      <c r="B371" s="5" t="n"/>
+      <c r="C371" s="6" t="n"/>
+      <c r="D371" s="6" t="n"/>
+      <c r="E371" s="6" t="n"/>
+      <c r="F371" s="5" t="n"/>
+      <c r="G371" s="5" t="n"/>
+      <c r="H371" s="6" t="n"/>
+    </row>
+    <row r="372" hidden="1" outlineLevel="2">
+      <c r="A372" s="4" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="B372" s="5" t="n"/>
+      <c r="C372" s="6" t="n"/>
+      <c r="D372" s="6" t="n"/>
+      <c r="E372" s="6" t="n"/>
+      <c r="F372" s="5" t="n"/>
+      <c r="G372" s="5" t="n"/>
+      <c r="H372" s="6" t="n"/>
+    </row>
+    <row r="373" hidden="1" outlineLevel="2">
+      <c r="A373" s="4" t="n">
+        <v>92.75</v>
+      </c>
+      <c r="B373" s="5" t="n"/>
+      <c r="C373" s="6" t="n"/>
+      <c r="D373" s="6" t="n"/>
+      <c r="E373" s="6" t="n"/>
+      <c r="F373" s="5" t="n"/>
+      <c r="G373" s="5" t="n"/>
+      <c r="H373" s="6" t="n"/>
+    </row>
+    <row r="374" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A374" s="4" t="n">
+        <v>93</v>
+      </c>
+      <c r="B374" s="5" t="n"/>
+      <c r="C374" s="6" t="n"/>
+      <c r="D374" s="6" t="n"/>
+      <c r="E374" s="6" t="n"/>
+      <c r="F374" s="5" t="n"/>
+      <c r="G374" s="5" t="n"/>
+      <c r="H374" s="6" t="n"/>
+    </row>
+    <row r="375" hidden="1" outlineLevel="2">
+      <c r="A375" s="4" t="n">
+        <v>93.25</v>
+      </c>
+      <c r="B375" s="5" t="n"/>
+      <c r="C375" s="6" t="n"/>
+      <c r="D375" s="6" t="n"/>
+      <c r="E375" s="6" t="n"/>
+      <c r="F375" s="5" t="n"/>
+      <c r="G375" s="5" t="n"/>
+      <c r="H375" s="6" t="n"/>
+    </row>
+    <row r="376" hidden="1" outlineLevel="2">
+      <c r="A376" s="4" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="B376" s="5" t="n"/>
+      <c r="C376" s="6" t="n"/>
+      <c r="D376" s="6" t="n"/>
+      <c r="E376" s="6" t="n"/>
+      <c r="F376" s="5" t="n"/>
+      <c r="G376" s="5" t="n"/>
+      <c r="H376" s="6" t="n"/>
+    </row>
+    <row r="377" hidden="1" outlineLevel="2">
+      <c r="A377" s="4" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="B377" s="5" t="n"/>
+      <c r="C377" s="6" t="n"/>
+      <c r="D377" s="6" t="n"/>
+      <c r="E377" s="6" t="n"/>
+      <c r="F377" s="5" t="n"/>
+      <c r="G377" s="5" t="n"/>
+      <c r="H377" s="6" t="n"/>
+    </row>
+    <row r="378" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A378" s="4" t="n">
+        <v>94</v>
+      </c>
+      <c r="B378" s="5" t="n"/>
+      <c r="C378" s="6" t="n"/>
+      <c r="D378" s="6" t="n"/>
+      <c r="E378" s="6" t="n"/>
+      <c r="F378" s="5" t="n"/>
+      <c r="G378" s="5" t="n"/>
+      <c r="H378" s="6" t="n"/>
+    </row>
+    <row r="379" hidden="1" outlineLevel="2">
+      <c r="A379" s="4" t="n">
+        <v>94.25</v>
+      </c>
+      <c r="B379" s="5" t="n"/>
+      <c r="C379" s="6" t="n"/>
+      <c r="D379" s="6" t="n"/>
+      <c r="E379" s="6" t="n"/>
+      <c r="F379" s="5" t="n"/>
+      <c r="G379" s="5" t="n"/>
+      <c r="H379" s="6" t="n"/>
+    </row>
+    <row r="380" hidden="1" outlineLevel="2">
+      <c r="A380" s="4" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="B380" s="5" t="n"/>
+      <c r="C380" s="6" t="n"/>
+      <c r="D380" s="6" t="n"/>
+      <c r="E380" s="6" t="n"/>
+      <c r="F380" s="5" t="n"/>
+      <c r="G380" s="5" t="n"/>
+      <c r="H380" s="6" t="n"/>
+    </row>
+    <row r="381" hidden="1" outlineLevel="2">
+      <c r="A381" s="4" t="n">
+        <v>94.75</v>
+      </c>
+      <c r="B381" s="5" t="n"/>
+      <c r="C381" s="6" t="n"/>
+      <c r="D381" s="6" t="n"/>
+      <c r="E381" s="6" t="n"/>
+      <c r="F381" s="5" t="n"/>
+      <c r="G381" s="5" t="n"/>
+      <c r="H381" s="6" t="n"/>
+    </row>
+    <row r="382" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A382" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="B382" s="5" t="n"/>
+      <c r="C382" s="6" t="n"/>
+      <c r="D382" s="6" t="n"/>
+      <c r="E382" s="6" t="n"/>
+      <c r="F382" s="5" t="n"/>
+      <c r="G382" s="5" t="n"/>
+      <c r="H382" s="6" t="n"/>
+    </row>
+    <row r="383" hidden="1" outlineLevel="2">
+      <c r="A383" s="4" t="n">
+        <v>95.25</v>
+      </c>
+      <c r="B383" s="5" t="n"/>
+      <c r="C383" s="6" t="n"/>
+      <c r="D383" s="6" t="n"/>
+      <c r="E383" s="6" t="n"/>
+      <c r="F383" s="5" t="n"/>
+      <c r="G383" s="5" t="n"/>
+      <c r="H383" s="6" t="n"/>
+    </row>
+    <row r="384" hidden="1" outlineLevel="2">
+      <c r="A384" s="4" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="B384" s="5" t="n"/>
+      <c r="C384" s="6" t="n"/>
+      <c r="D384" s="6" t="n"/>
+      <c r="E384" s="6" t="n"/>
+      <c r="F384" s="5" t="n"/>
+      <c r="G384" s="5" t="n"/>
+      <c r="H384" s="6" t="n"/>
+    </row>
+    <row r="385" hidden="1" outlineLevel="2">
+      <c r="A385" s="4" t="n">
+        <v>95.75</v>
+      </c>
+      <c r="B385" s="5" t="n"/>
+      <c r="C385" s="6" t="n"/>
+      <c r="D385" s="6" t="n"/>
+      <c r="E385" s="6" t="n"/>
+      <c r="F385" s="5" t="n"/>
+      <c r="G385" s="5" t="n"/>
+      <c r="H385" s="6" t="n"/>
+    </row>
+    <row r="386" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A386" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="B386" s="5" t="n"/>
+      <c r="C386" s="6" t="n"/>
+      <c r="D386" s="6" t="n"/>
+      <c r="E386" s="6" t="n"/>
+      <c r="F386" s="5" t="n"/>
+      <c r="G386" s="5" t="n"/>
+      <c r="H386" s="6" t="n"/>
+    </row>
+    <row r="387" hidden="1" outlineLevel="2">
+      <c r="A387" s="4" t="n">
+        <v>96.25</v>
+      </c>
+      <c r="B387" s="5" t="n"/>
+      <c r="C387" s="6" t="n"/>
+      <c r="D387" s="6" t="n"/>
+      <c r="E387" s="6" t="n"/>
+      <c r="F387" s="5" t="n"/>
+      <c r="G387" s="5" t="n"/>
+      <c r="H387" s="6" t="n"/>
+    </row>
+    <row r="388" hidden="1" outlineLevel="2">
+      <c r="A388" s="4" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="B388" s="5" t="n"/>
+      <c r="C388" s="6" t="n"/>
+      <c r="D388" s="6" t="n"/>
+      <c r="E388" s="6" t="n"/>
+      <c r="F388" s="5" t="n"/>
+      <c r="G388" s="5" t="n"/>
+      <c r="H388" s="6" t="n"/>
+    </row>
+    <row r="389" hidden="1" outlineLevel="2">
+      <c r="A389" s="4" t="n">
+        <v>96.75</v>
+      </c>
+      <c r="B389" s="5" t="n"/>
+      <c r="C389" s="6" t="n"/>
+      <c r="D389" s="6" t="n"/>
+      <c r="E389" s="6" t="n"/>
+      <c r="F389" s="5" t="n"/>
+      <c r="G389" s="5" t="n"/>
+      <c r="H389" s="6" t="n"/>
+    </row>
+    <row r="390" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A390" s="4" t="n">
+        <v>97</v>
+      </c>
+      <c r="B390" s="5" t="n"/>
+      <c r="C390" s="6" t="n"/>
+      <c r="D390" s="6" t="n"/>
+      <c r="E390" s="6" t="n"/>
+      <c r="F390" s="5" t="n"/>
+      <c r="G390" s="5" t="n"/>
+      <c r="H390" s="6" t="n"/>
+    </row>
+    <row r="391" hidden="1" outlineLevel="2">
+      <c r="A391" s="4" t="n">
+        <v>97.25</v>
+      </c>
+      <c r="B391" s="5" t="n"/>
+      <c r="C391" s="6" t="n"/>
+      <c r="D391" s="6" t="n"/>
+      <c r="E391" s="6" t="n"/>
+      <c r="F391" s="5" t="n"/>
+      <c r="G391" s="5" t="n"/>
+      <c r="H391" s="6" t="n"/>
+    </row>
+    <row r="392" hidden="1" outlineLevel="2">
+      <c r="A392" s="4" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="B392" s="5" t="n"/>
+      <c r="C392" s="6" t="n"/>
+      <c r="D392" s="6" t="n"/>
+      <c r="E392" s="6" t="n"/>
+      <c r="F392" s="5" t="n"/>
+      <c r="G392" s="5" t="n"/>
+      <c r="H392" s="6" t="n"/>
+    </row>
+    <row r="393" hidden="1" outlineLevel="2">
+      <c r="A393" s="4" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="B393" s="5" t="n"/>
+      <c r="C393" s="6" t="n"/>
+      <c r="D393" s="6" t="n"/>
+      <c r="E393" s="6" t="n"/>
+      <c r="F393" s="5" t="n"/>
+      <c r="G393" s="5" t="n"/>
+      <c r="H393" s="6" t="n"/>
+    </row>
+    <row r="394" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A394" s="4" t="n">
+        <v>98</v>
+      </c>
+      <c r="B394" s="5" t="n"/>
+      <c r="C394" s="6" t="n"/>
+      <c r="D394" s="6" t="n"/>
+      <c r="E394" s="6" t="n"/>
+      <c r="F394" s="5" t="n"/>
+      <c r="G394" s="5" t="n"/>
+      <c r="H394" s="6" t="n"/>
+    </row>
+    <row r="395" hidden="1" outlineLevel="2">
+      <c r="A395" s="4" t="n">
+        <v>98.25</v>
+      </c>
+      <c r="B395" s="5" t="n"/>
+      <c r="C395" s="6" t="n"/>
+      <c r="D395" s="6" t="n"/>
+      <c r="E395" s="6" t="n"/>
+      <c r="F395" s="5" t="n"/>
+      <c r="G395" s="5" t="n"/>
+      <c r="H395" s="6" t="n"/>
+    </row>
+    <row r="396" hidden="1" outlineLevel="2">
+      <c r="A396" s="4" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="B396" s="5" t="n"/>
+      <c r="C396" s="6" t="n"/>
+      <c r="D396" s="6" t="n"/>
+      <c r="E396" s="6" t="n"/>
+      <c r="F396" s="5" t="n"/>
+      <c r="G396" s="5" t="n"/>
+      <c r="H396" s="6" t="n"/>
+    </row>
+    <row r="397" hidden="1" outlineLevel="2">
+      <c r="A397" s="4" t="n">
+        <v>98.75</v>
+      </c>
+      <c r="B397" s="5" t="n"/>
+      <c r="C397" s="6" t="n"/>
+      <c r="D397" s="6" t="n"/>
+      <c r="E397" s="6" t="n"/>
+      <c r="F397" s="5" t="n"/>
+      <c r="G397" s="5" t="n"/>
+      <c r="H397" s="6" t="n"/>
+    </row>
+    <row r="398" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A398" s="4" t="n">
+        <v>99</v>
+      </c>
+      <c r="B398" s="5" t="n"/>
+      <c r="C398" s="6" t="n"/>
+      <c r="D398" s="6" t="n"/>
+      <c r="E398" s="6" t="n"/>
+      <c r="F398" s="5" t="n"/>
+      <c r="G398" s="5" t="n"/>
+      <c r="H398" s="6" t="n"/>
+    </row>
+    <row r="399" hidden="1" outlineLevel="2">
+      <c r="A399" s="4" t="n">
+        <v>99.25</v>
+      </c>
+      <c r="B399" s="5" t="n"/>
+      <c r="C399" s="6" t="n"/>
+      <c r="D399" s="6" t="n"/>
+      <c r="E399" s="6" t="n"/>
+      <c r="F399" s="5" t="n"/>
+      <c r="G399" s="5" t="n"/>
+      <c r="H399" s="6" t="n"/>
+    </row>
+    <row r="400" hidden="1" outlineLevel="2">
+      <c r="A400" s="4" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="B400" s="5" t="n"/>
+      <c r="C400" s="6" t="n"/>
+      <c r="D400" s="6" t="n"/>
+      <c r="E400" s="6" t="n"/>
+      <c r="F400" s="5" t="n"/>
+      <c r="G400" s="5" t="n"/>
+      <c r="H400" s="6" t="n"/>
+    </row>
+    <row r="401" hidden="1" outlineLevel="2">
+      <c r="A401" s="4" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="B401" s="5" t="n"/>
+      <c r="C401" s="6" t="n"/>
+      <c r="D401" s="6" t="n"/>
+      <c r="E401" s="6" t="n"/>
+      <c r="F401" s="5" t="n"/>
+      <c r="G401" s="5" t="n"/>
+      <c r="H401" s="6" t="n"/>
+    </row>
+    <row r="402" collapsed="1">
+      <c r="A402" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B402" s="5" t="inlineStr">
         <is>
           <t>chorus 3</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>alter Code (handgeschrieben, läuft so in der Firmware):
-progFastBlingBling(30480, 1, 75, 1, 100, 2000)</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="C402" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_SPARKLE, Farben SCHEME_ICE
+Ausgabe: Blinder voll bei Takt 100 = 0 ms, 4762 ms lang, Blinder blendet in den 3810 ms davor ein, 0 ms voll, 952 ms aus
+Glitzern in Eisblau; der Blinder aus der Pause steht voll auf dem Einsatz (Takt 100) und klingt in 2 Beats ab.</t>
+        </is>
+      </c>
+      <c r="D402" s="6" t="n"/>
+      <c r="E402" s="6" t="inlineStr">
         <is>
           <t>Anwachsende Einzelblitze bleiben (16 Takte), in ICE -&gt; ab der Hälfte FIRE (bei Takt 108 eine eigene Zeile anlegen); der Blinder aus der Pause steht auf dem Einsatz.</t>
         </is>
       </c>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5">
+      <c r="F402" s="5" t="n"/>
+      <c r="G402" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H20" s="6" t="inlineStr">
+      <c r="H402" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(30480, 1, 75, 1, 100, 2000)</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="n">
+    <row r="403" hidden="1" outlineLevel="2">
+      <c r="A403" s="4" t="n">
+        <v>100.25</v>
+      </c>
+      <c r="B403" s="5" t="n"/>
+      <c r="C403" s="6" t="n"/>
+      <c r="D403" s="6" t="n"/>
+      <c r="E403" s="6" t="n"/>
+      <c r="F403" s="5" t="n"/>
+      <c r="G403" s="5" t="n"/>
+      <c r="H403" s="6" t="n"/>
+    </row>
+    <row r="404" hidden="1" outlineLevel="2">
+      <c r="A404" s="4" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="B404" s="5" t="n"/>
+      <c r="C404" s="6" t="n"/>
+      <c r="D404" s="6" t="n"/>
+      <c r="E404" s="6" t="n"/>
+      <c r="F404" s="5" t="n"/>
+      <c r="G404" s="5" t="n"/>
+      <c r="H404" s="6" t="n"/>
+    </row>
+    <row r="405" hidden="1" outlineLevel="2">
+      <c r="A405" s="4" t="n">
+        <v>100.75</v>
+      </c>
+      <c r="B405" s="5" t="n"/>
+      <c r="C405" s="6" t="n"/>
+      <c r="D405" s="6" t="n"/>
+      <c r="E405" s="6" t="n"/>
+      <c r="F405" s="5" t="n"/>
+      <c r="G405" s="5" t="n"/>
+      <c r="H405" s="6" t="n"/>
+    </row>
+    <row r="406" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A406" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="B406" s="5" t="n"/>
+      <c r="C406" s="6" t="n"/>
+      <c r="D406" s="6" t="n"/>
+      <c r="E406" s="6" t="n"/>
+      <c r="F406" s="5" t="n"/>
+      <c r="G406" s="5" t="n"/>
+      <c r="H406" s="6" t="n"/>
+    </row>
+    <row r="407" hidden="1" outlineLevel="2">
+      <c r="A407" s="4" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="B407" s="5" t="n"/>
+      <c r="C407" s="6" t="n"/>
+      <c r="D407" s="6" t="n"/>
+      <c r="E407" s="6" t="n"/>
+      <c r="F407" s="5" t="n"/>
+      <c r="G407" s="5" t="n"/>
+      <c r="H407" s="6" t="n"/>
+    </row>
+    <row r="408" hidden="1" outlineLevel="2">
+      <c r="A408" s="4" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="B408" s="5" t="n"/>
+      <c r="C408" s="6" t="n"/>
+      <c r="D408" s="6" t="n"/>
+      <c r="E408" s="6" t="n"/>
+      <c r="F408" s="5" t="n"/>
+      <c r="G408" s="5" t="n"/>
+      <c r="H408" s="6" t="n"/>
+    </row>
+    <row r="409" hidden="1" outlineLevel="2">
+      <c r="A409" s="4" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="B409" s="5" t="n"/>
+      <c r="C409" s="6" t="n"/>
+      <c r="D409" s="6" t="n"/>
+      <c r="E409" s="6" t="n"/>
+      <c r="F409" s="5" t="n"/>
+      <c r="G409" s="5" t="n"/>
+      <c r="H409" s="6" t="n"/>
+    </row>
+    <row r="410" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A410" s="4" t="n">
+        <v>102</v>
+      </c>
+      <c r="B410" s="5" t="n"/>
+      <c r="C410" s="6" t="n"/>
+      <c r="D410" s="6" t="n"/>
+      <c r="E410" s="6" t="n"/>
+      <c r="F410" s="5" t="n"/>
+      <c r="G410" s="5" t="n"/>
+      <c r="H410" s="6" t="n"/>
+    </row>
+    <row r="411" hidden="1" outlineLevel="2">
+      <c r="A411" s="4" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="B411" s="5" t="n"/>
+      <c r="C411" s="6" t="n"/>
+      <c r="D411" s="6" t="n"/>
+      <c r="E411" s="6" t="n"/>
+      <c r="F411" s="5" t="n"/>
+      <c r="G411" s="5" t="n"/>
+      <c r="H411" s="6" t="n"/>
+    </row>
+    <row r="412" hidden="1" outlineLevel="2">
+      <c r="A412" s="4" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="B412" s="5" t="n"/>
+      <c r="C412" s="6" t="n"/>
+      <c r="D412" s="6" t="n"/>
+      <c r="E412" s="6" t="n"/>
+      <c r="F412" s="5" t="n"/>
+      <c r="G412" s="5" t="n"/>
+      <c r="H412" s="6" t="n"/>
+    </row>
+    <row r="413" hidden="1" outlineLevel="2">
+      <c r="A413" s="4" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="B413" s="5" t="n"/>
+      <c r="C413" s="6" t="n"/>
+      <c r="D413" s="6" t="n"/>
+      <c r="E413" s="6" t="n"/>
+      <c r="F413" s="5" t="n"/>
+      <c r="G413" s="5" t="n"/>
+      <c r="H413" s="6" t="n"/>
+    </row>
+    <row r="414" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A414" s="4" t="n">
+        <v>103</v>
+      </c>
+      <c r="B414" s="5" t="n"/>
+      <c r="C414" s="6" t="n"/>
+      <c r="D414" s="6" t="n"/>
+      <c r="E414" s="6" t="n"/>
+      <c r="F414" s="5" t="n"/>
+      <c r="G414" s="5" t="n"/>
+      <c r="H414" s="6" t="n"/>
+    </row>
+    <row r="415" hidden="1" outlineLevel="2">
+      <c r="A415" s="4" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="B415" s="5" t="n"/>
+      <c r="C415" s="6" t="n"/>
+      <c r="D415" s="6" t="n"/>
+      <c r="E415" s="6" t="n"/>
+      <c r="F415" s="5" t="n"/>
+      <c r="G415" s="5" t="n"/>
+      <c r="H415" s="6" t="n"/>
+    </row>
+    <row r="416" hidden="1" outlineLevel="2">
+      <c r="A416" s="4" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="B416" s="5" t="n"/>
+      <c r="C416" s="6" t="n"/>
+      <c r="D416" s="6" t="n"/>
+      <c r="E416" s="6" t="n"/>
+      <c r="F416" s="5" t="n"/>
+      <c r="G416" s="5" t="n"/>
+      <c r="H416" s="6" t="n"/>
+    </row>
+    <row r="417" hidden="1" outlineLevel="2">
+      <c r="A417" s="4" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="B417" s="5" t="n"/>
+      <c r="C417" s="6" t="n"/>
+      <c r="D417" s="6" t="n"/>
+      <c r="E417" s="6" t="n"/>
+      <c r="F417" s="5" t="n"/>
+      <c r="G417" s="5" t="n"/>
+      <c r="H417" s="6" t="n"/>
+    </row>
+    <row r="418" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A418" s="4" t="n">
+        <v>104</v>
+      </c>
+      <c r="B418" s="5" t="n"/>
+      <c r="C418" s="6" t="n"/>
+      <c r="D418" s="6" t="n"/>
+      <c r="E418" s="6" t="n"/>
+      <c r="F418" s="5" t="n"/>
+      <c r="G418" s="5" t="n"/>
+      <c r="H418" s="6" t="n"/>
+    </row>
+    <row r="419" hidden="1" outlineLevel="2">
+      <c r="A419" s="4" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="B419" s="5" t="n"/>
+      <c r="C419" s="6" t="n"/>
+      <c r="D419" s="6" t="n"/>
+      <c r="E419" s="6" t="n"/>
+      <c r="F419" s="5" t="n"/>
+      <c r="G419" s="5" t="n"/>
+      <c r="H419" s="6" t="n"/>
+    </row>
+    <row r="420" hidden="1" outlineLevel="2">
+      <c r="A420" s="4" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="B420" s="5" t="n"/>
+      <c r="C420" s="6" t="n"/>
+      <c r="D420" s="6" t="n"/>
+      <c r="E420" s="6" t="n"/>
+      <c r="F420" s="5" t="n"/>
+      <c r="G420" s="5" t="n"/>
+      <c r="H420" s="6" t="n"/>
+    </row>
+    <row r="421" hidden="1" outlineLevel="2">
+      <c r="A421" s="4" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="B421" s="5" t="n"/>
+      <c r="C421" s="6" t="n"/>
+      <c r="D421" s="6" t="n"/>
+      <c r="E421" s="6" t="n"/>
+      <c r="F421" s="5" t="n"/>
+      <c r="G421" s="5" t="n"/>
+      <c r="H421" s="6" t="n"/>
+    </row>
+    <row r="422" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A422" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="B422" s="5" t="n"/>
+      <c r="C422" s="6" t="n"/>
+      <c r="D422" s="6" t="n"/>
+      <c r="E422" s="6" t="n"/>
+      <c r="F422" s="5" t="n"/>
+      <c r="G422" s="5" t="n"/>
+      <c r="H422" s="6" t="n"/>
+    </row>
+    <row r="423" hidden="1" outlineLevel="2">
+      <c r="A423" s="4" t="n">
+        <v>105.25</v>
+      </c>
+      <c r="B423" s="5" t="n"/>
+      <c r="C423" s="6" t="n"/>
+      <c r="D423" s="6" t="n"/>
+      <c r="E423" s="6" t="n"/>
+      <c r="F423" s="5" t="n"/>
+      <c r="G423" s="5" t="n"/>
+      <c r="H423" s="6" t="n"/>
+    </row>
+    <row r="424" hidden="1" outlineLevel="2">
+      <c r="A424" s="4" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="B424" s="5" t="n"/>
+      <c r="C424" s="6" t="n"/>
+      <c r="D424" s="6" t="n"/>
+      <c r="E424" s="6" t="n"/>
+      <c r="F424" s="5" t="n"/>
+      <c r="G424" s="5" t="n"/>
+      <c r="H424" s="6" t="n"/>
+    </row>
+    <row r="425" hidden="1" outlineLevel="2">
+      <c r="A425" s="4" t="n">
+        <v>105.75</v>
+      </c>
+      <c r="B425" s="5" t="n"/>
+      <c r="C425" s="6" t="n"/>
+      <c r="D425" s="6" t="n"/>
+      <c r="E425" s="6" t="n"/>
+      <c r="F425" s="5" t="n"/>
+      <c r="G425" s="5" t="n"/>
+      <c r="H425" s="6" t="n"/>
+    </row>
+    <row r="426" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A426" s="4" t="n">
+        <v>106</v>
+      </c>
+      <c r="B426" s="5" t="n"/>
+      <c r="C426" s="6" t="n"/>
+      <c r="D426" s="6" t="n"/>
+      <c r="E426" s="6" t="n"/>
+      <c r="F426" s="5" t="n"/>
+      <c r="G426" s="5" t="n"/>
+      <c r="H426" s="6" t="n"/>
+    </row>
+    <row r="427" hidden="1" outlineLevel="2">
+      <c r="A427" s="4" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="B427" s="5" t="n"/>
+      <c r="C427" s="6" t="n"/>
+      <c r="D427" s="6" t="n"/>
+      <c r="E427" s="6" t="n"/>
+      <c r="F427" s="5" t="n"/>
+      <c r="G427" s="5" t="n"/>
+      <c r="H427" s="6" t="n"/>
+    </row>
+    <row r="428" hidden="1" outlineLevel="2">
+      <c r="A428" s="4" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="B428" s="5" t="n"/>
+      <c r="C428" s="6" t="n"/>
+      <c r="D428" s="6" t="n"/>
+      <c r="E428" s="6" t="n"/>
+      <c r="F428" s="5" t="n"/>
+      <c r="G428" s="5" t="n"/>
+      <c r="H428" s="6" t="n"/>
+    </row>
+    <row r="429" hidden="1" outlineLevel="2">
+      <c r="A429" s="4" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="B429" s="5" t="n"/>
+      <c r="C429" s="6" t="n"/>
+      <c r="D429" s="6" t="n"/>
+      <c r="E429" s="6" t="n"/>
+      <c r="F429" s="5" t="n"/>
+      <c r="G429" s="5" t="n"/>
+      <c r="H429" s="6" t="n"/>
+    </row>
+    <row r="430" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A430" s="4" t="n">
+        <v>107</v>
+      </c>
+      <c r="B430" s="5" t="n"/>
+      <c r="C430" s="6" t="n"/>
+      <c r="D430" s="6" t="n"/>
+      <c r="E430" s="6" t="n"/>
+      <c r="F430" s="5" t="n"/>
+      <c r="G430" s="5" t="n"/>
+      <c r="H430" s="6" t="n"/>
+    </row>
+    <row r="431" hidden="1" outlineLevel="2">
+      <c r="A431" s="4" t="n">
+        <v>107.25</v>
+      </c>
+      <c r="B431" s="5" t="n"/>
+      <c r="C431" s="6" t="n"/>
+      <c r="D431" s="6" t="n"/>
+      <c r="E431" s="6" t="n"/>
+      <c r="F431" s="5" t="n"/>
+      <c r="G431" s="5" t="n"/>
+      <c r="H431" s="6" t="n"/>
+    </row>
+    <row r="432" hidden="1" outlineLevel="2">
+      <c r="A432" s="4" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="B432" s="5" t="n"/>
+      <c r="C432" s="6" t="n"/>
+      <c r="D432" s="6" t="n"/>
+      <c r="E432" s="6" t="n"/>
+      <c r="F432" s="5" t="n"/>
+      <c r="G432" s="5" t="n"/>
+      <c r="H432" s="6" t="n"/>
+    </row>
+    <row r="433" hidden="1" outlineLevel="2">
+      <c r="A433" s="4" t="n">
+        <v>107.75</v>
+      </c>
+      <c r="B433" s="5" t="n"/>
+      <c r="C433" s="6" t="n"/>
+      <c r="D433" s="6" t="n"/>
+      <c r="E433" s="6" t="n"/>
+      <c r="F433" s="5" t="n"/>
+      <c r="G433" s="5" t="n"/>
+      <c r="H433" s="6" t="n"/>
+    </row>
+    <row r="434" collapsed="1">
+      <c r="A434" s="4" t="n">
+        <v>108</v>
+      </c>
+      <c r="B434" s="5" t="inlineStr">
+        <is>
+          <t>chorus 3b</t>
+        </is>
+      </c>
+      <c r="C434" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_SPARKLE, Farben SCHEME_FIRE
+Zweite Hälfte: das Glitzern wird heiß - Rot, Orange und Gelb.</t>
+        </is>
+      </c>
+      <c r="D434" s="6" t="n"/>
+      <c r="E434" s="6" t="n"/>
+      <c r="F434" s="5" t="n"/>
+      <c r="G434" s="5" t="n"/>
+      <c r="H434" s="6" t="n"/>
+    </row>
+    <row r="435" hidden="1" outlineLevel="2">
+      <c r="A435" s="4" t="n">
+        <v>108.25</v>
+      </c>
+      <c r="B435" s="5" t="n"/>
+      <c r="C435" s="6" t="n"/>
+      <c r="D435" s="6" t="n"/>
+      <c r="E435" s="6" t="n"/>
+      <c r="F435" s="5" t="n"/>
+      <c r="G435" s="5" t="n"/>
+      <c r="H435" s="6" t="n"/>
+    </row>
+    <row r="436" hidden="1" outlineLevel="2">
+      <c r="A436" s="4" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="B436" s="5" t="n"/>
+      <c r="C436" s="6" t="n"/>
+      <c r="D436" s="6" t="n"/>
+      <c r="E436" s="6" t="n"/>
+      <c r="F436" s="5" t="n"/>
+      <c r="G436" s="5" t="n"/>
+      <c r="H436" s="6" t="n"/>
+    </row>
+    <row r="437" hidden="1" outlineLevel="2">
+      <c r="A437" s="4" t="n">
+        <v>108.75</v>
+      </c>
+      <c r="B437" s="5" t="n"/>
+      <c r="C437" s="6" t="n"/>
+      <c r="D437" s="6" t="n"/>
+      <c r="E437" s="6" t="n"/>
+      <c r="F437" s="5" t="n"/>
+      <c r="G437" s="5" t="n"/>
+      <c r="H437" s="6" t="n"/>
+    </row>
+    <row r="438" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A438" s="4" t="n">
+        <v>109</v>
+      </c>
+      <c r="B438" s="5" t="n"/>
+      <c r="C438" s="6" t="n"/>
+      <c r="D438" s="6" t="n"/>
+      <c r="E438" s="6" t="n"/>
+      <c r="F438" s="5" t="n"/>
+      <c r="G438" s="5" t="n"/>
+      <c r="H438" s="6" t="n"/>
+    </row>
+    <row r="439" hidden="1" outlineLevel="2">
+      <c r="A439" s="4" t="n">
+        <v>109.25</v>
+      </c>
+      <c r="B439" s="5" t="n"/>
+      <c r="C439" s="6" t="n"/>
+      <c r="D439" s="6" t="n"/>
+      <c r="E439" s="6" t="n"/>
+      <c r="F439" s="5" t="n"/>
+      <c r="G439" s="5" t="n"/>
+      <c r="H439" s="6" t="n"/>
+    </row>
+    <row r="440" hidden="1" outlineLevel="2">
+      <c r="A440" s="4" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="B440" s="5" t="n"/>
+      <c r="C440" s="6" t="n"/>
+      <c r="D440" s="6" t="n"/>
+      <c r="E440" s="6" t="n"/>
+      <c r="F440" s="5" t="n"/>
+      <c r="G440" s="5" t="n"/>
+      <c r="H440" s="6" t="n"/>
+    </row>
+    <row r="441" hidden="1" outlineLevel="2">
+      <c r="A441" s="4" t="n">
+        <v>109.75</v>
+      </c>
+      <c r="B441" s="5" t="n"/>
+      <c r="C441" s="6" t="n"/>
+      <c r="D441" s="6" t="n"/>
+      <c r="E441" s="6" t="n"/>
+      <c r="F441" s="5" t="n"/>
+      <c r="G441" s="5" t="n"/>
+      <c r="H441" s="6" t="n"/>
+    </row>
+    <row r="442" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A442" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="B442" s="5" t="n"/>
+      <c r="C442" s="6" t="n"/>
+      <c r="D442" s="6" t="n"/>
+      <c r="E442" s="6" t="n"/>
+      <c r="F442" s="5" t="n"/>
+      <c r="G442" s="5" t="n"/>
+      <c r="H442" s="6" t="n"/>
+    </row>
+    <row r="443" hidden="1" outlineLevel="2">
+      <c r="A443" s="4" t="n">
+        <v>110.25</v>
+      </c>
+      <c r="B443" s="5" t="n"/>
+      <c r="C443" s="6" t="n"/>
+      <c r="D443" s="6" t="n"/>
+      <c r="E443" s="6" t="n"/>
+      <c r="F443" s="5" t="n"/>
+      <c r="G443" s="5" t="n"/>
+      <c r="H443" s="6" t="n"/>
+    </row>
+    <row r="444" hidden="1" outlineLevel="2">
+      <c r="A444" s="4" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="B444" s="5" t="n"/>
+      <c r="C444" s="6" t="n"/>
+      <c r="D444" s="6" t="n"/>
+      <c r="E444" s="6" t="n"/>
+      <c r="F444" s="5" t="n"/>
+      <c r="G444" s="5" t="n"/>
+      <c r="H444" s="6" t="n"/>
+    </row>
+    <row r="445" hidden="1" outlineLevel="2">
+      <c r="A445" s="4" t="n">
+        <v>110.75</v>
+      </c>
+      <c r="B445" s="5" t="n"/>
+      <c r="C445" s="6" t="n"/>
+      <c r="D445" s="6" t="n"/>
+      <c r="E445" s="6" t="n"/>
+      <c r="F445" s="5" t="n"/>
+      <c r="G445" s="5" t="n"/>
+      <c r="H445" s="6" t="n"/>
+    </row>
+    <row r="446" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A446" s="4" t="n">
+        <v>111</v>
+      </c>
+      <c r="B446" s="5" t="n"/>
+      <c r="C446" s="6" t="n"/>
+      <c r="D446" s="6" t="n"/>
+      <c r="E446" s="6" t="n"/>
+      <c r="F446" s="5" t="n"/>
+      <c r="G446" s="5" t="n"/>
+      <c r="H446" s="6" t="n"/>
+    </row>
+    <row r="447" hidden="1" outlineLevel="2">
+      <c r="A447" s="4" t="n">
+        <v>111.25</v>
+      </c>
+      <c r="B447" s="5" t="n"/>
+      <c r="C447" s="6" t="n"/>
+      <c r="D447" s="6" t="n"/>
+      <c r="E447" s="6" t="n"/>
+      <c r="F447" s="5" t="n"/>
+      <c r="G447" s="5" t="n"/>
+      <c r="H447" s="6" t="n"/>
+    </row>
+    <row r="448" hidden="1" outlineLevel="2">
+      <c r="A448" s="4" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="B448" s="5" t="n"/>
+      <c r="C448" s="6" t="n"/>
+      <c r="D448" s="6" t="n"/>
+      <c r="E448" s="6" t="n"/>
+      <c r="F448" s="5" t="n"/>
+      <c r="G448" s="5" t="n"/>
+      <c r="H448" s="6" t="n"/>
+    </row>
+    <row r="449" hidden="1" outlineLevel="2">
+      <c r="A449" s="4" t="n">
+        <v>111.75</v>
+      </c>
+      <c r="B449" s="5" t="n"/>
+      <c r="C449" s="6" t="n"/>
+      <c r="D449" s="6" t="n"/>
+      <c r="E449" s="6" t="n"/>
+      <c r="F449" s="5" t="n"/>
+      <c r="G449" s="5" t="n"/>
+      <c r="H449" s="6" t="n"/>
+    </row>
+    <row r="450" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A450" s="4" t="n">
+        <v>112</v>
+      </c>
+      <c r="B450" s="5" t="n"/>
+      <c r="C450" s="6" t="n"/>
+      <c r="D450" s="6" t="n"/>
+      <c r="E450" s="6" t="n"/>
+      <c r="F450" s="5" t="n"/>
+      <c r="G450" s="5" t="n"/>
+      <c r="H450" s="6" t="n"/>
+    </row>
+    <row r="451" hidden="1" outlineLevel="2">
+      <c r="A451" s="4" t="n">
+        <v>112.25</v>
+      </c>
+      <c r="B451" s="5" t="n"/>
+      <c r="C451" s="6" t="n"/>
+      <c r="D451" s="6" t="n"/>
+      <c r="E451" s="6" t="n"/>
+      <c r="F451" s="5" t="n"/>
+      <c r="G451" s="5" t="n"/>
+      <c r="H451" s="6" t="n"/>
+    </row>
+    <row r="452" hidden="1" outlineLevel="2">
+      <c r="A452" s="4" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="B452" s="5" t="n"/>
+      <c r="C452" s="6" t="n"/>
+      <c r="D452" s="6" t="n"/>
+      <c r="E452" s="6" t="n"/>
+      <c r="F452" s="5" t="n"/>
+      <c r="G452" s="5" t="n"/>
+      <c r="H452" s="6" t="n"/>
+    </row>
+    <row r="453" hidden="1" outlineLevel="2">
+      <c r="A453" s="4" t="n">
+        <v>112.75</v>
+      </c>
+      <c r="B453" s="5" t="n"/>
+      <c r="C453" s="6" t="n"/>
+      <c r="D453" s="6" t="n"/>
+      <c r="E453" s="6" t="n"/>
+      <c r="F453" s="5" t="n"/>
+      <c r="G453" s="5" t="n"/>
+      <c r="H453" s="6" t="n"/>
+    </row>
+    <row r="454" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A454" s="4" t="n">
+        <v>113</v>
+      </c>
+      <c r="B454" s="5" t="n"/>
+      <c r="C454" s="6" t="n"/>
+      <c r="D454" s="6" t="n"/>
+      <c r="E454" s="6" t="n"/>
+      <c r="F454" s="5" t="n"/>
+      <c r="G454" s="5" t="n"/>
+      <c r="H454" s="6" t="n"/>
+    </row>
+    <row r="455" hidden="1" outlineLevel="2">
+      <c r="A455" s="4" t="n">
+        <v>113.25</v>
+      </c>
+      <c r="B455" s="5" t="n"/>
+      <c r="C455" s="6" t="n"/>
+      <c r="D455" s="6" t="n"/>
+      <c r="E455" s="6" t="n"/>
+      <c r="F455" s="5" t="n"/>
+      <c r="G455" s="5" t="n"/>
+      <c r="H455" s="6" t="n"/>
+    </row>
+    <row r="456" hidden="1" outlineLevel="2">
+      <c r="A456" s="4" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="B456" s="5" t="n"/>
+      <c r="C456" s="6" t="n"/>
+      <c r="D456" s="6" t="n"/>
+      <c r="E456" s="6" t="n"/>
+      <c r="F456" s="5" t="n"/>
+      <c r="G456" s="5" t="n"/>
+      <c r="H456" s="6" t="n"/>
+    </row>
+    <row r="457" hidden="1" outlineLevel="2">
+      <c r="A457" s="4" t="n">
+        <v>113.75</v>
+      </c>
+      <c r="B457" s="5" t="n"/>
+      <c r="C457" s="6" t="n"/>
+      <c r="D457" s="6" t="n"/>
+      <c r="E457" s="6" t="n"/>
+      <c r="F457" s="5" t="n"/>
+      <c r="G457" s="5" t="n"/>
+      <c r="H457" s="6" t="n"/>
+    </row>
+    <row r="458" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A458" s="4" t="n">
+        <v>114</v>
+      </c>
+      <c r="B458" s="5" t="n"/>
+      <c r="C458" s="6" t="n"/>
+      <c r="D458" s="6" t="n"/>
+      <c r="E458" s="6" t="n"/>
+      <c r="F458" s="5" t="n"/>
+      <c r="G458" s="5" t="n"/>
+      <c r="H458" s="6" t="n"/>
+    </row>
+    <row r="459" hidden="1" outlineLevel="2">
+      <c r="A459" s="4" t="n">
+        <v>114.25</v>
+      </c>
+      <c r="B459" s="5" t="n"/>
+      <c r="C459" s="6" t="n"/>
+      <c r="D459" s="6" t="n"/>
+      <c r="E459" s="6" t="n"/>
+      <c r="F459" s="5" t="n"/>
+      <c r="G459" s="5" t="n"/>
+      <c r="H459" s="6" t="n"/>
+    </row>
+    <row r="460" hidden="1" outlineLevel="2">
+      <c r="A460" s="4" t="n">
+        <v>114.5</v>
+      </c>
+      <c r="B460" s="5" t="n"/>
+      <c r="C460" s="6" t="n"/>
+      <c r="D460" s="6" t="n"/>
+      <c r="E460" s="6" t="n"/>
+      <c r="F460" s="5" t="n"/>
+      <c r="G460" s="5" t="n"/>
+      <c r="H460" s="6" t="n"/>
+    </row>
+    <row r="461" hidden="1" outlineLevel="2">
+      <c r="A461" s="4" t="n">
+        <v>114.75</v>
+      </c>
+      <c r="B461" s="5" t="n"/>
+      <c r="C461" s="6" t="n"/>
+      <c r="D461" s="6" t="n"/>
+      <c r="E461" s="6" t="n"/>
+      <c r="F461" s="5" t="n"/>
+      <c r="G461" s="5" t="n"/>
+      <c r="H461" s="6" t="n"/>
+    </row>
+    <row r="462" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A462" s="4" t="n">
+        <v>115</v>
+      </c>
+      <c r="B462" s="5" t="n"/>
+      <c r="C462" s="6" t="n"/>
+      <c r="D462" s="6" t="n"/>
+      <c r="E462" s="6" t="n"/>
+      <c r="F462" s="5" t="n"/>
+      <c r="G462" s="5" t="n"/>
+      <c r="H462" s="6" t="n"/>
+    </row>
+    <row r="463" hidden="1" outlineLevel="2">
+      <c r="A463" s="4" t="n">
+        <v>115.25</v>
+      </c>
+      <c r="B463" s="5" t="n"/>
+      <c r="C463" s="6" t="n"/>
+      <c r="D463" s="6" t="n"/>
+      <c r="E463" s="6" t="n"/>
+      <c r="F463" s="5" t="n"/>
+      <c r="G463" s="5" t="n"/>
+      <c r="H463" s="6" t="n"/>
+    </row>
+    <row r="464" hidden="1" outlineLevel="2">
+      <c r="A464" s="4" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="B464" s="5" t="n"/>
+      <c r="C464" s="6" t="n"/>
+      <c r="D464" s="6" t="n"/>
+      <c r="E464" s="6" t="n"/>
+      <c r="F464" s="5" t="n"/>
+      <c r="G464" s="5" t="n"/>
+      <c r="H464" s="6" t="n"/>
+    </row>
+    <row r="465" hidden="1" outlineLevel="2">
+      <c r="A465" s="4" t="n">
+        <v>115.75</v>
+      </c>
+      <c r="B465" s="5" t="n"/>
+      <c r="C465" s="6" t="n"/>
+      <c r="D465" s="6" t="n"/>
+      <c r="E465" s="6" t="n"/>
+      <c r="F465" s="5" t="n"/>
+      <c r="G465" s="5" t="n"/>
+      <c r="H465" s="6" t="n"/>
+    </row>
+    <row r="466" collapsed="1">
+      <c r="A466" s="4" t="n">
         <v>116</v>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B466" s="5" t="inlineStr">
         <is>
           <t>bridge triolisch</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>alter Code (handgeschrieben, läuft so in der Firmware):
-progStrobo(13330, 80, 175, 255, 255, 255)</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="C466" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_COLORS, Farben SCHEME_WHITE
+Ausgabe: Tor 3x pro Beat, 50 % hell, Blinder voll bei Takt 122,25 = 11905 ms, 381 ms lang, Blinder blendet in den 95 ms davor ein, 95 ms voll, 191 ms aus, Blinder voll bei Takt 122,5 = 12381 ms, 381 ms lang, Blinder blendet in den 95 ms davor ein, 95 ms voll, 191 ms aus, Blinder voll bei Takt 122,75 = 12857 ms, 381 ms lang, Blinder blendet in den 95 ms davor ein, 95 ms voll, 191 ms aus
+Weißer Strobo im Takt, triolisch (3 Blitze pro Beat); drei kurze Blinder auf den letzten drei Vierteln (Takt 122,25 / 122,5 / 122,75).</t>
+        </is>
+      </c>
+      <c r="D466" s="6" t="n"/>
+      <c r="E466" s="6" t="inlineStr">
         <is>
           <t>Weißer Strobo bleibt (triolisch); drei kurze Blinder auf den letzten drei Vierteln (Takt 122,25 / 122,5 / 122,75).</t>
         </is>
       </c>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5">
+      <c r="F466" s="5" t="n"/>
+      <c r="G466" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H21" s="6" t="inlineStr">
+      <c r="H466" s="6" t="inlineStr">
         <is>
           <t>progStrobo(13330, 80, 175, 255, 255, 255)</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="n">
+    <row r="467" hidden="1" outlineLevel="2">
+      <c r="A467" s="4" t="n">
+        <v>116.25</v>
+      </c>
+      <c r="B467" s="5" t="n"/>
+      <c r="C467" s="6" t="n"/>
+      <c r="D467" s="6" t="n"/>
+      <c r="E467" s="6" t="n"/>
+      <c r="F467" s="5" t="n"/>
+      <c r="G467" s="5" t="n"/>
+      <c r="H467" s="6" t="n"/>
+    </row>
+    <row r="468" hidden="1" outlineLevel="2">
+      <c r="A468" s="4" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="B468" s="5" t="n"/>
+      <c r="C468" s="6" t="n"/>
+      <c r="D468" s="6" t="n"/>
+      <c r="E468" s="6" t="n"/>
+      <c r="F468" s="5" t="n"/>
+      <c r="G468" s="5" t="n"/>
+      <c r="H468" s="6" t="n"/>
+    </row>
+    <row r="469" hidden="1" outlineLevel="2">
+      <c r="A469" s="4" t="n">
+        <v>116.75</v>
+      </c>
+      <c r="B469" s="5" t="n"/>
+      <c r="C469" s="6" t="n"/>
+      <c r="D469" s="6" t="n"/>
+      <c r="E469" s="6" t="n"/>
+      <c r="F469" s="5" t="n"/>
+      <c r="G469" s="5" t="n"/>
+      <c r="H469" s="6" t="n"/>
+    </row>
+    <row r="470" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A470" s="4" t="n">
+        <v>117</v>
+      </c>
+      <c r="B470" s="5" t="n"/>
+      <c r="C470" s="6" t="n"/>
+      <c r="D470" s="6" t="n"/>
+      <c r="E470" s="6" t="n"/>
+      <c r="F470" s="5" t="n"/>
+      <c r="G470" s="5" t="n"/>
+      <c r="H470" s="6" t="n"/>
+    </row>
+    <row r="471" hidden="1" outlineLevel="2">
+      <c r="A471" s="4" t="n">
+        <v>117.25</v>
+      </c>
+      <c r="B471" s="5" t="n"/>
+      <c r="C471" s="6" t="n"/>
+      <c r="D471" s="6" t="n"/>
+      <c r="E471" s="6" t="n"/>
+      <c r="F471" s="5" t="n"/>
+      <c r="G471" s="5" t="n"/>
+      <c r="H471" s="6" t="n"/>
+    </row>
+    <row r="472" hidden="1" outlineLevel="2">
+      <c r="A472" s="4" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="B472" s="5" t="n"/>
+      <c r="C472" s="6" t="n"/>
+      <c r="D472" s="6" t="n"/>
+      <c r="E472" s="6" t="n"/>
+      <c r="F472" s="5" t="n"/>
+      <c r="G472" s="5" t="n"/>
+      <c r="H472" s="6" t="n"/>
+    </row>
+    <row r="473" hidden="1" outlineLevel="2">
+      <c r="A473" s="4" t="n">
+        <v>117.75</v>
+      </c>
+      <c r="B473" s="5" t="n"/>
+      <c r="C473" s="6" t="n"/>
+      <c r="D473" s="6" t="n"/>
+      <c r="E473" s="6" t="n"/>
+      <c r="F473" s="5" t="n"/>
+      <c r="G473" s="5" t="n"/>
+      <c r="H473" s="6" t="n"/>
+    </row>
+    <row r="474" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A474" s="4" t="n">
+        <v>118</v>
+      </c>
+      <c r="B474" s="5" t="n"/>
+      <c r="C474" s="6" t="n"/>
+      <c r="D474" s="6" t="n"/>
+      <c r="E474" s="6" t="n"/>
+      <c r="F474" s="5" t="n"/>
+      <c r="G474" s="5" t="n"/>
+      <c r="H474" s="6" t="n"/>
+    </row>
+    <row r="475" hidden="1" outlineLevel="2">
+      <c r="A475" s="4" t="n">
+        <v>118.25</v>
+      </c>
+      <c r="B475" s="5" t="n"/>
+      <c r="C475" s="6" t="n"/>
+      <c r="D475" s="6" t="n"/>
+      <c r="E475" s="6" t="n"/>
+      <c r="F475" s="5" t="n"/>
+      <c r="G475" s="5" t="n"/>
+      <c r="H475" s="6" t="n"/>
+    </row>
+    <row r="476" hidden="1" outlineLevel="2">
+      <c r="A476" s="4" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="B476" s="5" t="n"/>
+      <c r="C476" s="6" t="n"/>
+      <c r="D476" s="6" t="n"/>
+      <c r="E476" s="6" t="n"/>
+      <c r="F476" s="5" t="n"/>
+      <c r="G476" s="5" t="n"/>
+      <c r="H476" s="6" t="n"/>
+    </row>
+    <row r="477" hidden="1" outlineLevel="2">
+      <c r="A477" s="4" t="n">
+        <v>118.75</v>
+      </c>
+      <c r="B477" s="5" t="n"/>
+      <c r="C477" s="6" t="n"/>
+      <c r="D477" s="6" t="n"/>
+      <c r="E477" s="6" t="n"/>
+      <c r="F477" s="5" t="n"/>
+      <c r="G477" s="5" t="n"/>
+      <c r="H477" s="6" t="n"/>
+    </row>
+    <row r="478" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A478" s="4" t="n">
+        <v>119</v>
+      </c>
+      <c r="B478" s="5" t="n"/>
+      <c r="C478" s="6" t="n"/>
+      <c r="D478" s="6" t="n"/>
+      <c r="E478" s="6" t="n"/>
+      <c r="F478" s="5" t="n"/>
+      <c r="G478" s="5" t="n"/>
+      <c r="H478" s="6" t="n"/>
+    </row>
+    <row r="479" hidden="1" outlineLevel="2">
+      <c r="A479" s="4" t="n">
+        <v>119.25</v>
+      </c>
+      <c r="B479" s="5" t="n"/>
+      <c r="C479" s="6" t="n"/>
+      <c r="D479" s="6" t="n"/>
+      <c r="E479" s="6" t="n"/>
+      <c r="F479" s="5" t="n"/>
+      <c r="G479" s="5" t="n"/>
+      <c r="H479" s="6" t="n"/>
+    </row>
+    <row r="480" hidden="1" outlineLevel="2">
+      <c r="A480" s="4" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="B480" s="5" t="n"/>
+      <c r="C480" s="6" t="n"/>
+      <c r="D480" s="6" t="n"/>
+      <c r="E480" s="6" t="n"/>
+      <c r="F480" s="5" t="n"/>
+      <c r="G480" s="5" t="n"/>
+      <c r="H480" s="6" t="n"/>
+    </row>
+    <row r="481" hidden="1" outlineLevel="2">
+      <c r="A481" s="4" t="n">
+        <v>119.75</v>
+      </c>
+      <c r="B481" s="5" t="n"/>
+      <c r="C481" s="6" t="n"/>
+      <c r="D481" s="6" t="n"/>
+      <c r="E481" s="6" t="n"/>
+      <c r="F481" s="5" t="n"/>
+      <c r="G481" s="5" t="n"/>
+      <c r="H481" s="6" t="n"/>
+    </row>
+    <row r="482" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A482" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="B482" s="5" t="n"/>
+      <c r="C482" s="6" t="n"/>
+      <c r="D482" s="6" t="n"/>
+      <c r="E482" s="6" t="n"/>
+      <c r="F482" s="5" t="n"/>
+      <c r="G482" s="5" t="n"/>
+      <c r="H482" s="6" t="n"/>
+    </row>
+    <row r="483" hidden="1" outlineLevel="2">
+      <c r="A483" s="4" t="n">
+        <v>120.25</v>
+      </c>
+      <c r="B483" s="5" t="n"/>
+      <c r="C483" s="6" t="n"/>
+      <c r="D483" s="6" t="n"/>
+      <c r="E483" s="6" t="n"/>
+      <c r="F483" s="5" t="n"/>
+      <c r="G483" s="5" t="n"/>
+      <c r="H483" s="6" t="n"/>
+    </row>
+    <row r="484" hidden="1" outlineLevel="2">
+      <c r="A484" s="4" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="B484" s="5" t="n"/>
+      <c r="C484" s="6" t="n"/>
+      <c r="D484" s="6" t="n"/>
+      <c r="E484" s="6" t="n"/>
+      <c r="F484" s="5" t="n"/>
+      <c r="G484" s="5" t="n"/>
+      <c r="H484" s="6" t="n"/>
+    </row>
+    <row r="485" hidden="1" outlineLevel="2">
+      <c r="A485" s="4" t="n">
+        <v>120.75</v>
+      </c>
+      <c r="B485" s="5" t="n"/>
+      <c r="C485" s="6" t="n"/>
+      <c r="D485" s="6" t="n"/>
+      <c r="E485" s="6" t="n"/>
+      <c r="F485" s="5" t="n"/>
+      <c r="G485" s="5" t="n"/>
+      <c r="H485" s="6" t="n"/>
+    </row>
+    <row r="486" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A486" s="4" t="n">
+        <v>121</v>
+      </c>
+      <c r="B486" s="5" t="n"/>
+      <c r="C486" s="6" t="n"/>
+      <c r="D486" s="6" t="n"/>
+      <c r="E486" s="6" t="n"/>
+      <c r="F486" s="5" t="n"/>
+      <c r="G486" s="5" t="n"/>
+      <c r="H486" s="6" t="n"/>
+    </row>
+    <row r="487" hidden="1" outlineLevel="2">
+      <c r="A487" s="4" t="n">
+        <v>121.25</v>
+      </c>
+      <c r="B487" s="5" t="n"/>
+      <c r="C487" s="6" t="n"/>
+      <c r="D487" s="6" t="n"/>
+      <c r="E487" s="6" t="n"/>
+      <c r="F487" s="5" t="n"/>
+      <c r="G487" s="5" t="n"/>
+      <c r="H487" s="6" t="n"/>
+    </row>
+    <row r="488" hidden="1" outlineLevel="2">
+      <c r="A488" s="4" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="B488" s="5" t="n"/>
+      <c r="C488" s="6" t="n"/>
+      <c r="D488" s="6" t="n"/>
+      <c r="E488" s="6" t="n"/>
+      <c r="F488" s="5" t="n"/>
+      <c r="G488" s="5" t="n"/>
+      <c r="H488" s="6" t="n"/>
+    </row>
+    <row r="489" hidden="1" outlineLevel="2">
+      <c r="A489" s="4" t="n">
+        <v>121.75</v>
+      </c>
+      <c r="B489" s="5" t="n"/>
+      <c r="C489" s="6" t="n"/>
+      <c r="D489" s="6" t="n"/>
+      <c r="E489" s="6" t="n"/>
+      <c r="F489" s="5" t="n"/>
+      <c r="G489" s="5" t="n"/>
+      <c r="H489" s="6" t="n"/>
+    </row>
+    <row r="490" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A490" s="4" t="n">
+        <v>122</v>
+      </c>
+      <c r="B490" s="5" t="n"/>
+      <c r="C490" s="6" t="n"/>
+      <c r="D490" s="6" t="n"/>
+      <c r="E490" s="6" t="n"/>
+      <c r="F490" s="5" t="n"/>
+      <c r="G490" s="5" t="n"/>
+      <c r="H490" s="6" t="n"/>
+    </row>
+    <row r="491" hidden="1" outlineLevel="2">
+      <c r="A491" s="4" t="n">
+        <v>122.25</v>
+      </c>
+      <c r="B491" s="5" t="n"/>
+      <c r="C491" s="6" t="n"/>
+      <c r="D491" s="6" t="n"/>
+      <c r="E491" s="6" t="n"/>
+      <c r="F491" s="5" t="n"/>
+      <c r="G491" s="5" t="n"/>
+      <c r="H491" s="6" t="n"/>
+    </row>
+    <row r="492" hidden="1" outlineLevel="2">
+      <c r="A492" s="4" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="B492" s="5" t="n"/>
+      <c r="C492" s="6" t="n"/>
+      <c r="D492" s="6" t="n"/>
+      <c r="E492" s="6" t="n"/>
+      <c r="F492" s="5" t="n"/>
+      <c r="G492" s="5" t="n"/>
+      <c r="H492" s="6" t="n"/>
+    </row>
+    <row r="493" hidden="1" outlineLevel="2">
+      <c r="A493" s="4" t="n">
+        <v>122.75</v>
+      </c>
+      <c r="B493" s="5" t="n"/>
+      <c r="C493" s="6" t="n"/>
+      <c r="D493" s="6" t="n"/>
+      <c r="E493" s="6" t="n"/>
+      <c r="F493" s="5" t="n"/>
+      <c r="G493" s="5" t="n"/>
+      <c r="H493" s="6" t="n"/>
+    </row>
+    <row r="494" collapsed="1">
+      <c r="A494" s="4" t="n">
         <v>123</v>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B494" s="5" t="inlineStr">
         <is>
           <t>matrix</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>alter Code (handgeschrieben, läuft so in der Firmware):
-matrixMovieFX(7620, 85, 100, 6)</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="C494" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_FADEOUT, Farben SCHEME_ICE
+Eisblau, blendet über die 4 Takte weich nach Schwarz.</t>
+        </is>
+      </c>
+      <c r="D494" s="6" t="n"/>
+      <c r="E494" s="6" t="inlineStr">
         <is>
           <t>Szene Fadeout, ICE: blendet über die 4 Takte weich nach Schwarz (die Matrix kann ihren Regen behalten).</t>
         </is>
       </c>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5">
+      <c r="F494" s="5" t="n"/>
+      <c r="G494" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H22" s="6" t="inlineStr">
+      <c r="H494" s="6" t="inlineStr">
         <is>
           <t>matrixMovieFX(7620, 85, 100, 6)</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="7" t="n">
+    <row r="495" hidden="1" outlineLevel="2">
+      <c r="A495" s="4" t="n">
+        <v>123.25</v>
+      </c>
+      <c r="B495" s="5" t="n"/>
+      <c r="C495" s="6" t="n"/>
+      <c r="D495" s="6" t="n"/>
+      <c r="E495" s="6" t="n"/>
+      <c r="F495" s="5" t="n"/>
+      <c r="G495" s="5" t="n"/>
+      <c r="H495" s="6" t="n"/>
+    </row>
+    <row r="496" hidden="1" outlineLevel="2">
+      <c r="A496" s="4" t="n">
+        <v>123.5</v>
+      </c>
+      <c r="B496" s="5" t="n"/>
+      <c r="C496" s="6" t="n"/>
+      <c r="D496" s="6" t="n"/>
+      <c r="E496" s="6" t="n"/>
+      <c r="F496" s="5" t="n"/>
+      <c r="G496" s="5" t="n"/>
+      <c r="H496" s="6" t="n"/>
+    </row>
+    <row r="497" hidden="1" outlineLevel="2">
+      <c r="A497" s="4" t="n">
+        <v>123.75</v>
+      </c>
+      <c r="B497" s="5" t="n"/>
+      <c r="C497" s="6" t="n"/>
+      <c r="D497" s="6" t="n"/>
+      <c r="E497" s="6" t="n"/>
+      <c r="F497" s="5" t="n"/>
+      <c r="G497" s="5" t="n"/>
+      <c r="H497" s="6" t="n"/>
+    </row>
+    <row r="498" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A498" s="4" t="n">
+        <v>124</v>
+      </c>
+      <c r="B498" s="5" t="n"/>
+      <c r="C498" s="6" t="n"/>
+      <c r="D498" s="6" t="n"/>
+      <c r="E498" s="6" t="n"/>
+      <c r="F498" s="5" t="n"/>
+      <c r="G498" s="5" t="n"/>
+      <c r="H498" s="6" t="n"/>
+    </row>
+    <row r="499" hidden="1" outlineLevel="2">
+      <c r="A499" s="4" t="n">
+        <v>124.25</v>
+      </c>
+      <c r="B499" s="5" t="n"/>
+      <c r="C499" s="6" t="n"/>
+      <c r="D499" s="6" t="n"/>
+      <c r="E499" s="6" t="n"/>
+      <c r="F499" s="5" t="n"/>
+      <c r="G499" s="5" t="n"/>
+      <c r="H499" s="6" t="n"/>
+    </row>
+    <row r="500" hidden="1" outlineLevel="2">
+      <c r="A500" s="4" t="n">
+        <v>124.5</v>
+      </c>
+      <c r="B500" s="5" t="n"/>
+      <c r="C500" s="6" t="n"/>
+      <c r="D500" s="6" t="n"/>
+      <c r="E500" s="6" t="n"/>
+      <c r="F500" s="5" t="n"/>
+      <c r="G500" s="5" t="n"/>
+      <c r="H500" s="6" t="n"/>
+    </row>
+    <row r="501" hidden="1" outlineLevel="2">
+      <c r="A501" s="4" t="n">
+        <v>124.75</v>
+      </c>
+      <c r="B501" s="5" t="n"/>
+      <c r="C501" s="6" t="n"/>
+      <c r="D501" s="6" t="n"/>
+      <c r="E501" s="6" t="n"/>
+      <c r="F501" s="5" t="n"/>
+      <c r="G501" s="5" t="n"/>
+      <c r="H501" s="6" t="n"/>
+    </row>
+    <row r="502" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A502" s="4" t="n">
+        <v>125</v>
+      </c>
+      <c r="B502" s="5" t="n"/>
+      <c r="C502" s="6" t="n"/>
+      <c r="D502" s="6" t="n"/>
+      <c r="E502" s="6" t="n"/>
+      <c r="F502" s="5" t="n"/>
+      <c r="G502" s="5" t="n"/>
+      <c r="H502" s="6" t="n"/>
+    </row>
+    <row r="503" hidden="1" outlineLevel="2">
+      <c r="A503" s="4" t="n">
+        <v>125.25</v>
+      </c>
+      <c r="B503" s="5" t="n"/>
+      <c r="C503" s="6" t="n"/>
+      <c r="D503" s="6" t="n"/>
+      <c r="E503" s="6" t="n"/>
+      <c r="F503" s="5" t="n"/>
+      <c r="G503" s="5" t="n"/>
+      <c r="H503" s="6" t="n"/>
+    </row>
+    <row r="504" hidden="1" outlineLevel="2">
+      <c r="A504" s="4" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="B504" s="5" t="n"/>
+      <c r="C504" s="6" t="n"/>
+      <c r="D504" s="6" t="n"/>
+      <c r="E504" s="6" t="n"/>
+      <c r="F504" s="5" t="n"/>
+      <c r="G504" s="5" t="n"/>
+      <c r="H504" s="6" t="n"/>
+    </row>
+    <row r="505" hidden="1" outlineLevel="2">
+      <c r="A505" s="4" t="n">
+        <v>125.75</v>
+      </c>
+      <c r="B505" s="5" t="n"/>
+      <c r="C505" s="6" t="n"/>
+      <c r="D505" s="6" t="n"/>
+      <c r="E505" s="6" t="n"/>
+      <c r="F505" s="5" t="n"/>
+      <c r="G505" s="5" t="n"/>
+      <c r="H505" s="6" t="n"/>
+    </row>
+    <row r="506" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A506" s="4" t="n">
+        <v>126</v>
+      </c>
+      <c r="B506" s="5" t="n"/>
+      <c r="C506" s="6" t="n"/>
+      <c r="D506" s="6" t="n"/>
+      <c r="E506" s="6" t="n"/>
+      <c r="F506" s="5" t="n"/>
+      <c r="G506" s="5" t="n"/>
+      <c r="H506" s="6" t="n"/>
+    </row>
+    <row r="507" hidden="1" outlineLevel="2">
+      <c r="A507" s="4" t="n">
+        <v>126.25</v>
+      </c>
+      <c r="B507" s="5" t="n"/>
+      <c r="C507" s="6" t="n"/>
+      <c r="D507" s="6" t="n"/>
+      <c r="E507" s="6" t="n"/>
+      <c r="F507" s="5" t="n"/>
+      <c r="G507" s="5" t="n"/>
+      <c r="H507" s="6" t="n"/>
+    </row>
+    <row r="508" hidden="1" outlineLevel="2">
+      <c r="A508" s="4" t="n">
+        <v>126.5</v>
+      </c>
+      <c r="B508" s="5" t="n"/>
+      <c r="C508" s="6" t="n"/>
+      <c r="D508" s="6" t="n"/>
+      <c r="E508" s="6" t="n"/>
+      <c r="F508" s="5" t="n"/>
+      <c r="G508" s="5" t="n"/>
+      <c r="H508" s="6" t="n"/>
+    </row>
+    <row r="509" hidden="1" outlineLevel="2">
+      <c r="A509" s="4" t="n">
+        <v>126.75</v>
+      </c>
+      <c r="B509" s="5" t="n"/>
+      <c r="C509" s="6" t="n"/>
+      <c r="D509" s="6" t="n"/>
+      <c r="E509" s="6" t="n"/>
+      <c r="F509" s="5" t="n"/>
+      <c r="G509" s="5" t="n"/>
+      <c r="H509" s="6" t="n"/>
+    </row>
+    <row r="510">
+      <c r="A510" s="7" t="n">
         <v>127</v>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B510" t="inlineStr">
         <is>
           <t>Ende</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C510" t="inlineStr">
         <is>
           <t>10 sek. BLACK</t>
         </is>
       </c>
-      <c r="F23" t="n">
+      <c r="F510" t="n">
         <v>0</v>
       </c>
-      <c r="G23">
+      <c r="G510">
         <f>$C$3</f>
         <v/>
       </c>
